--- a/outputs/tables/results_15_11a.xlsx
+++ b/outputs/tables/results_15_11a.xlsx
@@ -466,22 +466,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.897</v>
+        <v>0.864</v>
       </c>
       <c r="C2" t="n">
-        <v>0.79</v>
+        <v>0.755</v>
       </c>
       <c r="D2" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="E2" t="n">
-        <v>0.699</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0.739</v>
       </c>
       <c r="G2" t="n">
-        <v>0.665</v>
+        <v>0.679</v>
       </c>
     </row>
     <row r="3">
@@ -491,22 +491,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.613</v>
+        <v>0.652</v>
       </c>
       <c r="C3" t="n">
-        <v>0.376</v>
+        <v>0.412</v>
       </c>
       <c r="D3" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="E3" t="n">
-        <v>0.38</v>
+        <v>0.354</v>
       </c>
       <c r="F3" t="n">
-        <v>0.53</v>
+        <v>0.664</v>
       </c>
       <c r="G3" t="n">
-        <v>0.361</v>
+        <v>0.417</v>
       </c>
     </row>
     <row r="4">
@@ -516,22 +516,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.745</v>
+        <v>0.767</v>
       </c>
       <c r="C4" t="n">
-        <v>0.579</v>
+        <v>0.611</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.641</v>
       </c>
       <c r="E4" t="n">
-        <v>0.605</v>
+        <v>0.577</v>
       </c>
       <c r="F4" t="n">
-        <v>0.646</v>
+        <v>0.645</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.577</v>
       </c>
     </row>
     <row r="5">
@@ -541,22 +541,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.748</v>
+        <v>0.749</v>
       </c>
       <c r="C5" t="n">
-        <v>0.587</v>
+        <v>0.551</v>
       </c>
       <c r="D5" t="n">
-        <v>0.708</v>
+        <v>0.641</v>
       </c>
       <c r="E5" t="n">
-        <v>0.606</v>
+        <v>0.539</v>
       </c>
       <c r="F5" t="n">
-        <v>0.677</v>
+        <v>0.713</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="6">
@@ -566,22 +566,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.747</v>
+        <v>0.757</v>
       </c>
       <c r="C6" t="n">
-        <v>0.573</v>
+        <v>0.592</v>
       </c>
       <c r="D6" t="n">
-        <v>0.657</v>
+        <v>0.697</v>
       </c>
       <c r="E6" t="n">
-        <v>0.552</v>
+        <v>0.611</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="G6" t="n">
-        <v>0.583</v>
+        <v>0.529</v>
       </c>
     </row>
     <row r="7">
@@ -591,22 +591,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.744</v>
+        <v>0.701</v>
       </c>
       <c r="C7" t="n">
-        <v>0.541</v>
+        <v>0.498</v>
       </c>
       <c r="D7" t="n">
-        <v>0.582</v>
+        <v>0.613</v>
       </c>
       <c r="E7" t="n">
-        <v>0.503</v>
+        <v>0.581</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.542</v>
       </c>
       <c r="G7" t="n">
-        <v>0.471</v>
+        <v>0.444</v>
       </c>
     </row>
   </sheetData>
@@ -667,17 +667,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.126</v>
+        <v>0.008</v>
       </c>
       <c r="D2" t="n">
-        <v>0.13</v>
+        <v>0.532</v>
       </c>
       <c r="E2" t="n">
-        <v>0.127</v>
+        <v>0.112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.052</t>
         </is>
       </c>
     </row>
@@ -693,17 +693,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.212</v>
+        <v>0.242</v>
       </c>
       <c r="D3" t="n">
-        <v>0.521</v>
+        <v>0.546</v>
       </c>
       <c r="E3" t="n">
-        <v>0.274</v>
+        <v>0.302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.030</t>
         </is>
       </c>
     </row>
@@ -719,17 +719,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.17</v>
+        <v>0.167</v>
       </c>
       <c r="D4" t="n">
-        <v>0.385</v>
+        <v>0.419</v>
       </c>
       <c r="E4" t="n">
-        <v>0.213</v>
+        <v>0.217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.025</t>
         </is>
       </c>
     </row>
@@ -745,17 +745,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.189</v>
+        <v>0.116</v>
       </c>
       <c r="D5" t="n">
-        <v>0.394</v>
+        <v>0.486</v>
       </c>
       <c r="E5" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.021</t>
+          <t>-0.037</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.181</v>
+        <v>0.132</v>
       </c>
       <c r="D6" t="n">
-        <v>0.408</v>
+        <v>0.478</v>
       </c>
       <c r="E6" t="n">
-        <v>0.227</v>
+        <v>0.201</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.023</t>
+          <t>-0.035</t>
         </is>
       </c>
     </row>
@@ -797,17 +797,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.19</v>
+        <v>0.047</v>
       </c>
       <c r="D7" t="n">
-        <v>0.434</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.239</v>
+        <v>0.175</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.025</t>
+          <t>-0.064</t>
         </is>
       </c>
     </row>
@@ -823,17 +823,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.111</v>
+        <v>0.064</v>
       </c>
       <c r="D8" t="n">
-        <v>0.315</v>
+        <v>0.777</v>
       </c>
       <c r="E8" t="n">
-        <v>0.152</v>
+        <v>0.207</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.072</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.387</v>
+        <v>0.259</v>
       </c>
       <c r="D9" t="n">
-        <v>0.399</v>
+        <v>0.712</v>
       </c>
       <c r="E9" t="n">
-        <v>0.389</v>
+        <v>0.349</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.045</t>
         </is>
       </c>
     </row>
@@ -875,17 +875,17 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.215</v>
       </c>
       <c r="D10" t="n">
-        <v>0.466</v>
+        <v>0.672</v>
       </c>
       <c r="E10" t="n">
-        <v>0.162</v>
+        <v>0.306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.038</t>
+          <t>-0.045</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.195</v>
+        <v>0.272</v>
       </c>
       <c r="D11" t="n">
-        <v>0.211</v>
+        <v>0.608</v>
       </c>
       <c r="E11" t="n">
-        <v>0.199</v>
+        <v>0.339</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>-0.033</t>
         </is>
       </c>
     </row>
@@ -927,17 +927,17 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.144</v>
+        <v>0.241</v>
       </c>
       <c r="D12" t="n">
-        <v>0.432</v>
+        <v>0.479</v>
       </c>
       <c r="E12" t="n">
-        <v>0.202</v>
+        <v>0.289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.029</t>
+          <t>-0.024</t>
         </is>
       </c>
     </row>
@@ -953,17 +953,17 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1</v>
+        <v>0.061</v>
       </c>
       <c r="D13" t="n">
-        <v>0.417</v>
+        <v>0.731</v>
       </c>
       <c r="E13" t="n">
-        <v>0.163</v>
+        <v>0.195</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.067</t>
         </is>
       </c>
     </row>
@@ -979,17 +979,17 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.098</v>
+        <v>0.037</v>
       </c>
       <c r="D14" t="n">
-        <v>0.354</v>
+        <v>0.792</v>
       </c>
       <c r="E14" t="n">
-        <v>0.149</v>
+        <v>0.188</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.026</t>
+          <t>-0.076</t>
         </is>
       </c>
     </row>
@@ -1005,17 +1005,17 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.42</v>
+        <v>0.023</v>
       </c>
       <c r="D15" t="n">
-        <v>0.386</v>
+        <v>0.763</v>
       </c>
       <c r="E15" t="n">
-        <v>0.413</v>
+        <v>0.171</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.003</t>
+          <t>-0.074</t>
         </is>
       </c>
     </row>
@@ -1031,17 +1031,17 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.125</v>
+        <v>0.215</v>
       </c>
       <c r="D16" t="n">
-        <v>0.442</v>
+        <v>0.61</v>
       </c>
       <c r="E16" t="n">
-        <v>0.188</v>
+        <v>0.294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.040</t>
         </is>
       </c>
     </row>
@@ -1057,17 +1057,17 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.282</v>
+        <v>0.286</v>
       </c>
       <c r="D17" t="n">
-        <v>0.183</v>
+        <v>0.628</v>
       </c>
       <c r="E17" t="n">
-        <v>0.262</v>
+        <v>0.354</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.034</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.182</v>
+        <v>0.259</v>
       </c>
       <c r="D18" t="n">
-        <v>0.369</v>
+        <v>0.482</v>
       </c>
       <c r="E18" t="n">
-        <v>0.22</v>
+        <v>0.304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.019</t>
+          <t>-0.023</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1109,17 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.165</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>0.477</v>
+        <v>0.72</v>
       </c>
       <c r="E19" t="n">
-        <v>0.227</v>
+        <v>0.202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.065</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1150,12 +1150,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Brier Score</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Best Threshold</t>
+          <t>Alarm cut-off (mean over test years)</t>
         </is>
       </c>
     </row>
@@ -1171,10 +1166,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.657</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="3">
@@ -1189,10 +1181,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.473</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="4">
@@ -1207,10 +1196,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.437</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="5">
@@ -1225,10 +1211,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.436</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="6">
@@ -1243,10 +1226,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.467</v>
+        <v>0.316</v>
       </c>
     </row>
     <row r="7">
@@ -1261,10 +1241,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.223</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.466</v>
+        <v>0.366</v>
       </c>
     </row>
     <row r="8">
@@ -1279,10 +1256,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.475</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="9">
@@ -1297,10 +1271,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.379</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="10">
@@ -1315,10 +1286,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.339</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="11">
@@ -1333,10 +1301,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.488</v>
+        <v>0.208</v>
       </c>
     </row>
     <row r="12">
@@ -1351,10 +1316,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.349</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.293</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="13">
@@ -1369,10 +1331,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.315</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="14">
@@ -1387,10 +1346,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.48</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="15">
@@ -1405,10 +1361,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.667</v>
+        <v>0.179</v>
       </c>
     </row>
     <row r="16">
@@ -1423,10 +1376,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.267</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="17">
@@ -1441,10 +1391,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.535</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="18">
@@ -1459,10 +1406,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.264</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="19">
@@ -1477,10 +1421,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.404</v>
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +1435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1550,25 +1491,20 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>brier</t>
+          <t>best_threshold</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>best_threshold</t>
+          <t>loss_07</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>loss_07</t>
+          <t>loss_09</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
-        <is>
-          <t>loss_09</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
@@ -1586,43 +1522,40 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.53</v>
+        <v>0.664</v>
       </c>
       <c r="D2" t="n">
-        <v>0.451</v>
+        <v>0.505</v>
       </c>
       <c r="E2" t="n">
-        <v>0.58</v>
+        <v>0.977</v>
       </c>
       <c r="F2" t="n">
-        <v>0.539</v>
+        <v>0.354</v>
       </c>
       <c r="G2" t="n">
-        <v>0.42</v>
+        <v>0.023</v>
       </c>
       <c r="H2" t="n">
-        <v>0.386</v>
+        <v>0.763</v>
       </c>
       <c r="I2" t="n">
-        <v>0.413</v>
+        <v>0.171</v>
       </c>
       <c r="J2" t="n">
-        <v>0.361</v>
+        <v>0.417</v>
       </c>
       <c r="K2" t="n">
-        <v>0.444</v>
+        <v>0.179</v>
       </c>
       <c r="L2" t="n">
-        <v>0.667</v>
+        <v>0.245</v>
       </c>
       <c r="M2" t="n">
-        <v>0.41</v>
+        <v>0.097</v>
       </c>
       <c r="N2" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.6</v>
+        <v>0.432</v>
       </c>
     </row>
     <row r="3">
@@ -1637,43 +1570,40 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="D3" t="n">
-        <v>0.471</v>
+        <v>0.37</v>
       </c>
       <c r="E3" t="n">
-        <v>0.613</v>
+        <v>0.741</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.387</v>
+        <v>0.259</v>
       </c>
       <c r="H3" t="n">
-        <v>0.399</v>
+        <v>0.712</v>
       </c>
       <c r="I3" t="n">
-        <v>0.389</v>
+        <v>0.349</v>
       </c>
       <c r="J3" t="n">
-        <v>0.38</v>
+        <v>0.354</v>
       </c>
       <c r="K3" t="n">
-        <v>0.443</v>
+        <v>0.333</v>
       </c>
       <c r="L3" t="n">
-        <v>0.379</v>
+        <v>0.395</v>
       </c>
       <c r="M3" t="n">
-        <v>0.39</v>
+        <v>0.304</v>
       </c>
       <c r="N3" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.602</v>
+        <v>0.404</v>
       </c>
     </row>
     <row r="4">
@@ -1688,43 +1618,40 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.613</v>
+        <v>0.652</v>
       </c>
       <c r="D4" t="n">
-        <v>0.501</v>
+        <v>0.473</v>
       </c>
       <c r="E4" t="n">
-        <v>0.788</v>
+        <v>0.758</v>
       </c>
       <c r="F4" t="n">
-        <v>0.382</v>
+        <v>0.36</v>
       </c>
       <c r="G4" t="n">
-        <v>0.212</v>
+        <v>0.242</v>
       </c>
       <c r="H4" t="n">
-        <v>0.521</v>
+        <v>0.546</v>
       </c>
       <c r="I4" t="n">
-        <v>0.274</v>
+        <v>0.302</v>
       </c>
       <c r="J4" t="n">
-        <v>0.376</v>
+        <v>0.412</v>
       </c>
       <c r="K4" t="n">
-        <v>0.289</v>
+        <v>0.403</v>
       </c>
       <c r="L4" t="n">
-        <v>0.473</v>
+        <v>0.333</v>
       </c>
       <c r="M4" t="n">
-        <v>0.305</v>
+        <v>0.272</v>
       </c>
       <c r="N4" t="n">
-        <v>0.243</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="5">
@@ -1739,43 +1666,40 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="D5" t="n">
-        <v>0.65</v>
+        <v>0.478</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.741</v>
       </c>
       <c r="F5" t="n">
-        <v>0.634</v>
+        <v>0.436</v>
       </c>
       <c r="G5" t="n">
-        <v>0.182</v>
+        <v>0.259</v>
       </c>
       <c r="H5" t="n">
-        <v>0.369</v>
+        <v>0.482</v>
       </c>
       <c r="I5" t="n">
-        <v>0.22</v>
+        <v>0.304</v>
       </c>
       <c r="J5" t="n">
-        <v>0.583</v>
+        <v>0.529</v>
       </c>
       <c r="K5" t="n">
-        <v>0.293</v>
+        <v>0.03</v>
       </c>
       <c r="L5" t="n">
-        <v>0.264</v>
+        <v>0.326</v>
       </c>
       <c r="M5" t="n">
-        <v>0.238</v>
+        <v>0.281</v>
       </c>
       <c r="N5" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.661</v>
+        <v>0.574</v>
       </c>
     </row>
     <row r="6">
@@ -1790,43 +1714,40 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.657</v>
+        <v>0.697</v>
       </c>
       <c r="D6" t="n">
-        <v>0.586</v>
+        <v>0.499</v>
       </c>
       <c r="E6" t="n">
-        <v>0.856</v>
+        <v>0.759</v>
       </c>
       <c r="F6" t="n">
-        <v>0.503</v>
+        <v>0.459</v>
       </c>
       <c r="G6" t="n">
-        <v>0.144</v>
+        <v>0.241</v>
       </c>
       <c r="H6" t="n">
-        <v>0.432</v>
+        <v>0.479</v>
       </c>
       <c r="I6" t="n">
-        <v>0.202</v>
+        <v>0.289</v>
       </c>
       <c r="J6" t="n">
-        <v>0.552</v>
+        <v>0.611</v>
       </c>
       <c r="K6" t="n">
-        <v>0.349</v>
+        <v>0.115</v>
       </c>
       <c r="L6" t="n">
-        <v>0.293</v>
+        <v>0.313</v>
       </c>
       <c r="M6" t="n">
-        <v>0.23</v>
+        <v>0.265</v>
       </c>
       <c r="N6" t="n">
-        <v>0.173</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.644</v>
+        <v>0.581</v>
       </c>
     </row>
     <row r="7">
@@ -1841,43 +1762,40 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.747</v>
+        <v>0.757</v>
       </c>
       <c r="D7" t="n">
-        <v>0.604</v>
+        <v>0.576</v>
       </c>
       <c r="E7" t="n">
-        <v>0.819</v>
+        <v>0.868</v>
       </c>
       <c r="F7" t="n">
-        <v>0.536</v>
+        <v>0.455</v>
       </c>
       <c r="G7" t="n">
-        <v>0.181</v>
+        <v>0.132</v>
       </c>
       <c r="H7" t="n">
-        <v>0.408</v>
+        <v>0.478</v>
       </c>
       <c r="I7" t="n">
-        <v>0.227</v>
+        <v>0.201</v>
       </c>
       <c r="J7" t="n">
-        <v>0.573</v>
+        <v>0.592</v>
       </c>
       <c r="K7" t="n">
-        <v>0.238</v>
+        <v>0.316</v>
       </c>
       <c r="L7" t="n">
-        <v>0.467</v>
+        <v>0.236</v>
       </c>
       <c r="M7" t="n">
-        <v>0.249</v>
+        <v>0.166</v>
       </c>
       <c r="N7" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.654</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="8">
@@ -1895,40 +1813,37 @@
         <v>0.739</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.471</v>
       </c>
       <c r="E8" t="n">
-        <v>0.902</v>
+        <v>0.963</v>
       </c>
       <c r="F8" t="n">
-        <v>0.609</v>
+        <v>0.314</v>
       </c>
       <c r="G8" t="n">
-        <v>0.098</v>
+        <v>0.037</v>
       </c>
       <c r="H8" t="n">
-        <v>0.354</v>
+        <v>0.792</v>
       </c>
       <c r="I8" t="n">
-        <v>0.149</v>
+        <v>0.188</v>
       </c>
       <c r="J8" t="n">
-        <v>0.665</v>
+        <v>0.679</v>
       </c>
       <c r="K8" t="n">
-        <v>0.357</v>
+        <v>0.157</v>
       </c>
       <c r="L8" t="n">
-        <v>0.48</v>
+        <v>0.263</v>
       </c>
       <c r="M8" t="n">
-        <v>0.175</v>
+        <v>0.112</v>
       </c>
       <c r="N8" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.715</v>
+        <v>0.408</v>
       </c>
     </row>
     <row r="9">
@@ -1943,43 +1858,40 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="D9" t="n">
-        <v>0.718</v>
+        <v>0.468</v>
       </c>
       <c r="E9" t="n">
-        <v>0.889</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.679</v>
+        <v>0.315</v>
       </c>
       <c r="G9" t="n">
-        <v>0.111</v>
+        <v>0.064</v>
       </c>
       <c r="H9" t="n">
-        <v>0.315</v>
+        <v>0.777</v>
       </c>
       <c r="I9" t="n">
-        <v>0.152</v>
+        <v>0.207</v>
       </c>
       <c r="J9" t="n">
-        <v>0.699</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.353</v>
+        <v>0.162</v>
       </c>
       <c r="L9" t="n">
-        <v>0.475</v>
+        <v>0.278</v>
       </c>
       <c r="M9" t="n">
-        <v>0.172</v>
+        <v>0.135</v>
       </c>
       <c r="N9" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.74</v>
+        <v>0.412</v>
       </c>
     </row>
     <row r="10">
@@ -1994,43 +1906,40 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.897</v>
+        <v>0.864</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.631</v>
       </c>
       <c r="E10" t="n">
-        <v>0.874</v>
+        <v>0.992</v>
       </c>
       <c r="F10" t="n">
-        <v>0.763</v>
+        <v>0.507</v>
       </c>
       <c r="G10" t="n">
-        <v>0.126</v>
+        <v>0.008</v>
       </c>
       <c r="H10" t="n">
-        <v>0.13</v>
+        <v>0.532</v>
       </c>
       <c r="I10" t="n">
-        <v>0.127</v>
+        <v>0.112</v>
       </c>
       <c r="J10" t="n">
-        <v>0.79</v>
+        <v>0.755</v>
       </c>
       <c r="K10" t="n">
-        <v>0.186</v>
+        <v>0.286</v>
       </c>
       <c r="L10" t="n">
-        <v>0.657</v>
+        <v>0.165</v>
       </c>
       <c r="M10" t="n">
-        <v>0.127</v>
+        <v>0.06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.871</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="11">
@@ -2045,43 +1954,40 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.542</v>
       </c>
       <c r="D11" t="n">
-        <v>0.58</v>
+        <v>0.494</v>
       </c>
       <c r="E11" t="n">
-        <v>0.835</v>
+        <v>0.928</v>
       </c>
       <c r="F11" t="n">
-        <v>0.492</v>
+        <v>0.353</v>
       </c>
       <c r="G11" t="n">
-        <v>0.165</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.477</v>
+        <v>0.72</v>
       </c>
       <c r="I11" t="n">
-        <v>0.227</v>
+        <v>0.202</v>
       </c>
       <c r="J11" t="n">
-        <v>0.471</v>
+        <v>0.444</v>
       </c>
       <c r="K11" t="n">
-        <v>0.353</v>
+        <v>0.04</v>
       </c>
       <c r="L11" t="n">
-        <v>0.404</v>
+        <v>0.266</v>
       </c>
       <c r="M11" t="n">
-        <v>0.258</v>
+        <v>0.137</v>
       </c>
       <c r="N11" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.609</v>
+        <v>0.452</v>
       </c>
     </row>
     <row r="12">
@@ -2096,43 +2002,40 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.582</v>
+        <v>0.613</v>
       </c>
       <c r="D12" t="n">
-        <v>0.644</v>
+        <v>0.493</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.536</v>
+        <v>0.347</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1</v>
+        <v>0.061</v>
       </c>
       <c r="H12" t="n">
-        <v>0.417</v>
+        <v>0.731</v>
       </c>
       <c r="I12" t="n">
-        <v>0.163</v>
+        <v>0.195</v>
       </c>
       <c r="J12" t="n">
-        <v>0.503</v>
+        <v>0.581</v>
       </c>
       <c r="K12" t="n">
-        <v>0.352</v>
+        <v>0.103</v>
       </c>
       <c r="L12" t="n">
-        <v>0.315</v>
+        <v>0.262</v>
       </c>
       <c r="M12" t="n">
-        <v>0.195</v>
+        <v>0.128</v>
       </c>
       <c r="N12" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.67</v>
+        <v>0.447</v>
       </c>
     </row>
     <row r="13">
@@ -2147,43 +2050,40 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.744</v>
+        <v>0.701</v>
       </c>
       <c r="D13" t="n">
-        <v>0.57</v>
+        <v>0.526</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.953</v>
       </c>
       <c r="F13" t="n">
-        <v>0.469</v>
+        <v>0.382</v>
       </c>
       <c r="G13" t="n">
-        <v>0.19</v>
+        <v>0.047</v>
       </c>
       <c r="H13" t="n">
-        <v>0.434</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="I13" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="L13" t="n">
         <v>0.239</v>
       </c>
-      <c r="J13" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.223</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.466</v>
-      </c>
       <c r="M13" t="n">
-        <v>0.263</v>
+        <v>0.111</v>
       </c>
       <c r="N13" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.633</v>
+        <v>0.483</v>
       </c>
     </row>
     <row r="14">
@@ -2198,43 +2098,40 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.646</v>
+        <v>0.645</v>
       </c>
       <c r="D14" t="n">
-        <v>0.625</v>
+        <v>0.439</v>
       </c>
       <c r="E14" t="n">
-        <v>0.875</v>
+        <v>0.785</v>
       </c>
       <c r="F14" t="n">
-        <v>0.533</v>
+        <v>0.347</v>
       </c>
       <c r="G14" t="n">
-        <v>0.125</v>
+        <v>0.215</v>
       </c>
       <c r="H14" t="n">
-        <v>0.442</v>
+        <v>0.61</v>
       </c>
       <c r="I14" t="n">
-        <v>0.188</v>
+        <v>0.294</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.577</v>
       </c>
       <c r="K14" t="n">
-        <v>0.209</v>
+        <v>0.191</v>
       </c>
       <c r="L14" t="n">
-        <v>0.267</v>
+        <v>0.333</v>
       </c>
       <c r="M14" t="n">
-        <v>0.22</v>
+        <v>0.254</v>
       </c>
       <c r="N14" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.645</v>
+        <v>0.492</v>
       </c>
     </row>
     <row r="15">
@@ -2249,43 +2146,40 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.641</v>
       </c>
       <c r="D15" t="n">
-        <v>0.64</v>
+        <v>0.437</v>
       </c>
       <c r="E15" t="n">
-        <v>0.914</v>
+        <v>0.785</v>
       </c>
       <c r="F15" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="J15" t="n">
         <v>0.577</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.466</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.605</v>
-      </c>
       <c r="K15" t="n">
-        <v>0.204</v>
+        <v>0.174</v>
       </c>
       <c r="L15" t="n">
-        <v>0.339</v>
+        <v>0.352</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2</v>
+        <v>0.261</v>
       </c>
       <c r="N15" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.639</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="16">
@@ -2300,43 +2194,40 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.745</v>
+        <v>0.767</v>
       </c>
       <c r="D16" t="n">
-        <v>0.626</v>
+        <v>0.6</v>
       </c>
       <c r="E16" t="n">
-        <v>0.83</v>
+        <v>0.833</v>
       </c>
       <c r="F16" t="n">
-        <v>0.548</v>
+        <v>0.511</v>
       </c>
       <c r="G16" t="n">
-        <v>0.17</v>
+        <v>0.167</v>
       </c>
       <c r="H16" t="n">
-        <v>0.385</v>
+        <v>0.419</v>
       </c>
       <c r="I16" t="n">
-        <v>0.213</v>
+        <v>0.217</v>
       </c>
       <c r="J16" t="n">
-        <v>0.579</v>
+        <v>0.611</v>
       </c>
       <c r="K16" t="n">
-        <v>0.226</v>
+        <v>0.402</v>
       </c>
       <c r="L16" t="n">
-        <v>0.437</v>
+        <v>0.242</v>
       </c>
       <c r="M16" t="n">
-        <v>0.234</v>
+        <v>0.192</v>
       </c>
       <c r="N16" t="n">
-        <v>0.191</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.675</v>
+        <v>0.646</v>
       </c>
     </row>
     <row r="17">
@@ -2351,43 +2242,40 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.677</v>
+        <v>0.713</v>
       </c>
       <c r="D17" t="n">
-        <v>0.67</v>
+        <v>0.386</v>
       </c>
       <c r="E17" t="n">
-        <v>0.718</v>
+        <v>0.714</v>
       </c>
       <c r="F17" t="n">
-        <v>0.713</v>
+        <v>0.379</v>
       </c>
       <c r="G17" t="n">
-        <v>0.282</v>
+        <v>0.286</v>
       </c>
       <c r="H17" t="n">
-        <v>0.183</v>
+        <v>0.628</v>
       </c>
       <c r="I17" t="n">
-        <v>0.262</v>
+        <v>0.354</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="K17" t="n">
-        <v>0.25</v>
+        <v>0.192</v>
       </c>
       <c r="L17" t="n">
-        <v>0.535</v>
+        <v>0.389</v>
       </c>
       <c r="M17" t="n">
-        <v>0.253</v>
+        <v>0.32</v>
       </c>
       <c r="N17" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.791</v>
+        <v>0.459</v>
       </c>
     </row>
     <row r="18">
@@ -2402,43 +2290,40 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.708</v>
+        <v>0.641</v>
       </c>
       <c r="D18" t="n">
-        <v>0.709</v>
+        <v>0.421</v>
       </c>
       <c r="E18" t="n">
-        <v>0.805</v>
+        <v>0.728</v>
       </c>
       <c r="F18" t="n">
-        <v>0.696</v>
+        <v>0.515</v>
       </c>
       <c r="G18" t="n">
-        <v>0.195</v>
+        <v>0.272</v>
       </c>
       <c r="H18" t="n">
-        <v>0.211</v>
+        <v>0.608</v>
       </c>
       <c r="I18" t="n">
-        <v>0.199</v>
+        <v>0.339</v>
       </c>
       <c r="J18" t="n">
-        <v>0.606</v>
+        <v>0.539</v>
       </c>
       <c r="K18" t="n">
-        <v>0.25</v>
+        <v>0.208</v>
       </c>
       <c r="L18" t="n">
-        <v>0.488</v>
+        <v>0.373</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2</v>
+        <v>0.306</v>
       </c>
       <c r="N18" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.794</v>
+        <v>0.478</v>
       </c>
     </row>
     <row r="19">
@@ -2453,43 +2338,40 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.748</v>
+        <v>0.749</v>
       </c>
       <c r="D19" t="n">
-        <v>0.604</v>
+        <v>0.573</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.884</v>
       </c>
       <c r="F19" t="n">
-        <v>0.527</v>
+        <v>0.445</v>
       </c>
       <c r="G19" t="n">
-        <v>0.189</v>
+        <v>0.116</v>
       </c>
       <c r="H19" t="n">
-        <v>0.394</v>
+        <v>0.486</v>
       </c>
       <c r="I19" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="J19" t="n">
-        <v>0.587</v>
+        <v>0.551</v>
       </c>
       <c r="K19" t="n">
-        <v>0.233</v>
+        <v>0.306</v>
       </c>
       <c r="L19" t="n">
-        <v>0.436</v>
+        <v>0.227</v>
       </c>
       <c r="M19" t="n">
-        <v>0.25</v>
+        <v>0.153</v>
       </c>
       <c r="N19" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.662</v>
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -2555,7 +2437,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.174</v>
+        <v>3.494</v>
       </c>
       <c r="D2" t="n">
         <v>0.667</v>
@@ -2568,6 +2450,11 @@
           <t>Decision Tree</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2581,10 +2468,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.957</v>
+        <v>-1.085</v>
       </c>
       <c r="D3" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>3</v>
@@ -2594,11 +2481,6 @@
           <t>LightGBM</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2612,10 +2494,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-1.108</v>
+        <v>0.501</v>
       </c>
       <c r="D4" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -2638,10 +2520,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.742</v>
+        <v>-1.133</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
@@ -2664,10 +2546,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-1.932</v>
+        <v>0.204</v>
       </c>
       <c r="D6" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -2690,10 +2572,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.706</v>
+        <v>3.334</v>
       </c>
       <c r="D7" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
@@ -2716,10 +2598,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-2.131</v>
+        <v>0.435</v>
       </c>
       <c r="D8" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
@@ -2742,10 +2624,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-1.107</v>
+        <v>-1.228</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -2768,10 +2650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-4.19</v>
+        <v>-2.79</v>
       </c>
       <c r="D10" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
@@ -2794,10 +2676,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-4.297</v>
+        <v>-3.753</v>
       </c>
       <c r="D11" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -2820,10 +2702,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-2.14</v>
+        <v>-2.314</v>
       </c>
       <c r="D12" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
@@ -2846,10 +2728,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-1.46</v>
+        <v>-0.885</v>
       </c>
       <c r="D13" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>3</v>
@@ -2937,16 +2819,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.174</v>
+        <v>3.494</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.131</v>
+        <v>0.435</v>
       </c>
       <c r="D4" t="n">
         <v>0.667</v>
       </c>
       <c r="E4" t="n">
-        <v>0.667</v>
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -2956,21 +2843,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.957</v>
+        <v>-1.085</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.107</v>
+        <v>-1.228</v>
       </c>
       <c r="D5" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
+        <v>0.333</v>
       </c>
     </row>
     <row r="6">
@@ -2980,16 +2862,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.108</v>
+        <v>0.501</v>
       </c>
       <c r="C6" t="n">
-        <v>-4.19</v>
+        <v>-2.79</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.333</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.667</v>
       </c>
     </row>
     <row r="7">
@@ -2999,16 +2881,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.742</v>
+        <v>-1.133</v>
       </c>
       <c r="C7" t="n">
-        <v>-4.297</v>
+        <v>-3.753</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="E7" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="8">
@@ -3018,16 +2900,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.932</v>
+        <v>0.204</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.14</v>
+        <v>-2.314</v>
       </c>
       <c r="D8" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="9">
@@ -3037,16 +2919,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.706</v>
+        <v>3.334</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.46</v>
+        <v>-0.885</v>
       </c>
       <c r="D9" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3152,10 +3034,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9265863122647752</v>
+        <v>1.028174815066897</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.8501461146113416</v>
+        <v>-0.8747475420764206</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3178,22 +3060,22 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>-0.9560395534847204</v>
+        <v>-0.943717525843264</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.7614875654324363</v>
+        <v>-0.7673619190650265</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.8596650558447358</v>
+        <v>-0.8855584115054902</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.9207121452627373</v>
+        <v>-0.8828967693274231</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8406271733779473</v>
+        <v>-0.7535225188601469</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7654476686680941</v>
+        <v>-0.866598314825418</v>
       </c>
     </row>
     <row r="3">
@@ -3208,10 +3090,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.6542367001081102</v>
+        <v>0.7911943644863896</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7863099168273141</v>
+        <v>0.7889034748419088</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3234,22 +3116,22 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.7602334581970298</v>
+        <v>0.6504462261562497</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6359875800366256</v>
+        <v>0.7917379920657813</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8290485760380926</v>
+        <v>0.8820442086805217</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8657536232434998</v>
+        <v>0.7860689576180364</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8024969368506468</v>
+        <v>0.7928589504187892</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7701228968039814</v>
+        <v>0.7131643056150712</v>
       </c>
     </row>
     <row r="4">
@@ -3264,19 +3146,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.5710484494305808</v>
+        <v>0.605079008173689</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5505683435119144</v>
+        <v>-0.4430207377987793</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3290,22 +3172,22 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>-0.3060631041203119</v>
+        <v>-0.3401127381686726</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.5910784730513579</v>
+        <v>0.02544574055289366</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5111258226201523</v>
+        <v>-0.4305353497202984</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5586845865036839</v>
+        <v>-0.45550612587726</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5424521005201449</v>
+        <v>-0.5426891210905509</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5739820287820051</v>
+        <v>-0.5969656850308234</v>
       </c>
     </row>
     <row r="5">
@@ -3320,19 +3202,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.3275418728407907</v>
+        <v>0.3671982857071837</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9029537103531189</v>
+        <v>0.8559364433455986</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3342,26 +3224,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>reportable</t>
+          <t>non-monotone</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.8850546727255526</v>
+        <v>0.8860782092369827</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5002986811705231</v>
+        <v>0.4933814531499772</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9214079847251373</v>
+        <v>0.8403395248293732</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9350347558674083</v>
+        <v>0.8719873650807006</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9208527479806852</v>
+        <v>0.6317397873192069</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8561962013528077</v>
+        <v>0.871533361861824</v>
       </c>
     </row>
     <row r="6">
@@ -3376,14 +3258,14 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.2773734126547638</v>
+        <v>0.3264464808682149</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3493613287215372</v>
+        <v>0.2909722992617821</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3402,22 +3284,22 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>-0.1032107381408622</v>
+        <v>0.2816895121901261</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4174638922038403</v>
+        <v>0.1626099008040462</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7363635532739682</v>
+        <v>0.7460293485188076</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2812587652392342</v>
+        <v>0.7457172214372422</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7427053615415067</v>
+        <v>0.3002550863334381</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.241150567660822</v>
+        <v>-0.2400671842917834</v>
       </c>
     </row>
     <row r="7">
@@ -3432,10 +3314,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2561800350696424</v>
+        <v>0.3094097782386557</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4208330499318674</v>
+        <v>-0.4134204545546528</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3444,7 +3326,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3458,22 +3340,22 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>-0.7931592247819945</v>
+        <v>-0.8024041157697863</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3967241847934448</v>
+        <v>-0.4217865988196605</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3895043791282821</v>
+        <v>-0.347805654804097</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.44494191507029</v>
+        <v>-0.4050543102896452</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3531146271776288</v>
+        <v>-0.3997504988242319</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5208725287142381</v>
+        <v>-0.460957047599489</v>
       </c>
     </row>
     <row r="8">
@@ -3488,19 +3370,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1193977124790572</v>
+        <v>0.1459404118688925</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04557599331390627</v>
+        <v>0.2075772904493873</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3514,22 +3396,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>-0.09629930569732617</v>
+        <v>-0.2679176689999989</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2454631318451621</v>
+        <v>-0.003364451149075939</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09215629152405835</v>
+        <v>0.3214663993785055</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2797573075974532</v>
+        <v>0.5748443277436313</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1125944690013834</v>
+        <v>0.700526401952597</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.001004304896245808</v>
+        <v>0.09368818152026918</v>
       </c>
     </row>
     <row r="9">
@@ -3544,10 +3426,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.1011193558996304</v>
+        <v>0.1276158018641854</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5115169928661184</v>
+        <v>0.6401560515371097</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -3570,22 +3452,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9446948581645295</v>
+        <v>0.9077251719676878</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2055171304562143</v>
+        <v>0.3531858925148132</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7609499101432272</v>
+        <v>0.7959797319896051</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5563630746846909</v>
+        <v>0.7028503713721251</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4666709110475459</v>
+        <v>0.5774617317020944</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3471567092015995</v>
+        <v>0.4704228964053333</v>
       </c>
     </row>
     <row r="10">
@@ -3600,19 +3482,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.09082432606716123</v>
+        <v>0.09894954112919906</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4294555279147809</v>
+        <v>0.3820486949543465</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3626,28 +3508,26 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>-0.3338476561245598</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.5715904730313753</v>
-      </c>
+        <v>-0.2291476560397598</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>0.546826040018039</v>
+        <v>0.6297323122920723</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5229421000588953</v>
+        <v>0.5562253145025079</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3359689557706665</v>
+        <v>0.3820486949543465</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1353174598395</v>
+        <v>-0.07046726864009516</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>p_roe</t>
+          <t>l_assets</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3656,10 +3536,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.05473046835154706</v>
+        <v>0.0498700146732942</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4777226175957648</v>
+        <v>0.5906667752084218</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -3668,12 +3548,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>lowers risk</t>
+          <t>raises risk</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3682,20 +3562,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>-0.8829776051711064</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
+        <v>0.9253145243895884</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.01873613841988211</v>
+      </c>
       <c r="K11" t="n">
-        <v>-0.6966622873865808</v>
+        <v>0.6256250451340086</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3846476250237861</v>
+        <v>0.5557085052828351</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4777226175957648</v>
+        <v>0.1726912559981267</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4393462907808177</v>
+        <v>0.9155130148722369</v>
       </c>
     </row>
     <row r="12">
@@ -3710,10 +3592,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04293170879251015</v>
+        <v>0.0492648911907287</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4521540911098725</v>
+        <v>-0.7795190609409296</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3722,7 +3604,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3732,32 +3614,30 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>non-monotone</t>
+          <t>reportable</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>-0.9399936133719057</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-0.3529095816908794</v>
-      </c>
+        <v>-0.9673672177207374</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>-0.7061009443174298</v>
+        <v>-0.7896694292044539</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1391119653083442</v>
+        <v>-0.4937363346701218</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1426358921537539</v>
+        <v>-0.1049740935444794</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5513986005288657</v>
+        <v>-0.7795190609409296</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>l_assets</t>
+          <t>p_roe</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3766,24 +3646,24 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02786723628180906</v>
+        <v>0.03843036897383465</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7212820164239462</v>
+        <v>-0.6626578224609326</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3792,28 +3672,26 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9593608852380473</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.2912548156217548</v>
-      </c>
+        <v>-0.8843421783418381</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>0.744583230804149</v>
+        <v>-0.7566987461879002</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8334196791731932</v>
+        <v>-0.4763251558640076</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6979808020437432</v>
+        <v>-0.2653049523125874</v>
       </c>
       <c r="N13" t="n">
-        <v>0.305870586292858</v>
+        <v>-0.6626578224609326</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>p_roa</t>
+          <t>l_loans</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3822,19 +3700,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02295011574974603</v>
+        <v>0.03761508684692079</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3467844784464797</v>
+        <v>-0.09299429856361068</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3844,32 +3722,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>reportable</t>
+          <t>weak/noisy</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6056669098469238</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-0.2220149032530638</v>
-      </c>
+        <v>-0.6622599500651964</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>-0.8520520887291622</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-0.4510167188506159</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-0.4870885407404747</v>
-      </c>
+        <v>0.254910663695001</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>-0.2425522380423436</v>
+        <v>-0.09299429856361068</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>r_cti</t>
+          <t>c_leverage</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3878,19 +3750,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.01843497381777106</v>
+        <v>0.02399745652544161</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3284025128537458</v>
+        <v>0.5632545968554429</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3900,32 +3772,30 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>reportable</t>
+          <t>weak/noisy</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.1739525125801134</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.03130369573642432</v>
-      </c>
+        <v>-0.2010884650353895</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>0.5729904391587065</v>
+        <v>0.5632545968554429</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7886989191386873</v>
+        <v>0.6625800631880311</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4828525131273782</v>
+        <v>0.7118715974987947</v>
       </c>
       <c r="N15" t="n">
-        <v>0.01535865970019359</v>
+        <v>0.3107883189337868</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>x_loans_gross</t>
+          <t>r_dep_liab</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3934,10 +3804,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.01721962998688673</v>
+        <v>0.02300361046831802</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1527592351245601</v>
+        <v>-0.5088941514230449</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3946,12 +3816,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3960,26 +3830,26 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.2583954166090168</v>
+        <v>0.8931009968579126</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>0.1527592351245601</v>
+        <v>-0.6443134998961501</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.01890137895093107</v>
+        <v>-0.6132014898815135</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4847434414606122</v>
+        <v>-0.5088941514230449</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2235916619418466</v>
+        <v>0.4491520736807521</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>c_eqratio</t>
+          <t>inc_nii</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3988,19 +3858,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01675021584638044</v>
+        <v>0.01798178209554291</v>
       </c>
       <c r="D17" t="n">
-        <v>0.05282997114440009</v>
+        <v>0.4940848773341945</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4010,32 +3880,30 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>weak/noisy</t>
+          <t>reportable</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>-0.9442227256629292</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.6743117087762643</v>
-      </c>
+        <v>0.7508996459559023</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
-        <v>-0.1443095191281283</v>
+        <v>0.4811071820813183</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2671898290856319</v>
+        <v>0.5171929347138725</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2267675931589018</v>
+        <v>0.4940848773341945</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1211076508701016</v>
+        <v>0.3222451785662913</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>c_leverage</t>
+          <t>r_loans_assets</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4044,54 +3912,52 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01628334930962503</v>
+        <v>0.01776075751430692</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02090598614255212</v>
+        <v>-0.4522092031340975</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>weak/noisy</t>
+          <t>reportable</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8554233531278415</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-0.01372941228540354</v>
-      </c>
+        <v>-0.0743513169972382</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>0.05554138457050777</v>
+        <v>-0.629359094036499</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3125672931641892</v>
+        <v>-0.5949403664296113</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4699844374802075</v>
+        <v>-0.4522092031340975</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1245702620095101</v>
+        <v>-0.08844205058246539</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>inc_nii</t>
+          <t>x_ib_liab</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4100,19 +3966,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0158586996350084</v>
+        <v>0.01561091055187576</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2446780438675702</v>
+        <v>0.07720996221086084</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4126,26 +3992,26 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7957428921585367</v>
+        <v>-0.7789950174530728</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
-        <v>0.4629312423976412</v>
+        <v>0.7625832200369187</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2042913840283628</v>
+        <v>0.6231073162781569</v>
       </c>
       <c r="M19" t="n">
-        <v>0.07114333173461385</v>
+        <v>0.07720996221086084</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2446780438675702</v>
+        <v>-0.2336862112221306</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>l_loans</t>
+          <t>x_loans_gross</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4154,10 +4020,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01579385868721337</v>
+        <v>0.0106461746631332</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2102211965039827</v>
+        <v>-0.3377674437257613</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -4166,42 +4032,40 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>weak/noisy</t>
+          <t>non-monotone</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>-0.9216271484216884</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.3691480340409087</v>
-      </c>
+        <v>-0.5369648390026898</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>0.1271015883484623</v>
+        <v>-0.183142259367312</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6160627695018456</v>
+        <v>-0.2380772999571943</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2933408046595032</v>
+        <v>-0.4166726887422401</v>
       </c>
       <c r="N20" t="n">
-        <v>0.06074357636202452</v>
+        <v>-0.3377674437257613</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>inc_op</t>
+          <t>p_roa</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4210,54 +4074,52 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.014775861726635</v>
+        <v>0.009785784291943385</v>
       </c>
       <c r="D21" t="n">
-        <v>0.03879948696708894</v>
+        <v>-0.6501866993393738</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>weak/noisy</t>
+          <t>reportable</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>-0.7854007029733936</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.0956584239277749</v>
-      </c>
+        <v>-0.3637140636162855</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>0.6035777785626077</v>
+        <v>-0.8427971715139384</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3435087042773529</v>
+        <v>-0.6533511031794792</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1077717961005886</v>
+        <v>-0.6501866993393738</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.01805944999359701</v>
+        <v>-0.3744589155168295</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>x_dep</t>
+          <t>inc_op</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4266,19 +4128,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01394502921070186</v>
+        <v>0.008676348939200286</v>
       </c>
       <c r="D22" t="n">
-        <v>0.02092406826779631</v>
+        <v>0.3635502929556129</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4292,28 +4154,26 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.01908724499681764</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.01078215976994487</v>
-      </c>
+        <v>-0.08644418935517809</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="n">
-        <v>0.1969284645667818</v>
+        <v>0.7145110040752476</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02276089153877498</v>
+        <v>0.3635502929556129</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1156350731373365</v>
+        <v>0.4741934089946412</v>
       </c>
       <c r="N22" t="n">
-        <v>0.316506137619509</v>
+        <v>0.1976102710175017</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>x_ib_liab</t>
+          <t>c_eqratio</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4322,10 +4182,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.009152551474894551</v>
+        <v>0.008075565826686426</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.04751412914801201</v>
+        <v>-0.5293420992316948</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -4334,7 +4194,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4348,28 +4208,26 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>-0.04283346816640132</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-0.4990597395874152</v>
-      </c>
+        <v>-0.9842524595173295</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
-        <v>0.07701146774078677</v>
+        <v>-0.5293420992316948</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5045583851396825</v>
+        <v>-0.2059986385557094</v>
       </c>
       <c r="M23" t="n">
-        <v>0.191187786639902</v>
+        <v>-0.6680944844966552</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.05219479012962269</v>
+        <v>0.07685456718032103</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>r_loans_assets</t>
+          <t>r_cti</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4378,10 +4236,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.008553948843064438</v>
+        <v>0.007190283537018697</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.07561025955867963</v>
+        <v>0.07982069553730753</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4390,12 +4248,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>lowers risk</t>
+          <t>raises risk</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4404,28 +4262,28 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>-0.288878793842746</v>
+        <v>0.1841191059292823</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5069463220709832</v>
+        <v>-0.07737215590971719</v>
       </c>
       <c r="K24" t="n">
-        <v>0.08026007973424193</v>
+        <v>0.5926739301524859</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1815027688649611</v>
+        <v>0.2131915004260302</v>
       </c>
       <c r="M24" t="n">
-        <v>0.03028224974760179</v>
+        <v>-0.0244777148546672</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2453835145277737</v>
+        <v>-0.2085907392400383</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>r_dep_liab</t>
+          <t>x_dep</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4434,10 +4292,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.007007032705532137</v>
+        <v>0.0040828026864785</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.140599762983867</v>
+        <v>0.1486797345842358</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4446,12 +4304,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>lowers risk</t>
+          <t>raises risk</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4460,20 +4318,18 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>-0.3607412825128094</v>
+        <v>0.1184528131779062</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
-        <v>-0.140599762983867</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.325176830166655</v>
-      </c>
+        <v>0.2517137030695448</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
-        <v>0.1267605301309362</v>
+        <v>-0.1574231869242516</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.28857799339305</v>
+        <v>0.1789066559905654</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/results_15_11a.xlsx
+++ b/outputs/tables/results_15_11a.xlsx
@@ -466,22 +466,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.897</v>
+        <v>0.864</v>
       </c>
       <c r="C2" t="n">
-        <v>0.79</v>
+        <v>0.755</v>
       </c>
       <c r="D2" t="n">
-        <v>0.74</v>
+        <v>0.725</v>
       </c>
       <c r="E2" t="n">
-        <v>0.699</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0.739</v>
       </c>
       <c r="G2" t="n">
-        <v>0.665</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="3">
@@ -491,22 +491,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.613</v>
+        <v>0.66</v>
       </c>
       <c r="C3" t="n">
-        <v>0.376</v>
+        <v>0.423</v>
       </c>
       <c r="D3" t="n">
-        <v>0.54</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="F3" t="n">
-        <v>0.53</v>
+        <v>0.653</v>
       </c>
       <c r="G3" t="n">
-        <v>0.361</v>
+        <v>0.388</v>
       </c>
     </row>
     <row r="4">
@@ -516,22 +516,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.745</v>
+        <v>0.735</v>
       </c>
       <c r="C4" t="n">
-        <v>0.579</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.661</v>
       </c>
       <c r="E4" t="n">
-        <v>0.605</v>
+        <v>0.604</v>
       </c>
       <c r="F4" t="n">
-        <v>0.646</v>
+        <v>0.678</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="5">
@@ -541,22 +541,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.748</v>
+        <v>0.732</v>
       </c>
       <c r="C5" t="n">
-        <v>0.587</v>
+        <v>0.549</v>
       </c>
       <c r="D5" t="n">
-        <v>0.708</v>
+        <v>0.671</v>
       </c>
       <c r="E5" t="n">
-        <v>0.606</v>
+        <v>0.556</v>
       </c>
       <c r="F5" t="n">
-        <v>0.677</v>
+        <v>0.709</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5669999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -566,22 +566,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.747</v>
+        <v>0.749</v>
       </c>
       <c r="C6" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.573</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.657</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.552</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.583</v>
       </c>
     </row>
     <row r="7">
@@ -591,22 +591,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.744</v>
+        <v>0.665</v>
       </c>
       <c r="C7" t="n">
-        <v>0.541</v>
+        <v>0.466</v>
       </c>
       <c r="D7" t="n">
-        <v>0.582</v>
+        <v>0.547</v>
       </c>
       <c r="E7" t="n">
-        <v>0.503</v>
+        <v>0.494</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.594</v>
       </c>
       <c r="G7" t="n">
-        <v>0.471</v>
+        <v>0.511</v>
       </c>
     </row>
   </sheetData>
@@ -667,17 +667,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.126</v>
+        <v>0.008</v>
       </c>
       <c r="D2" t="n">
-        <v>0.13</v>
+        <v>0.53</v>
       </c>
       <c r="E2" t="n">
-        <v>0.127</v>
+        <v>0.112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.052</t>
         </is>
       </c>
     </row>
@@ -693,17 +693,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.212</v>
+        <v>0.245</v>
       </c>
       <c r="D3" t="n">
-        <v>0.521</v>
+        <v>0.545</v>
       </c>
       <c r="E3" t="n">
-        <v>0.274</v>
+        <v>0.305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.030</t>
         </is>
       </c>
     </row>
@@ -719,17 +719,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.17</v>
+        <v>0.151</v>
       </c>
       <c r="D4" t="n">
-        <v>0.385</v>
+        <v>0.486</v>
       </c>
       <c r="E4" t="n">
-        <v>0.213</v>
+        <v>0.218</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.033</t>
         </is>
       </c>
     </row>
@@ -745,17 +745,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.189</v>
+        <v>0.162</v>
       </c>
       <c r="D5" t="n">
-        <v>0.394</v>
+        <v>0.533</v>
       </c>
       <c r="E5" t="n">
-        <v>0.23</v>
+        <v>0.236</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.021</t>
+          <t>-0.037</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.181</v>
+        <v>0.147</v>
       </c>
       <c r="D6" t="n">
-        <v>0.408</v>
+        <v>0.473</v>
       </c>
       <c r="E6" t="n">
-        <v>0.227</v>
+        <v>0.212</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.023</t>
+          <t>-0.032</t>
         </is>
       </c>
     </row>
@@ -797,17 +797,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.19</v>
+        <v>0.171</v>
       </c>
       <c r="D7" t="n">
-        <v>0.434</v>
+        <v>0.61</v>
       </c>
       <c r="E7" t="n">
-        <v>0.239</v>
+        <v>0.259</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.025</t>
+          <t>-0.044</t>
         </is>
       </c>
     </row>
@@ -823,17 +823,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.111</v>
+        <v>0.064</v>
       </c>
       <c r="D8" t="n">
-        <v>0.315</v>
+        <v>0.777</v>
       </c>
       <c r="E8" t="n">
-        <v>0.152</v>
+        <v>0.207</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.072</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.387</v>
+        <v>0.276</v>
       </c>
       <c r="D9" t="n">
-        <v>0.399</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.389</v>
+        <v>0.358</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.041</t>
         </is>
       </c>
     </row>
@@ -875,17 +875,17 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.241</v>
       </c>
       <c r="D10" t="n">
-        <v>0.466</v>
+        <v>0.522</v>
       </c>
       <c r="E10" t="n">
-        <v>0.162</v>
+        <v>0.298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.038</t>
+          <t>-0.029</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.195</v>
+        <v>0.246</v>
       </c>
       <c r="D11" t="n">
-        <v>0.211</v>
+        <v>0.636</v>
       </c>
       <c r="E11" t="n">
-        <v>0.199</v>
+        <v>0.324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>-0.039</t>
         </is>
       </c>
     </row>
@@ -927,17 +927,17 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.144</v>
+        <v>0.241</v>
       </c>
       <c r="D12" t="n">
-        <v>0.432</v>
+        <v>0.413</v>
       </c>
       <c r="E12" t="n">
-        <v>0.202</v>
+        <v>0.276</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.029</t>
+          <t>-0.017</t>
         </is>
       </c>
     </row>
@@ -953,17 +953,17 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1</v>
+        <v>0.076</v>
       </c>
       <c r="D13" t="n">
-        <v>0.417</v>
+        <v>0.669</v>
       </c>
       <c r="E13" t="n">
-        <v>0.163</v>
+        <v>0.194</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.059</t>
         </is>
       </c>
     </row>
@@ -979,17 +979,17 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.098</v>
+        <v>0.037</v>
       </c>
       <c r="D14" t="n">
-        <v>0.354</v>
+        <v>0.797</v>
       </c>
       <c r="E14" t="n">
-        <v>0.149</v>
+        <v>0.189</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.026</t>
+          <t>-0.076</t>
         </is>
       </c>
     </row>
@@ -1005,17 +1005,17 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.42</v>
+        <v>0.232</v>
       </c>
       <c r="D15" t="n">
-        <v>0.386</v>
+        <v>0.707</v>
       </c>
       <c r="E15" t="n">
-        <v>0.413</v>
+        <v>0.327</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.003</t>
+          <t>-0.047</t>
         </is>
       </c>
     </row>
@@ -1031,17 +1031,17 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.125</v>
+        <v>0.105</v>
       </c>
       <c r="D16" t="n">
-        <v>0.442</v>
+        <v>0.588</v>
       </c>
       <c r="E16" t="n">
-        <v>0.188</v>
+        <v>0.202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.048</t>
         </is>
       </c>
     </row>
@@ -1057,17 +1057,17 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.282</v>
+        <v>0.246</v>
       </c>
       <c r="D17" t="n">
-        <v>0.183</v>
+        <v>0.675</v>
       </c>
       <c r="E17" t="n">
-        <v>0.262</v>
+        <v>0.331</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.042</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.182</v>
+        <v>0.241</v>
       </c>
       <c r="D18" t="n">
-        <v>0.369</v>
+        <v>0.441</v>
       </c>
       <c r="E18" t="n">
-        <v>0.22</v>
+        <v>0.281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.019</t>
+          <t>-0.020</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1109,17 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.165</v>
+        <v>0.038</v>
       </c>
       <c r="D19" t="n">
-        <v>0.477</v>
+        <v>0.833</v>
       </c>
       <c r="E19" t="n">
-        <v>0.227</v>
+        <v>0.197</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.080</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1150,12 +1150,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Brier Score</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Best Threshold</t>
+          <t>Alarm cut-off (mean over test years)</t>
         </is>
       </c>
     </row>
@@ -1171,10 +1166,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.657</v>
+        <v>0.287</v>
       </c>
     </row>
     <row r="3">
@@ -1189,10 +1181,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.473</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="4">
@@ -1207,10 +1196,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.437</v>
+        <v>0.404</v>
       </c>
     </row>
     <row r="5">
@@ -1225,10 +1211,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.436</v>
+        <v>0.355</v>
       </c>
     </row>
     <row r="6">
@@ -1243,10 +1226,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.467</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="7">
@@ -1261,10 +1241,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.223</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.466</v>
+        <v>0.435</v>
       </c>
     </row>
     <row r="8">
@@ -1279,10 +1256,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.475</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="9">
@@ -1297,10 +1271,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.379</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="10">
@@ -1315,10 +1286,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.339</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="11">
@@ -1333,10 +1301,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.488</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="12">
@@ -1351,10 +1316,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.349</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.293</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="13">
@@ -1369,10 +1331,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.315</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="14">
@@ -1387,10 +1346,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.48</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="15">
@@ -1405,10 +1361,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.667</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="16">
@@ -1423,10 +1376,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.267</v>
+        <v>0.236</v>
       </c>
     </row>
     <row r="17">
@@ -1441,10 +1391,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.535</v>
+        <v>0.177</v>
       </c>
     </row>
     <row r="18">
@@ -1459,10 +1406,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.264</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="19">
@@ -1477,10 +1421,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.404</v>
+        <v>0.151</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +1435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1550,25 +1491,20 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>brier</t>
+          <t>best_threshold</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>best_threshold</t>
+          <t>loss_07</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>loss_07</t>
+          <t>loss_09</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
-        <is>
-          <t>loss_09</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
@@ -1586,43 +1522,40 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.53</v>
+        <v>0.653</v>
       </c>
       <c r="D2" t="n">
-        <v>0.451</v>
+        <v>0.399</v>
       </c>
       <c r="E2" t="n">
-        <v>0.58</v>
+        <v>0.768</v>
       </c>
       <c r="F2" t="n">
-        <v>0.539</v>
+        <v>0.334</v>
       </c>
       <c r="G2" t="n">
-        <v>0.42</v>
+        <v>0.232</v>
       </c>
       <c r="H2" t="n">
-        <v>0.386</v>
+        <v>0.707</v>
       </c>
       <c r="I2" t="n">
-        <v>0.413</v>
+        <v>0.327</v>
       </c>
       <c r="J2" t="n">
-        <v>0.361</v>
+        <v>0.388</v>
       </c>
       <c r="K2" t="n">
-        <v>0.444</v>
+        <v>0.263</v>
       </c>
       <c r="L2" t="n">
-        <v>0.667</v>
+        <v>0.375</v>
       </c>
       <c r="M2" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="N2" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.6</v>
+        <v>0.415</v>
       </c>
     </row>
     <row r="3">
@@ -1637,43 +1570,40 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.54</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.471</v>
+        <v>0.363</v>
       </c>
       <c r="E3" t="n">
-        <v>0.613</v>
+        <v>0.724</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.354</v>
       </c>
       <c r="G3" t="n">
-        <v>0.387</v>
+        <v>0.276</v>
       </c>
       <c r="H3" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="L3" t="n">
         <v>0.399</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.379</v>
-      </c>
       <c r="M3" t="n">
-        <v>0.39</v>
+        <v>0.317</v>
       </c>
       <c r="N3" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.602</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="4">
@@ -1688,43 +1618,40 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.613</v>
+        <v>0.66</v>
       </c>
       <c r="D4" t="n">
-        <v>0.501</v>
+        <v>0.471</v>
       </c>
       <c r="E4" t="n">
-        <v>0.788</v>
+        <v>0.755</v>
       </c>
       <c r="F4" t="n">
-        <v>0.382</v>
+        <v>0.36</v>
       </c>
       <c r="G4" t="n">
-        <v>0.212</v>
+        <v>0.245</v>
       </c>
       <c r="H4" t="n">
-        <v>0.521</v>
+        <v>0.545</v>
       </c>
       <c r="I4" t="n">
-        <v>0.274</v>
+        <v>0.305</v>
       </c>
       <c r="J4" t="n">
-        <v>0.376</v>
+        <v>0.423</v>
       </c>
       <c r="K4" t="n">
-        <v>0.289</v>
+        <v>0.403</v>
       </c>
       <c r="L4" t="n">
-        <v>0.473</v>
+        <v>0.335</v>
       </c>
       <c r="M4" t="n">
-        <v>0.305</v>
+        <v>0.275</v>
       </c>
       <c r="N4" t="n">
-        <v>0.243</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.533</v>
       </c>
     </row>
     <row r="5">
@@ -1739,43 +1666,40 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.65</v>
+        <v>0.523</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.759</v>
       </c>
       <c r="F5" t="n">
-        <v>0.634</v>
+        <v>0.483</v>
       </c>
       <c r="G5" t="n">
-        <v>0.182</v>
+        <v>0.241</v>
       </c>
       <c r="H5" t="n">
-        <v>0.369</v>
+        <v>0.441</v>
       </c>
       <c r="I5" t="n">
-        <v>0.22</v>
+        <v>0.281</v>
       </c>
       <c r="J5" t="n">
-        <v>0.583</v>
+        <v>0.573</v>
       </c>
       <c r="K5" t="n">
-        <v>0.293</v>
+        <v>0.03</v>
       </c>
       <c r="L5" t="n">
-        <v>0.264</v>
+        <v>0.301</v>
       </c>
       <c r="M5" t="n">
-        <v>0.238</v>
+        <v>0.261</v>
       </c>
       <c r="N5" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.661</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="6">
@@ -1790,43 +1714,40 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.657</v>
+        <v>0.714</v>
       </c>
       <c r="D6" t="n">
-        <v>0.586</v>
+        <v>0.549</v>
       </c>
       <c r="E6" t="n">
-        <v>0.856</v>
+        <v>0.759</v>
       </c>
       <c r="F6" t="n">
-        <v>0.503</v>
+        <v>0.507</v>
       </c>
       <c r="G6" t="n">
-        <v>0.144</v>
+        <v>0.241</v>
       </c>
       <c r="H6" t="n">
-        <v>0.432</v>
+        <v>0.413</v>
       </c>
       <c r="I6" t="n">
-        <v>0.202</v>
+        <v>0.276</v>
       </c>
       <c r="J6" t="n">
-        <v>0.552</v>
+        <v>0.634</v>
       </c>
       <c r="K6" t="n">
-        <v>0.349</v>
+        <v>0.133</v>
       </c>
       <c r="L6" t="n">
         <v>0.293</v>
       </c>
       <c r="M6" t="n">
-        <v>0.23</v>
+        <v>0.259</v>
       </c>
       <c r="N6" t="n">
-        <v>0.173</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.644</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="7">
@@ -1841,43 +1762,40 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.747</v>
+        <v>0.749</v>
       </c>
       <c r="D7" t="n">
-        <v>0.604</v>
+        <v>0.572</v>
       </c>
       <c r="E7" t="n">
-        <v>0.819</v>
+        <v>0.853</v>
       </c>
       <c r="F7" t="n">
-        <v>0.536</v>
+        <v>0.457</v>
       </c>
       <c r="G7" t="n">
-        <v>0.181</v>
+        <v>0.147</v>
       </c>
       <c r="H7" t="n">
-        <v>0.408</v>
+        <v>0.473</v>
       </c>
       <c r="I7" t="n">
-        <v>0.227</v>
+        <v>0.212</v>
       </c>
       <c r="J7" t="n">
-        <v>0.573</v>
+        <v>0.585</v>
       </c>
       <c r="K7" t="n">
-        <v>0.238</v>
+        <v>0.325</v>
       </c>
       <c r="L7" t="n">
-        <v>0.467</v>
+        <v>0.245</v>
       </c>
       <c r="M7" t="n">
-        <v>0.249</v>
+        <v>0.18</v>
       </c>
       <c r="N7" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.654</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="8">
@@ -1895,40 +1813,37 @@
         <v>0.739</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.469</v>
       </c>
       <c r="E8" t="n">
-        <v>0.902</v>
+        <v>0.963</v>
       </c>
       <c r="F8" t="n">
-        <v>0.609</v>
+        <v>0.312</v>
       </c>
       <c r="G8" t="n">
-        <v>0.098</v>
+        <v>0.037</v>
       </c>
       <c r="H8" t="n">
-        <v>0.354</v>
+        <v>0.797</v>
       </c>
       <c r="I8" t="n">
-        <v>0.149</v>
+        <v>0.189</v>
       </c>
       <c r="J8" t="n">
-        <v>0.665</v>
+        <v>0.677</v>
       </c>
       <c r="K8" t="n">
-        <v>0.357</v>
+        <v>0.157</v>
       </c>
       <c r="L8" t="n">
-        <v>0.48</v>
+        <v>0.265</v>
       </c>
       <c r="M8" t="n">
-        <v>0.175</v>
+        <v>0.113</v>
       </c>
       <c r="N8" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.715</v>
+        <v>0.404</v>
       </c>
     </row>
     <row r="9">
@@ -1943,43 +1858,40 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.74</v>
+        <v>0.725</v>
       </c>
       <c r="D9" t="n">
-        <v>0.718</v>
+        <v>0.468</v>
       </c>
       <c r="E9" t="n">
-        <v>0.889</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.679</v>
+        <v>0.315</v>
       </c>
       <c r="G9" t="n">
-        <v>0.111</v>
+        <v>0.064</v>
       </c>
       <c r="H9" t="n">
-        <v>0.315</v>
+        <v>0.777</v>
       </c>
       <c r="I9" t="n">
-        <v>0.152</v>
+        <v>0.207</v>
       </c>
       <c r="J9" t="n">
-        <v>0.699</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.353</v>
+        <v>0.16</v>
       </c>
       <c r="L9" t="n">
-        <v>0.475</v>
+        <v>0.278</v>
       </c>
       <c r="M9" t="n">
-        <v>0.172</v>
+        <v>0.135</v>
       </c>
       <c r="N9" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.74</v>
+        <v>0.412</v>
       </c>
     </row>
     <row r="10">
@@ -1994,43 +1906,40 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.897</v>
+        <v>0.864</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.633</v>
       </c>
       <c r="E10" t="n">
-        <v>0.874</v>
+        <v>0.992</v>
       </c>
       <c r="F10" t="n">
-        <v>0.763</v>
+        <v>0.51</v>
       </c>
       <c r="G10" t="n">
-        <v>0.126</v>
+        <v>0.008</v>
       </c>
       <c r="H10" t="n">
-        <v>0.13</v>
+        <v>0.53</v>
       </c>
       <c r="I10" t="n">
-        <v>0.127</v>
+        <v>0.112</v>
       </c>
       <c r="J10" t="n">
-        <v>0.79</v>
+        <v>0.755</v>
       </c>
       <c r="K10" t="n">
-        <v>0.186</v>
+        <v>0.287</v>
       </c>
       <c r="L10" t="n">
-        <v>0.657</v>
+        <v>0.164</v>
       </c>
       <c r="M10" t="n">
-        <v>0.127</v>
+        <v>0.06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.871</v>
+        <v>0.608</v>
       </c>
     </row>
     <row r="11">
@@ -2045,43 +1954,40 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.594</v>
       </c>
       <c r="D11" t="n">
-        <v>0.58</v>
+        <v>0.453</v>
       </c>
       <c r="E11" t="n">
-        <v>0.835</v>
+        <v>0.962</v>
       </c>
       <c r="F11" t="n">
-        <v>0.492</v>
+        <v>0.298</v>
       </c>
       <c r="G11" t="n">
-        <v>0.165</v>
+        <v>0.038</v>
       </c>
       <c r="H11" t="n">
-        <v>0.477</v>
+        <v>0.833</v>
       </c>
       <c r="I11" t="n">
-        <v>0.227</v>
+        <v>0.197</v>
       </c>
       <c r="J11" t="n">
-        <v>0.471</v>
+        <v>0.511</v>
       </c>
       <c r="K11" t="n">
-        <v>0.353</v>
+        <v>0.151</v>
       </c>
       <c r="L11" t="n">
-        <v>0.404</v>
+        <v>0.276</v>
       </c>
       <c r="M11" t="n">
-        <v>0.258</v>
+        <v>0.117</v>
       </c>
       <c r="N11" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.609</v>
+        <v>0.377</v>
       </c>
     </row>
     <row r="12">
@@ -2096,43 +2002,40 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.582</v>
+        <v>0.547</v>
       </c>
       <c r="D12" t="n">
-        <v>0.644</v>
+        <v>0.534</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9</v>
+        <v>0.924</v>
       </c>
       <c r="F12" t="n">
-        <v>0.536</v>
+        <v>0.418</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1</v>
+        <v>0.076</v>
       </c>
       <c r="H12" t="n">
-        <v>0.417</v>
+        <v>0.669</v>
       </c>
       <c r="I12" t="n">
-        <v>0.163</v>
+        <v>0.194</v>
       </c>
       <c r="J12" t="n">
-        <v>0.503</v>
+        <v>0.494</v>
       </c>
       <c r="K12" t="n">
-        <v>0.352</v>
+        <v>0.158</v>
       </c>
       <c r="L12" t="n">
-        <v>0.315</v>
+        <v>0.254</v>
       </c>
       <c r="M12" t="n">
-        <v>0.195</v>
+        <v>0.135</v>
       </c>
       <c r="N12" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.67</v>
+        <v>0.488</v>
       </c>
     </row>
     <row r="13">
@@ -2147,43 +2050,40 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.744</v>
+        <v>0.665</v>
       </c>
       <c r="D13" t="n">
-        <v>0.57</v>
+        <v>0.482</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.829</v>
       </c>
       <c r="F13" t="n">
-        <v>0.469</v>
+        <v>0.364</v>
       </c>
       <c r="G13" t="n">
-        <v>0.19</v>
+        <v>0.171</v>
       </c>
       <c r="H13" t="n">
-        <v>0.434</v>
+        <v>0.61</v>
       </c>
       <c r="I13" t="n">
-        <v>0.239</v>
+        <v>0.259</v>
       </c>
       <c r="J13" t="n">
-        <v>0.541</v>
+        <v>0.466</v>
       </c>
       <c r="K13" t="n">
-        <v>0.223</v>
+        <v>0.435</v>
       </c>
       <c r="L13" t="n">
-        <v>0.466</v>
+        <v>0.303</v>
       </c>
       <c r="M13" t="n">
-        <v>0.263</v>
+        <v>0.215</v>
       </c>
       <c r="N13" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.633</v>
+        <v>0.506</v>
       </c>
     </row>
     <row r="14">
@@ -2198,43 +2098,40 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.646</v>
+        <v>0.678</v>
       </c>
       <c r="D14" t="n">
-        <v>0.625</v>
+        <v>0.524</v>
       </c>
       <c r="E14" t="n">
-        <v>0.875</v>
+        <v>0.895</v>
       </c>
       <c r="F14" t="n">
-        <v>0.533</v>
+        <v>0.382</v>
       </c>
       <c r="G14" t="n">
-        <v>0.125</v>
+        <v>0.105</v>
       </c>
       <c r="H14" t="n">
-        <v>0.442</v>
+        <v>0.588</v>
       </c>
       <c r="I14" t="n">
-        <v>0.188</v>
+        <v>0.202</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.588</v>
       </c>
       <c r="K14" t="n">
-        <v>0.209</v>
+        <v>0.236</v>
       </c>
       <c r="L14" t="n">
-        <v>0.267</v>
+        <v>0.25</v>
       </c>
       <c r="M14" t="n">
-        <v>0.22</v>
+        <v>0.154</v>
       </c>
       <c r="N14" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.645</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="15">
@@ -2249,43 +2146,40 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.661</v>
       </c>
       <c r="D15" t="n">
-        <v>0.64</v>
+        <v>0.481</v>
       </c>
       <c r="E15" t="n">
-        <v>0.914</v>
+        <v>0.759</v>
       </c>
       <c r="F15" t="n">
-        <v>0.577</v>
+        <v>0.478</v>
       </c>
       <c r="G15" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.241</v>
       </c>
       <c r="H15" t="n">
-        <v>0.466</v>
+        <v>0.522</v>
       </c>
       <c r="I15" t="n">
-        <v>0.162</v>
+        <v>0.298</v>
       </c>
       <c r="J15" t="n">
-        <v>0.605</v>
+        <v>0.604</v>
       </c>
       <c r="K15" t="n">
-        <v>0.204</v>
+        <v>0.17</v>
       </c>
       <c r="L15" t="n">
-        <v>0.339</v>
+        <v>0.326</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2</v>
+        <v>0.269</v>
       </c>
       <c r="N15" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.639</v>
+        <v>0.549</v>
       </c>
     </row>
     <row r="16">
@@ -2300,43 +2194,40 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.745</v>
+        <v>0.735</v>
       </c>
       <c r="D16" t="n">
-        <v>0.626</v>
+        <v>0.575</v>
       </c>
       <c r="E16" t="n">
-        <v>0.83</v>
+        <v>0.849</v>
       </c>
       <c r="F16" t="n">
-        <v>0.548</v>
+        <v>0.504</v>
       </c>
       <c r="G16" t="n">
-        <v>0.17</v>
+        <v>0.151</v>
       </c>
       <c r="H16" t="n">
-        <v>0.385</v>
+        <v>0.486</v>
       </c>
       <c r="I16" t="n">
-        <v>0.213</v>
+        <v>0.218</v>
       </c>
       <c r="J16" t="n">
-        <v>0.579</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.226</v>
+        <v>0.404</v>
       </c>
       <c r="L16" t="n">
-        <v>0.437</v>
+        <v>0.252</v>
       </c>
       <c r="M16" t="n">
-        <v>0.234</v>
+        <v>0.185</v>
       </c>
       <c r="N16" t="n">
-        <v>0.191</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.675</v>
+        <v>0.601</v>
       </c>
     </row>
     <row r="17">
@@ -2351,43 +2242,40 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.677</v>
+        <v>0.709</v>
       </c>
       <c r="D17" t="n">
-        <v>0.67</v>
+        <v>0.408</v>
       </c>
       <c r="E17" t="n">
-        <v>0.718</v>
+        <v>0.754</v>
       </c>
       <c r="F17" t="n">
-        <v>0.713</v>
+        <v>0.441</v>
       </c>
       <c r="G17" t="n">
-        <v>0.282</v>
+        <v>0.246</v>
       </c>
       <c r="H17" t="n">
-        <v>0.183</v>
+        <v>0.675</v>
       </c>
       <c r="I17" t="n">
-        <v>0.262</v>
+        <v>0.331</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.25</v>
+        <v>0.177</v>
       </c>
       <c r="L17" t="n">
-        <v>0.535</v>
+        <v>0.374</v>
       </c>
       <c r="M17" t="n">
-        <v>0.253</v>
+        <v>0.289</v>
       </c>
       <c r="N17" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.791</v>
+        <v>0.435</v>
       </c>
     </row>
     <row r="18">
@@ -2402,43 +2290,40 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.708</v>
+        <v>0.671</v>
       </c>
       <c r="D18" t="n">
-        <v>0.709</v>
+        <v>0.423</v>
       </c>
       <c r="E18" t="n">
-        <v>0.805</v>
+        <v>0.754</v>
       </c>
       <c r="F18" t="n">
-        <v>0.696</v>
+        <v>0.514</v>
       </c>
       <c r="G18" t="n">
-        <v>0.195</v>
+        <v>0.246</v>
       </c>
       <c r="H18" t="n">
-        <v>0.211</v>
+        <v>0.636</v>
       </c>
       <c r="I18" t="n">
-        <v>0.199</v>
+        <v>0.324</v>
       </c>
       <c r="J18" t="n">
-        <v>0.606</v>
+        <v>0.556</v>
       </c>
       <c r="K18" t="n">
-        <v>0.25</v>
+        <v>0.192</v>
       </c>
       <c r="L18" t="n">
-        <v>0.488</v>
+        <v>0.363</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2</v>
+        <v>0.285</v>
       </c>
       <c r="N18" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.794</v>
+        <v>0.464</v>
       </c>
     </row>
     <row r="19">
@@ -2453,43 +2338,40 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.748</v>
+        <v>0.732</v>
       </c>
       <c r="D19" t="n">
-        <v>0.604</v>
+        <v>0.526</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.838</v>
       </c>
       <c r="F19" t="n">
-        <v>0.527</v>
+        <v>0.431</v>
       </c>
       <c r="G19" t="n">
-        <v>0.189</v>
+        <v>0.162</v>
       </c>
       <c r="H19" t="n">
-        <v>0.394</v>
+        <v>0.533</v>
       </c>
       <c r="I19" t="n">
-        <v>0.23</v>
+        <v>0.236</v>
       </c>
       <c r="J19" t="n">
-        <v>0.587</v>
+        <v>0.549</v>
       </c>
       <c r="K19" t="n">
-        <v>0.233</v>
+        <v>0.355</v>
       </c>
       <c r="L19" t="n">
-        <v>0.436</v>
+        <v>0.273</v>
       </c>
       <c r="M19" t="n">
-        <v>0.25</v>
+        <v>0.199</v>
       </c>
       <c r="N19" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.662</v>
+        <v>0.5649999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2555,10 +2437,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.174</v>
+        <v>0.376</v>
       </c>
       <c r="D2" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -2581,10 +2463,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.957</v>
+        <v>0.344</v>
       </c>
       <c r="D3" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>3</v>
@@ -2594,11 +2476,6 @@
           <t>LightGBM</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2612,10 +2489,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-1.108</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -2638,10 +2515,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.742</v>
+        <v>2.32</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
@@ -2664,10 +2541,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-1.932</v>
+        <v>0.43</v>
       </c>
       <c r="D6" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -2690,10 +2567,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.706</v>
+        <v>2.911</v>
       </c>
       <c r="D7" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
@@ -2716,10 +2593,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-2.131</v>
+        <v>0.007</v>
       </c>
       <c r="D8" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
@@ -2742,10 +2619,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-1.107</v>
+        <v>-0.13</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -2768,10 +2645,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-4.19</v>
+        <v>-2.882</v>
       </c>
       <c r="D10" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
@@ -2794,10 +2671,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-4.297</v>
+        <v>-1.023</v>
       </c>
       <c r="D11" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -2820,10 +2697,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-2.14</v>
+        <v>-0.408</v>
       </c>
       <c r="D12" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
@@ -2846,10 +2723,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-1.46</v>
+        <v>-0.542</v>
       </c>
       <c r="D13" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>3</v>
@@ -2937,16 +2814,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.174</v>
+        <v>0.376</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.131</v>
+        <v>0.007</v>
       </c>
       <c r="D4" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="E4" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2956,21 +2833,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.957</v>
+        <v>0.344</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.107</v>
+        <v>-0.13</v>
       </c>
       <c r="D5" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
+        <v>0.333</v>
       </c>
     </row>
     <row r="6">
@@ -2980,16 +2852,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.108</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>-4.19</v>
+        <v>-2.882</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.333</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.667</v>
       </c>
     </row>
     <row r="7">
@@ -2999,16 +2871,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.742</v>
+        <v>2.32</v>
       </c>
       <c r="C7" t="n">
-        <v>-4.297</v>
+        <v>-1.023</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="E7" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="8">
@@ -3018,16 +2890,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.932</v>
+        <v>0.43</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.14</v>
+        <v>-0.408</v>
       </c>
       <c r="D8" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="9">
@@ -3037,16 +2909,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.706</v>
+        <v>2.911</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.46</v>
+        <v>-0.542</v>
       </c>
       <c r="D9" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3152,10 +3024,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9265863122647752</v>
+        <v>1.032773784137212</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.8501461146113416</v>
+        <v>-0.8719744950484274</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3178,22 +3050,22 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>-0.9560395534847204</v>
+        <v>-0.943717525843264</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.7614875654324363</v>
+        <v>-0.7371497091221957</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.8596650558447358</v>
+        <v>-0.9128862494754632</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.9207121452627373</v>
+        <v>-0.8488623243911635</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8406271733779473</v>
+        <v>-0.8042145924988621</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7654476686680941</v>
+        <v>-0.8950866657056914</v>
       </c>
     </row>
     <row r="3">
@@ -3208,10 +3080,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.6542367001081102</v>
+        <v>0.8269826604382882</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7863099168273141</v>
+        <v>0.779763660094883</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3220,7 +3092,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3230,26 +3102,26 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>reportable</t>
+          <t>non-monotone</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.7602334581970298</v>
+        <v>0.6504462261562497</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6359875800366256</v>
+        <v>0.7384028081528031</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8290485760380926</v>
+        <v>0.8335378541142042</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8657536232434998</v>
+        <v>0.8211245120369628</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8024969368506468</v>
+        <v>0.8452869480722035</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7701228968039814</v>
+        <v>0.6308204319460128</v>
       </c>
     </row>
     <row r="4">
@@ -3264,10 +3136,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.5710484494305808</v>
+        <v>0.6624594161121981</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5505683435119144</v>
+        <v>-0.5186564973361854</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3290,22 +3162,22 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>-0.3060631041203119</v>
+        <v>-0.3401127381686726</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.5910784730513579</v>
+        <v>-0.224596570834034</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5111258226201523</v>
+        <v>-0.5192711998992002</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5586845865036839</v>
+        <v>-0.5770339890900116</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5424521005201449</v>
+        <v>-0.5180417947731706</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5739820287820051</v>
+        <v>-0.5226655214839088</v>
       </c>
     </row>
     <row r="5">
@@ -3320,19 +3192,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.3275418728407907</v>
+        <v>0.4152876345499928</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9029537103531189</v>
+        <v>0.840975532836941</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3342,32 +3214,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>reportable</t>
+          <t>non-monotone</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.8850546727255526</v>
+        <v>0.8860782092369827</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5002986811705231</v>
+        <v>0.4898040182027296</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9214079847251373</v>
+        <v>0.8233414756657024</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9350347558674083</v>
+        <v>0.7097693292634097</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9208527479806852</v>
+        <v>0.8933960602842023</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8561962013528077</v>
+        <v>0.8586095900081797</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PCPIPCH</t>
+          <t>RXF11FX_REVS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3376,54 +3248,54 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.2773734126547638</v>
+        <v>0.3332198103611085</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3493613287215372</v>
+        <v>-0.4403943606759736</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>weak/noisy</t>
+          <t>non-monotone</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>-0.1032107381408622</v>
+        <v>-0.8024041157697863</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4174638922038403</v>
+        <v>-0.3878017183124833</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7363635532739682</v>
+        <v>-0.3616964032704416</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2812587652392342</v>
+        <v>-0.492987003039464</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7427053615415067</v>
+        <v>-0.33702074404163</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.241150567660822</v>
+        <v>-0.7741211673486569</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RXF11FX_REVS</t>
+          <t>PCPIPCH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3432,24 +3304,24 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2561800350696424</v>
+        <v>0.2914349150211836</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4208330499318674</v>
+        <v>0.3781523132877141</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>lowers risk</t>
+          <t>raises risk</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3458,22 +3330,22 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>-0.7931592247819945</v>
+        <v>0.2816895121901261</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3967241847934448</v>
+        <v>0.1569132566767494</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3895043791282821</v>
+        <v>0.8102242417981107</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.44494191507029</v>
+        <v>0.5624243939701383</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3531146271776288</v>
+        <v>0.4746151143853022</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5208725287142381</v>
+        <v>-0.1219769980960778</v>
       </c>
     </row>
     <row r="8">
@@ -3488,10 +3360,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1193977124790572</v>
+        <v>0.2083717687355721</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04557599331390627</v>
+        <v>0.05903570309008007</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -3500,7 +3372,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3514,22 +3386,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>-0.09629930569732617</v>
+        <v>-0.2679176689999989</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2454631318451621</v>
+        <v>0.2059383748376457</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09215629152405835</v>
+        <v>-0.08786696865748557</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2797573075974532</v>
+        <v>0.5606018884938758</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1125944690013834</v>
+        <v>0.472405890144256</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.001004304896245808</v>
+        <v>-0.5667370100534667</v>
       </c>
     </row>
     <row r="9">
@@ -3544,10 +3416,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.1011193558996304</v>
+        <v>0.1543220743360923</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5115169928661184</v>
+        <v>0.7613305615214552</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -3556,7 +3428,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3570,22 +3442,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9446948581645295</v>
+        <v>0.907728650626147</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2055171304562143</v>
+        <v>0.3933093205649017</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7609499101432272</v>
+        <v>0.7434412502655835</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5563630746846909</v>
+        <v>0.779219872777327</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4666709110475459</v>
+        <v>0.6031448953319424</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3471567092015995</v>
+        <v>0.8845982291647089</v>
       </c>
     </row>
     <row r="10">
@@ -3600,10 +3472,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.09082432606716123</v>
+        <v>0.1351485703631823</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4294555279147809</v>
+        <v>0.1662955004090336</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -3612,7 +3484,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3626,28 +3498,28 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>-0.3338476561245598</v>
+        <v>-0.2291476560397598</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5715904730313753</v>
+        <v>0.458661105782341</v>
       </c>
       <c r="K10" t="n">
-        <v>0.546826040018039</v>
+        <v>0.0486045310788026</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5229421000588953</v>
+        <v>0.5433787055846557</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3359689557706665</v>
+        <v>0.2839864697392646</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1353174598395</v>
+        <v>-0.06476909226700088</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>p_roe</t>
+          <t>p_nim</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3656,10 +3528,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.05473046835154706</v>
+        <v>0.06052978297622724</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4777226175957648</v>
+        <v>-0.5683153450447427</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -3668,7 +3540,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3678,30 +3550,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>reportable</t>
+          <t>non-monotone</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>-0.8829776051711064</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
+        <v>-0.9673504399320104</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.3600121836902482</v>
+      </c>
       <c r="K11" t="n">
-        <v>-0.6966622873865808</v>
+        <v>-0.7766185063992371</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3846476250237861</v>
+        <v>0.1324647477277681</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4777226175957648</v>
+        <v>-0.02921370777462992</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4393462907808177</v>
+        <v>-0.818500998558317</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>p_nim</t>
+          <t>l_assets</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3710,10 +3584,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04293170879251015</v>
+        <v>0.05873188725436807</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4521540911098725</v>
+        <v>0.7252423796331036</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3722,42 +3596,40 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>lowers risk</t>
+          <t>raises risk</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>non-monotone</t>
+          <t>reportable</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>-0.9399936133719057</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-0.3529095816908794</v>
-      </c>
+        <v>0.9252923269961124</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>-0.7061009443174298</v>
+        <v>0.883142113131124</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1391119653083442</v>
+        <v>0.4891149019126643</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1426358921537539</v>
+        <v>0.6886282464568604</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5513986005288657</v>
+        <v>0.7252423796331036</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>l_assets</t>
+          <t>p_roe</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3766,54 +3638,52 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02786723628180906</v>
+        <v>0.04006734634763794</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7212820164239462</v>
+        <v>-0.5232458792220661</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>reportable</t>
+          <t>weak/noisy</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9593608852380473</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.2912548156217548</v>
-      </c>
+        <v>-0.8843619886607456</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>0.744583230804149</v>
+        <v>-0.8368557913308675</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8334196791731932</v>
+        <v>-0.3890337741697946</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6979808020437432</v>
+        <v>0.1232349562970776</v>
       </c>
       <c r="N13" t="n">
-        <v>0.305870586292858</v>
+        <v>-0.5232458792220661</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>p_roa</t>
+          <t>l_loans</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3822,19 +3692,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02295011574974603</v>
+        <v>0.03675070454950769</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3467844784464797</v>
+        <v>-0.3842714159071761</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3844,32 +3714,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>reportable</t>
+          <t>weak/noisy</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6056669098469238</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-0.2220149032530638</v>
-      </c>
+        <v>-0.6623012233435205</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>-0.8520520887291622</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-0.4510167188506159</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-0.4870885407404747</v>
-      </c>
+        <v>-0.03060525907994812</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>-0.2425522380423436</v>
+        <v>-0.3842714159071761</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>r_cti</t>
+          <t>r_dep_liab</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3878,54 +3742,54 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.01843497381777106</v>
+        <v>0.02525540277799509</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3284025128537458</v>
+        <v>-0.4755262832998973</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>6/6</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>reportable</t>
+          <t>weak/noisy</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.1739525125801134</v>
+        <v>0.8930682788229291</v>
       </c>
       <c r="J15" t="n">
-        <v>0.03130369573642432</v>
+        <v>-0.3905288550556935</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5729904391587065</v>
+        <v>-0.5605237115441011</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7886989191386873</v>
+        <v>-0.6639176907567478</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4828525131273782</v>
+        <v>-0.6541230027504306</v>
       </c>
       <c r="N15" t="n">
-        <v>0.01535865970019359</v>
+        <v>0.5318973995431892</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>x_loans_gross</t>
+          <t>r_loans_assets</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3934,24 +3798,24 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.01721962998688673</v>
+        <v>0.02225233775851982</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1527592351245601</v>
+        <v>-0.446695774079799</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3960,26 +3824,26 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.2583954166090168</v>
+        <v>-0.07452291738210698</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>0.1527592351245601</v>
+        <v>-0.446695774079799</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.01890137895093107</v>
+        <v>-0.6006779333114977</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4847434414606122</v>
+        <v>-0.6860870638884407</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2235916619418466</v>
+        <v>0.4720556634755861</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>c_eqratio</t>
+          <t>inc_nii</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3988,19 +3852,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01675021584638044</v>
+        <v>0.02076308223689444</v>
       </c>
       <c r="D17" t="n">
-        <v>0.05282997114440009</v>
+        <v>0.5862177232459602</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4010,32 +3874,30 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>weak/noisy</t>
+          <t>reportable</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>-0.9442227256629292</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.6743117087762643</v>
-      </c>
+        <v>0.7508864957969494</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
-        <v>-0.1443095191281283</v>
+        <v>0.7093205299069919</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2671898290856319</v>
+        <v>0.4525689373676287</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2267675931589018</v>
+        <v>0.5862177232459602</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1211076508701016</v>
+        <v>0.3983364943697773</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>c_leverage</t>
+          <t>x_loans_gross</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4044,10 +3906,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01628334930962503</v>
+        <v>0.01872217025174462</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02090598614255212</v>
+        <v>-0.003296971762553974</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -4056,12 +3918,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -4070,28 +3932,26 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8554233531278415</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-0.01372941228540354</v>
-      </c>
+        <v>-0.5370711189330681</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>0.05554138457050777</v>
+        <v>0.04782698083351399</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3125672931641892</v>
+        <v>-0.38397506280868</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4699844374802075</v>
+        <v>-0.003296971762553974</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1245702620095101</v>
+        <v>0.0542248139192147</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>inc_nii</t>
+          <t>c_leverage</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4100,19 +3960,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0158586996350084</v>
+        <v>0.01827039650121052</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2446780438675702</v>
+        <v>0.2642505942521809</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4126,26 +3986,28 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7957428921585367</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
+        <v>-0.2009841009518949</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.04690491810753226</v>
+      </c>
       <c r="K19" t="n">
-        <v>0.4629312423976412</v>
+        <v>0.524596841711759</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2042913840283628</v>
+        <v>0.4931559790054853</v>
       </c>
       <c r="M19" t="n">
-        <v>0.07114333173461385</v>
+        <v>0.5966992048025511</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2446780438675702</v>
+        <v>0.03534520949887647</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>l_loans</t>
+          <t>x_ib_liab</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4154,14 +4016,14 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01579385868721337</v>
+        <v>0.01519316970475915</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2102211965039827</v>
+        <v>0.07450545037669355</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4180,28 +4042,28 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>-0.9216271484216884</v>
+        <v>-0.7790253571945079</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3691480340409087</v>
+        <v>-0.1540494970615119</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1271015883484623</v>
+        <v>0.5923561899961519</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6160627695018456</v>
+        <v>0.2447489555331812</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2933408046595032</v>
+        <v>0.2685031265750927</v>
       </c>
       <c r="N20" t="n">
-        <v>0.06074357636202452</v>
+        <v>-0.09573805477979411</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>inc_op</t>
+          <t>p_roa</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4210,24 +4072,24 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.014775861726635</v>
+        <v>0.01271756106188049</v>
       </c>
       <c r="D21" t="n">
-        <v>0.03879948696708894</v>
+        <v>-0.3632657715180529</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -4236,28 +4098,26 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>-0.7854007029733936</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.0956584239277749</v>
-      </c>
+        <v>-0.3632657715180529</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>0.6035777785626077</v>
+        <v>-0.9054324855699242</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3435087042773529</v>
+        <v>-0.4911600669362184</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1077717961005886</v>
+        <v>0.05361843863689399</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.01805944999359701</v>
+        <v>-0.338306599094662</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>x_dep</t>
+          <t>inc_op</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4266,10 +4126,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01394502921070186</v>
+        <v>0.01217030754986836</v>
       </c>
       <c r="D22" t="n">
-        <v>0.02092406826779631</v>
+        <v>0.2177003552882594</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4278,7 +4138,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4292,28 +4152,28 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.01908724499681764</v>
+        <v>-0.08645472651066857</v>
       </c>
       <c r="J22" t="n">
-        <v>0.01078215976994487</v>
+        <v>0.1023878304002853</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1969284645667818</v>
+        <v>0.6246268033554656</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02276089153877498</v>
+        <v>0.4876494695974377</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1156350731373365</v>
+        <v>0.3330128801762335</v>
       </c>
       <c r="N22" t="n">
-        <v>0.316506137619509</v>
+        <v>0.03372714997162787</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>x_ib_liab</t>
+          <t>c_eqratio</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4322,10 +4182,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.009152551474894551</v>
+        <v>0.01149137296833929</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.04751412914801201</v>
+        <v>-0.3494323689948215</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -4334,7 +4194,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4348,28 +4208,26 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>-0.04283346816640132</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-0.4990597395874152</v>
-      </c>
+        <v>-0.984636237450155</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
-        <v>0.07701146774078677</v>
+        <v>-0.6949521911737985</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5045583851396825</v>
+        <v>-0.0289160017157658</v>
       </c>
       <c r="M23" t="n">
-        <v>0.191187786639902</v>
+        <v>0.1156368219563309</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.05219479012962269</v>
+        <v>-0.3494323689948215</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>r_loans_assets</t>
+          <t>r_cti</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4378,24 +4236,24 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.008553948843064438</v>
+        <v>0.01042439229210962</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.07561025955867963</v>
+        <v>0.173141038908085</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>3/6</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>lowers risk</t>
+          <t>raises risk</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4404,28 +4262,28 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>-0.288878793842746</v>
+        <v>0.1838747198920969</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5069463220709832</v>
+        <v>-0.1238804682961273</v>
       </c>
       <c r="K24" t="n">
-        <v>0.08026007973424193</v>
+        <v>0.4855239043016484</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1815027688649611</v>
+        <v>0.1624073579240732</v>
       </c>
       <c r="M24" t="n">
-        <v>0.03028224974760179</v>
+        <v>0.05512685770161707</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2453835145277737</v>
+        <v>0.4406981440679242</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>r_dep_liab</t>
+          <t>x_dep</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4434,24 +4292,24 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.007007032705532137</v>
+        <v>0.007058606948741776</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.140599762983867</v>
+        <v>0.1563249500142058</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>lowers risk</t>
+          <t>raises risk</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4460,20 +4318,20 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>-0.3607412825128094</v>
+        <v>0.1185518591424677</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
-        <v>-0.140599762983867</v>
+        <v>0.1563249500142058</v>
       </c>
       <c r="L25" t="n">
-        <v>0.325176830166655</v>
+        <v>0.5689605116545343</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1267605301309362</v>
+        <v>0.1360213403922215</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.28857799339305</v>
+        <v>0.3119083295105621</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/results_15_11a.xlsx
+++ b/outputs/tables/results_15_11a.xlsx
@@ -466,22 +466,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.897</v>
+        <v>0.864</v>
       </c>
       <c r="C2" t="n">
-        <v>0.79</v>
+        <v>0.755</v>
       </c>
       <c r="D2" t="n">
-        <v>0.74</v>
+        <v>0.722</v>
       </c>
       <c r="E2" t="n">
-        <v>0.699</v>
+        <v>0.679</v>
       </c>
       <c r="F2" t="n">
         <v>0.739</v>
       </c>
       <c r="G2" t="n">
-        <v>0.665</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="3">
@@ -491,22 +491,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.613</v>
+        <v>0.653</v>
       </c>
       <c r="C3" t="n">
-        <v>0.376</v>
+        <v>0.426</v>
       </c>
       <c r="D3" t="n">
-        <v>0.54</v>
+        <v>0.534</v>
       </c>
       <c r="E3" t="n">
-        <v>0.38</v>
+        <v>0.358</v>
       </c>
       <c r="F3" t="n">
-        <v>0.53</v>
+        <v>0.664</v>
       </c>
       <c r="G3" t="n">
-        <v>0.361</v>
+        <v>0.417</v>
       </c>
     </row>
     <row r="4">
@@ -516,22 +516,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.745</v>
+        <v>0.759</v>
       </c>
       <c r="C4" t="n">
-        <v>0.579</v>
+        <v>0.588</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.672</v>
       </c>
       <c r="E4" t="n">
-        <v>0.605</v>
+        <v>0.621</v>
       </c>
       <c r="F4" t="n">
-        <v>0.646</v>
+        <v>0.681</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="5">
@@ -541,22 +541,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.748</v>
+        <v>0.746</v>
       </c>
       <c r="C5" t="n">
-        <v>0.587</v>
+        <v>0.569</v>
       </c>
       <c r="D5" t="n">
-        <v>0.708</v>
+        <v>0.647</v>
       </c>
       <c r="E5" t="n">
-        <v>0.606</v>
+        <v>0.537</v>
       </c>
       <c r="F5" t="n">
-        <v>0.677</v>
+        <v>0.648</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.508</v>
       </c>
     </row>
     <row r="6">
@@ -566,22 +566,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.747</v>
+        <v>0.745</v>
       </c>
       <c r="C6" t="n">
-        <v>0.573</v>
+        <v>0.57</v>
       </c>
       <c r="D6" t="n">
-        <v>0.657</v>
+        <v>0.703</v>
       </c>
       <c r="E6" t="n">
-        <v>0.552</v>
+        <v>0.613</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.583</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="7">
@@ -591,22 +591,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.744</v>
+        <v>0.626</v>
       </c>
       <c r="C7" t="n">
-        <v>0.541</v>
+        <v>0.428</v>
       </c>
       <c r="D7" t="n">
-        <v>0.582</v>
+        <v>0.668</v>
       </c>
       <c r="E7" t="n">
-        <v>0.503</v>
+        <v>0.608</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="G7" t="n">
-        <v>0.471</v>
+        <v>0.494</v>
       </c>
     </row>
   </sheetData>
@@ -667,17 +667,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.126</v>
+        <v>0.008</v>
       </c>
       <c r="D2" t="n">
-        <v>0.13</v>
+        <v>0.532</v>
       </c>
       <c r="E2" t="n">
-        <v>0.127</v>
+        <v>0.112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.052</t>
         </is>
       </c>
     </row>
@@ -693,17 +693,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.212</v>
+        <v>0.228</v>
       </c>
       <c r="D3" t="n">
-        <v>0.521</v>
+        <v>0.595</v>
       </c>
       <c r="E3" t="n">
-        <v>0.274</v>
+        <v>0.302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.037</t>
         </is>
       </c>
     </row>
@@ -719,17 +719,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.17</v>
+        <v>0.128</v>
       </c>
       <c r="D4" t="n">
-        <v>0.385</v>
+        <v>0.46</v>
       </c>
       <c r="E4" t="n">
-        <v>0.213</v>
+        <v>0.194</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.033</t>
         </is>
       </c>
     </row>
@@ -745,17 +745,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.189</v>
+        <v>0.092</v>
       </c>
       <c r="D5" t="n">
-        <v>0.394</v>
+        <v>0.64</v>
       </c>
       <c r="E5" t="n">
-        <v>0.23</v>
+        <v>0.202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.021</t>
+          <t>-0.055</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.181</v>
+        <v>0.141</v>
       </c>
       <c r="D6" t="n">
-        <v>0.408</v>
+        <v>0.487</v>
       </c>
       <c r="E6" t="n">
-        <v>0.227</v>
+        <v>0.21</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.023</t>
+          <t>-0.035</t>
         </is>
       </c>
     </row>
@@ -797,17 +797,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.19</v>
+        <v>0.191</v>
       </c>
       <c r="D7" t="n">
-        <v>0.434</v>
+        <v>0.663</v>
       </c>
       <c r="E7" t="n">
-        <v>0.239</v>
+        <v>0.285</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.025</t>
+          <t>-0.047</t>
         </is>
       </c>
     </row>
@@ -823,17 +823,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.111</v>
+        <v>0.064</v>
       </c>
       <c r="D8" t="n">
-        <v>0.315</v>
+        <v>0.777</v>
       </c>
       <c r="E8" t="n">
-        <v>0.152</v>
+        <v>0.207</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.072</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.387</v>
+        <v>0.276</v>
       </c>
       <c r="D9" t="n">
-        <v>0.399</v>
+        <v>0.712</v>
       </c>
       <c r="E9" t="n">
-        <v>0.389</v>
+        <v>0.363</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.043</t>
         </is>
       </c>
     </row>
@@ -875,17 +875,17 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.241</v>
       </c>
       <c r="D10" t="n">
-        <v>0.466</v>
+        <v>0.518</v>
       </c>
       <c r="E10" t="n">
-        <v>0.162</v>
+        <v>0.297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.038</t>
+          <t>-0.028</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.195</v>
+        <v>0.272</v>
       </c>
       <c r="D11" t="n">
-        <v>0.211</v>
+        <v>0.642</v>
       </c>
       <c r="E11" t="n">
-        <v>0.199</v>
+        <v>0.346</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>-0.037</t>
         </is>
       </c>
     </row>
@@ -927,17 +927,17 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.144</v>
+        <v>0.241</v>
       </c>
       <c r="D12" t="n">
-        <v>0.432</v>
+        <v>0.434</v>
       </c>
       <c r="E12" t="n">
-        <v>0.202</v>
+        <v>0.28</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.029</t>
+          <t>-0.019</t>
         </is>
       </c>
     </row>
@@ -953,17 +953,17 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1</v>
+        <v>0.215</v>
       </c>
       <c r="D13" t="n">
-        <v>0.417</v>
+        <v>0.63</v>
       </c>
       <c r="E13" t="n">
-        <v>0.163</v>
+        <v>0.298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.041</t>
         </is>
       </c>
     </row>
@@ -979,17 +979,17 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.098</v>
+        <v>0.037</v>
       </c>
       <c r="D14" t="n">
-        <v>0.354</v>
+        <v>0.8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.149</v>
+        <v>0.189</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.026</t>
+          <t>-0.076</t>
         </is>
       </c>
     </row>
@@ -1005,17 +1005,17 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.42</v>
+        <v>0.023</v>
       </c>
       <c r="D15" t="n">
-        <v>0.386</v>
+        <v>0.763</v>
       </c>
       <c r="E15" t="n">
-        <v>0.413</v>
+        <v>0.171</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.003</t>
+          <t>-0.074</t>
         </is>
       </c>
     </row>
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.125</v>
+        <v>0.2</v>
       </c>
       <c r="D16" t="n">
-        <v>0.442</v>
+        <v>0.517</v>
       </c>
       <c r="E16" t="n">
-        <v>0.188</v>
+        <v>0.263</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1057,17 +1057,17 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.282</v>
+        <v>0.25</v>
       </c>
       <c r="D17" t="n">
-        <v>0.183</v>
+        <v>0.657</v>
       </c>
       <c r="E17" t="n">
-        <v>0.262</v>
+        <v>0.331</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.040</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.182</v>
+        <v>0.215</v>
       </c>
       <c r="D18" t="n">
-        <v>0.369</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.22</v>
+        <v>0.285</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.019</t>
+          <t>-0.035</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1109,17 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.165</v>
+        <v>0.068</v>
       </c>
       <c r="D19" t="n">
-        <v>0.477</v>
+        <v>0.778</v>
       </c>
       <c r="E19" t="n">
-        <v>0.227</v>
+        <v>0.21</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.071</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1150,12 +1150,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Brier Score</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Best Threshold</t>
+          <t>Alarm cut-off (mean over test years)</t>
         </is>
       </c>
     </row>
@@ -1171,10 +1166,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.657</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="3">
@@ -1189,10 +1181,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.473</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="4">
@@ -1207,10 +1196,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.437</v>
+        <v>0.404</v>
       </c>
     </row>
     <row r="5">
@@ -1225,10 +1211,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.436</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="6">
@@ -1243,10 +1226,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.467</v>
+        <v>0.332</v>
       </c>
     </row>
     <row r="7">
@@ -1261,10 +1241,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.223</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.466</v>
+        <v>0.407</v>
       </c>
     </row>
     <row r="8">
@@ -1279,10 +1256,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.475</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="9">
@@ -1297,10 +1271,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.379</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="10">
@@ -1315,10 +1286,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.339</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="11">
@@ -1333,10 +1301,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.488</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="12">
@@ -1351,10 +1316,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.349</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.293</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="13">
@@ -1369,10 +1331,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1387,10 +1346,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.48</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="15">
@@ -1405,10 +1361,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.667</v>
+        <v>0.179</v>
       </c>
     </row>
     <row r="16">
@@ -1423,10 +1376,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.267</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="17">
@@ -1441,10 +1391,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.535</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="18">
@@ -1459,10 +1406,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.264</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="19">
@@ -1477,10 +1421,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.404</v>
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +1435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1550,25 +1491,20 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>brier</t>
+          <t>best_threshold</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>best_threshold</t>
+          <t>loss_07</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>loss_07</t>
+          <t>loss_09</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
-        <is>
-          <t>loss_09</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
@@ -1586,43 +1522,40 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.53</v>
+        <v>0.664</v>
       </c>
       <c r="D2" t="n">
-        <v>0.451</v>
+        <v>0.505</v>
       </c>
       <c r="E2" t="n">
-        <v>0.58</v>
+        <v>0.977</v>
       </c>
       <c r="F2" t="n">
-        <v>0.539</v>
+        <v>0.354</v>
       </c>
       <c r="G2" t="n">
-        <v>0.42</v>
+        <v>0.023</v>
       </c>
       <c r="H2" t="n">
-        <v>0.386</v>
+        <v>0.763</v>
       </c>
       <c r="I2" t="n">
-        <v>0.413</v>
+        <v>0.171</v>
       </c>
       <c r="J2" t="n">
-        <v>0.361</v>
+        <v>0.417</v>
       </c>
       <c r="K2" t="n">
-        <v>0.444</v>
+        <v>0.179</v>
       </c>
       <c r="L2" t="n">
-        <v>0.667</v>
+        <v>0.245</v>
       </c>
       <c r="M2" t="n">
-        <v>0.41</v>
+        <v>0.097</v>
       </c>
       <c r="N2" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.6</v>
+        <v>0.432</v>
       </c>
     </row>
     <row r="3">
@@ -1637,43 +1570,40 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.54</v>
+        <v>0.534</v>
       </c>
       <c r="D3" t="n">
-        <v>0.471</v>
+        <v>0.35</v>
       </c>
       <c r="E3" t="n">
-        <v>0.613</v>
+        <v>0.724</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.28</v>
       </c>
       <c r="G3" t="n">
-        <v>0.387</v>
+        <v>0.276</v>
       </c>
       <c r="H3" t="n">
-        <v>0.399</v>
+        <v>0.712</v>
       </c>
       <c r="I3" t="n">
-        <v>0.389</v>
+        <v>0.363</v>
       </c>
       <c r="J3" t="n">
-        <v>0.38</v>
+        <v>0.358</v>
       </c>
       <c r="K3" t="n">
-        <v>0.443</v>
+        <v>0.333</v>
       </c>
       <c r="L3" t="n">
-        <v>0.379</v>
+        <v>0.407</v>
       </c>
       <c r="M3" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="N3" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.602</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="4">
@@ -1688,43 +1618,40 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.613</v>
+        <v>0.653</v>
       </c>
       <c r="D4" t="n">
-        <v>0.501</v>
+        <v>0.458</v>
       </c>
       <c r="E4" t="n">
-        <v>0.788</v>
+        <v>0.772</v>
       </c>
       <c r="F4" t="n">
-        <v>0.382</v>
+        <v>0.341</v>
       </c>
       <c r="G4" t="n">
-        <v>0.212</v>
+        <v>0.228</v>
       </c>
       <c r="H4" t="n">
-        <v>0.521</v>
+        <v>0.595</v>
       </c>
       <c r="I4" t="n">
-        <v>0.274</v>
+        <v>0.302</v>
       </c>
       <c r="J4" t="n">
-        <v>0.376</v>
+        <v>0.426</v>
       </c>
       <c r="K4" t="n">
-        <v>0.289</v>
+        <v>0.403</v>
       </c>
       <c r="L4" t="n">
-        <v>0.473</v>
+        <v>0.338</v>
       </c>
       <c r="M4" t="n">
-        <v>0.305</v>
+        <v>0.265</v>
       </c>
       <c r="N4" t="n">
-        <v>0.243</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.502</v>
       </c>
     </row>
     <row r="5">
@@ -1739,43 +1666,40 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.65</v>
+        <v>0.464</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.785</v>
       </c>
       <c r="F5" t="n">
-        <v>0.634</v>
+        <v>0.396</v>
       </c>
       <c r="G5" t="n">
-        <v>0.182</v>
+        <v>0.215</v>
       </c>
       <c r="H5" t="n">
-        <v>0.369</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.22</v>
+        <v>0.285</v>
       </c>
       <c r="J5" t="n">
-        <v>0.583</v>
+        <v>0.504</v>
       </c>
       <c r="K5" t="n">
-        <v>0.293</v>
+        <v>0.027</v>
       </c>
       <c r="L5" t="n">
-        <v>0.264</v>
+        <v>0.32</v>
       </c>
       <c r="M5" t="n">
-        <v>0.238</v>
+        <v>0.25</v>
       </c>
       <c r="N5" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.661</v>
+        <v>0.524</v>
       </c>
     </row>
     <row r="6">
@@ -1790,43 +1714,40 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.657</v>
+        <v>0.703</v>
       </c>
       <c r="D6" t="n">
-        <v>0.586</v>
+        <v>0.529</v>
       </c>
       <c r="E6" t="n">
-        <v>0.856</v>
+        <v>0.759</v>
       </c>
       <c r="F6" t="n">
-        <v>0.503</v>
+        <v>0.497</v>
       </c>
       <c r="G6" t="n">
-        <v>0.144</v>
+        <v>0.241</v>
       </c>
       <c r="H6" t="n">
-        <v>0.432</v>
+        <v>0.434</v>
       </c>
       <c r="I6" t="n">
-        <v>0.202</v>
+        <v>0.28</v>
       </c>
       <c r="J6" t="n">
-        <v>0.552</v>
+        <v>0.613</v>
       </c>
       <c r="K6" t="n">
-        <v>0.349</v>
+        <v>0.113</v>
       </c>
       <c r="L6" t="n">
-        <v>0.293</v>
+        <v>0.299</v>
       </c>
       <c r="M6" t="n">
-        <v>0.23</v>
+        <v>0.261</v>
       </c>
       <c r="N6" t="n">
-        <v>0.173</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.644</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="7">
@@ -1841,43 +1762,40 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.747</v>
+        <v>0.745</v>
       </c>
       <c r="D7" t="n">
-        <v>0.604</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.819</v>
+        <v>0.859</v>
       </c>
       <c r="F7" t="n">
-        <v>0.536</v>
+        <v>0.441</v>
       </c>
       <c r="G7" t="n">
-        <v>0.181</v>
+        <v>0.141</v>
       </c>
       <c r="H7" t="n">
-        <v>0.408</v>
+        <v>0.487</v>
       </c>
       <c r="I7" t="n">
-        <v>0.227</v>
+        <v>0.21</v>
       </c>
       <c r="J7" t="n">
-        <v>0.573</v>
+        <v>0.57</v>
       </c>
       <c r="K7" t="n">
-        <v>0.238</v>
+        <v>0.332</v>
       </c>
       <c r="L7" t="n">
-        <v>0.467</v>
+        <v>0.244</v>
       </c>
       <c r="M7" t="n">
-        <v>0.249</v>
+        <v>0.175</v>
       </c>
       <c r="N7" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.654</v>
+        <v>0.603</v>
       </c>
     </row>
     <row r="8">
@@ -1895,40 +1813,37 @@
         <v>0.739</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.467</v>
       </c>
       <c r="E8" t="n">
-        <v>0.902</v>
+        <v>0.963</v>
       </c>
       <c r="F8" t="n">
-        <v>0.609</v>
+        <v>0.311</v>
       </c>
       <c r="G8" t="n">
-        <v>0.098</v>
+        <v>0.037</v>
       </c>
       <c r="H8" t="n">
-        <v>0.354</v>
+        <v>0.8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.149</v>
+        <v>0.189</v>
       </c>
       <c r="J8" t="n">
-        <v>0.665</v>
+        <v>0.678</v>
       </c>
       <c r="K8" t="n">
-        <v>0.357</v>
+        <v>0.157</v>
       </c>
       <c r="L8" t="n">
-        <v>0.48</v>
+        <v>0.266</v>
       </c>
       <c r="M8" t="n">
-        <v>0.175</v>
+        <v>0.113</v>
       </c>
       <c r="N8" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.715</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="9">
@@ -1943,43 +1858,40 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.74</v>
+        <v>0.722</v>
       </c>
       <c r="D9" t="n">
-        <v>0.718</v>
+        <v>0.468</v>
       </c>
       <c r="E9" t="n">
-        <v>0.889</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="F9" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="J9" t="n">
         <v>0.679</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.699</v>
-      </c>
       <c r="K9" t="n">
-        <v>0.353</v>
+        <v>0.16</v>
       </c>
       <c r="L9" t="n">
-        <v>0.475</v>
+        <v>0.278</v>
       </c>
       <c r="M9" t="n">
-        <v>0.172</v>
+        <v>0.135</v>
       </c>
       <c r="N9" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.74</v>
+        <v>0.412</v>
       </c>
     </row>
     <row r="10">
@@ -1994,43 +1906,40 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.897</v>
+        <v>0.864</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.631</v>
       </c>
       <c r="E10" t="n">
-        <v>0.874</v>
+        <v>0.992</v>
       </c>
       <c r="F10" t="n">
-        <v>0.763</v>
+        <v>0.507</v>
       </c>
       <c r="G10" t="n">
-        <v>0.126</v>
+        <v>0.008</v>
       </c>
       <c r="H10" t="n">
-        <v>0.13</v>
+        <v>0.532</v>
       </c>
       <c r="I10" t="n">
-        <v>0.127</v>
+        <v>0.112</v>
       </c>
       <c r="J10" t="n">
-        <v>0.79</v>
+        <v>0.755</v>
       </c>
       <c r="K10" t="n">
-        <v>0.186</v>
+        <v>0.286</v>
       </c>
       <c r="L10" t="n">
-        <v>0.657</v>
+        <v>0.165</v>
       </c>
       <c r="M10" t="n">
-        <v>0.127</v>
+        <v>0.06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.871</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="11">
@@ -2045,43 +1954,40 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="D11" t="n">
-        <v>0.58</v>
+        <v>0.463</v>
       </c>
       <c r="E11" t="n">
-        <v>0.835</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.492</v>
+        <v>0.314</v>
       </c>
       <c r="G11" t="n">
-        <v>0.165</v>
+        <v>0.068</v>
       </c>
       <c r="H11" t="n">
-        <v>0.477</v>
+        <v>0.778</v>
       </c>
       <c r="I11" t="n">
-        <v>0.227</v>
+        <v>0.21</v>
       </c>
       <c r="J11" t="n">
-        <v>0.471</v>
+        <v>0.494</v>
       </c>
       <c r="K11" t="n">
-        <v>0.353</v>
+        <v>0.16</v>
       </c>
       <c r="L11" t="n">
-        <v>0.404</v>
+        <v>0.281</v>
       </c>
       <c r="M11" t="n">
-        <v>0.258</v>
+        <v>0.139</v>
       </c>
       <c r="N11" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.609</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="12">
@@ -2096,43 +2002,40 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.582</v>
+        <v>0.668</v>
       </c>
       <c r="D12" t="n">
-        <v>0.644</v>
+        <v>0.464</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9</v>
+        <v>0.785</v>
       </c>
       <c r="F12" t="n">
-        <v>0.536</v>
+        <v>0.43</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1</v>
+        <v>0.215</v>
       </c>
       <c r="H12" t="n">
-        <v>0.417</v>
+        <v>0.63</v>
       </c>
       <c r="I12" t="n">
-        <v>0.163</v>
+        <v>0.298</v>
       </c>
       <c r="J12" t="n">
-        <v>0.503</v>
+        <v>0.608</v>
       </c>
       <c r="K12" t="n">
-        <v>0.352</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.315</v>
+        <v>0.34</v>
       </c>
       <c r="M12" t="n">
-        <v>0.195</v>
+        <v>0.257</v>
       </c>
       <c r="N12" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.67</v>
+        <v>0.477</v>
       </c>
     </row>
     <row r="13">
@@ -2147,43 +2050,40 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.744</v>
+        <v>0.626</v>
       </c>
       <c r="D13" t="n">
-        <v>0.57</v>
+        <v>0.442</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.469</v>
+        <v>0.317</v>
       </c>
       <c r="G13" t="n">
-        <v>0.19</v>
+        <v>0.191</v>
       </c>
       <c r="H13" t="n">
-        <v>0.434</v>
+        <v>0.663</v>
       </c>
       <c r="I13" t="n">
-        <v>0.239</v>
+        <v>0.285</v>
       </c>
       <c r="J13" t="n">
-        <v>0.541</v>
+        <v>0.428</v>
       </c>
       <c r="K13" t="n">
-        <v>0.223</v>
+        <v>0.407</v>
       </c>
       <c r="L13" t="n">
-        <v>0.466</v>
+        <v>0.332</v>
       </c>
       <c r="M13" t="n">
-        <v>0.263</v>
+        <v>0.238</v>
       </c>
       <c r="N13" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.633</v>
+        <v>0.462</v>
       </c>
     </row>
     <row r="14">
@@ -2198,43 +2098,40 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.646</v>
+        <v>0.681</v>
       </c>
       <c r="D14" t="n">
-        <v>0.625</v>
+        <v>0.514</v>
       </c>
       <c r="E14" t="n">
-        <v>0.875</v>
+        <v>0.8</v>
       </c>
       <c r="F14" t="n">
-        <v>0.533</v>
+        <v>0.488</v>
       </c>
       <c r="G14" t="n">
-        <v>0.125</v>
+        <v>0.2</v>
       </c>
       <c r="H14" t="n">
-        <v>0.442</v>
+        <v>0.517</v>
       </c>
       <c r="I14" t="n">
-        <v>0.188</v>
+        <v>0.263</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.616</v>
       </c>
       <c r="K14" t="n">
-        <v>0.209</v>
+        <v>0.222</v>
       </c>
       <c r="L14" t="n">
-        <v>0.267</v>
+        <v>0.295</v>
       </c>
       <c r="M14" t="n">
-        <v>0.22</v>
+        <v>0.232</v>
       </c>
       <c r="N14" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.645</v>
+        <v>0.5639999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -2249,43 +2146,40 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.672</v>
       </c>
       <c r="D15" t="n">
-        <v>0.64</v>
+        <v>0.474</v>
       </c>
       <c r="E15" t="n">
-        <v>0.914</v>
+        <v>0.759</v>
       </c>
       <c r="F15" t="n">
-        <v>0.577</v>
+        <v>0.411</v>
       </c>
       <c r="G15" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.241</v>
       </c>
       <c r="H15" t="n">
-        <v>0.466</v>
+        <v>0.518</v>
       </c>
       <c r="I15" t="n">
-        <v>0.162</v>
+        <v>0.297</v>
       </c>
       <c r="J15" t="n">
-        <v>0.605</v>
+        <v>0.621</v>
       </c>
       <c r="K15" t="n">
-        <v>0.204</v>
+        <v>0.229</v>
       </c>
       <c r="L15" t="n">
-        <v>0.339</v>
+        <v>0.324</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2</v>
+        <v>0.269</v>
       </c>
       <c r="N15" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.639</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="16">
@@ -2300,43 +2194,40 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.745</v>
+        <v>0.759</v>
       </c>
       <c r="D16" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="N16" t="n">
         <v>0.626</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.548</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.213</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.437</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.234</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.191</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.675</v>
       </c>
     </row>
     <row r="17">
@@ -2351,43 +2242,40 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.677</v>
+        <v>0.648</v>
       </c>
       <c r="D17" t="n">
-        <v>0.67</v>
+        <v>0.401</v>
       </c>
       <c r="E17" t="n">
-        <v>0.718</v>
+        <v>0.75</v>
       </c>
       <c r="F17" t="n">
-        <v>0.713</v>
+        <v>0.378</v>
       </c>
       <c r="G17" t="n">
-        <v>0.282</v>
+        <v>0.25</v>
       </c>
       <c r="H17" t="n">
-        <v>0.183</v>
+        <v>0.657</v>
       </c>
       <c r="I17" t="n">
-        <v>0.262</v>
+        <v>0.331</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.508</v>
       </c>
       <c r="K17" t="n">
-        <v>0.25</v>
+        <v>0.204</v>
       </c>
       <c r="L17" t="n">
-        <v>0.535</v>
+        <v>0.372</v>
       </c>
       <c r="M17" t="n">
-        <v>0.253</v>
+        <v>0.291</v>
       </c>
       <c r="N17" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.791</v>
+        <v>0.447</v>
       </c>
     </row>
     <row r="18">
@@ -2402,43 +2290,40 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.708</v>
+        <v>0.647</v>
       </c>
       <c r="D18" t="n">
-        <v>0.709</v>
+        <v>0.383</v>
       </c>
       <c r="E18" t="n">
-        <v>0.805</v>
+        <v>0.728</v>
       </c>
       <c r="F18" t="n">
-        <v>0.696</v>
+        <v>0.44</v>
       </c>
       <c r="G18" t="n">
-        <v>0.195</v>
+        <v>0.272</v>
       </c>
       <c r="H18" t="n">
-        <v>0.211</v>
+        <v>0.642</v>
       </c>
       <c r="I18" t="n">
-        <v>0.199</v>
+        <v>0.346</v>
       </c>
       <c r="J18" t="n">
-        <v>0.606</v>
+        <v>0.537</v>
       </c>
       <c r="K18" t="n">
-        <v>0.25</v>
+        <v>0.191</v>
       </c>
       <c r="L18" t="n">
-        <v>0.488</v>
+        <v>0.383</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2</v>
+        <v>0.309</v>
       </c>
       <c r="N18" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.794</v>
+        <v>0.452</v>
       </c>
     </row>
     <row r="19">
@@ -2453,43 +2338,40 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.748</v>
+        <v>0.746</v>
       </c>
       <c r="D19" t="n">
-        <v>0.604</v>
+        <v>0.525</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.908</v>
       </c>
       <c r="F19" t="n">
-        <v>0.527</v>
+        <v>0.401</v>
       </c>
       <c r="G19" t="n">
-        <v>0.189</v>
+        <v>0.092</v>
       </c>
       <c r="H19" t="n">
-        <v>0.394</v>
+        <v>0.64</v>
       </c>
       <c r="I19" t="n">
-        <v>0.23</v>
+        <v>0.202</v>
       </c>
       <c r="J19" t="n">
-        <v>0.587</v>
+        <v>0.569</v>
       </c>
       <c r="K19" t="n">
-        <v>0.233</v>
+        <v>0.325</v>
       </c>
       <c r="L19" t="n">
-        <v>0.436</v>
+        <v>0.257</v>
       </c>
       <c r="M19" t="n">
-        <v>0.25</v>
+        <v>0.147</v>
       </c>
       <c r="N19" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.662</v>
+        <v>0.505</v>
       </c>
     </row>
   </sheetData>
@@ -2555,7 +2437,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.174</v>
+        <v>3.315</v>
       </c>
       <c r="D2" t="n">
         <v>0.667</v>
@@ -2568,6 +2450,11 @@
           <t>Decision Tree</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2581,10 +2468,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.957</v>
+        <v>-1.764</v>
       </c>
       <c r="D3" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>3</v>
@@ -2594,11 +2481,6 @@
           <t>LightGBM</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2612,10 +2494,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-1.108</v>
+        <v>1.216</v>
       </c>
       <c r="D4" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -2638,7 +2520,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.742</v>
+        <v>-2.355</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -2664,10 +2546,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-1.932</v>
+        <v>0.765</v>
       </c>
       <c r="D6" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -2690,10 +2572,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.706</v>
+        <v>0.324</v>
       </c>
       <c r="D7" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
@@ -2716,10 +2598,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-2.131</v>
+        <v>0.379</v>
       </c>
       <c r="D8" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
@@ -2742,10 +2624,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-1.107</v>
+        <v>-1.204</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -2768,10 +2650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-4.19</v>
+        <v>-2.864</v>
       </c>
       <c r="D10" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
@@ -2794,7 +2676,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-4.297</v>
+        <v>-1.07</v>
       </c>
       <c r="D11" t="n">
         <v>0.667</v>
@@ -2820,10 +2702,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-2.14</v>
+        <v>-0.968</v>
       </c>
       <c r="D12" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
@@ -2846,10 +2728,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-1.46</v>
+        <v>-2.175</v>
       </c>
       <c r="D13" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>3</v>
@@ -2937,16 +2819,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.174</v>
+        <v>3.315</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.131</v>
+        <v>0.379</v>
       </c>
       <c r="D4" t="n">
         <v>0.667</v>
       </c>
       <c r="E4" t="n">
-        <v>0.667</v>
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -2956,21 +2843,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.957</v>
+        <v>-1.764</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.107</v>
+        <v>-1.204</v>
       </c>
       <c r="D5" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2980,16 +2862,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.108</v>
+        <v>1.216</v>
       </c>
       <c r="C6" t="n">
-        <v>-4.19</v>
+        <v>-2.864</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.333</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.667</v>
       </c>
     </row>
     <row r="7">
@@ -2999,10 +2881,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.742</v>
+        <v>-2.355</v>
       </c>
       <c r="C7" t="n">
-        <v>-4.297</v>
+        <v>-1.07</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -3018,16 +2900,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.932</v>
+        <v>0.765</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.14</v>
+        <v>-0.968</v>
       </c>
       <c r="D8" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="9">
@@ -3037,16 +2919,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.706</v>
+        <v>0.324</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.46</v>
+        <v>-2.175</v>
       </c>
       <c r="D9" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3152,10 +3034,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9265863122647752</v>
+        <v>0.9602812479234683</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.8501461146113416</v>
+        <v>-0.8755984404247799</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3178,22 +3060,22 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>-0.9560395534847204</v>
+        <v>-0.943717525843264</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.7614875654324363</v>
+        <v>-0.7669719265146999</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.8596650558447358</v>
+        <v>-0.9129553194017935</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.9207121452627373</v>
+        <v>-0.8796048136468574</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8406271733779473</v>
+        <v>-0.8132940504730691</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7654476686680941</v>
+        <v>-0.8715920672027022</v>
       </c>
     </row>
     <row r="3">
@@ -3208,10 +3090,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.6542367001081102</v>
+        <v>0.7328938382644471</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7863099168273141</v>
+        <v>0.8046500651275855</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3220,7 +3102,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3230,26 +3112,26 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>reportable</t>
+          <t>non-monotone</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.7602334581970298</v>
+        <v>0.6506265366197256</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6359875800366256</v>
+        <v>0.7915473520481222</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8290485760380926</v>
+        <v>0.8568306167885279</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8657536232434998</v>
+        <v>0.8177527782070488</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8024969368506468</v>
+        <v>0.8755817901372858</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7701228968039814</v>
+        <v>0.6544222169767808</v>
       </c>
     </row>
     <row r="4">
@@ -3264,14 +3146,14 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.5710484494305808</v>
+        <v>0.5685450174872665</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5505683435119144</v>
+        <v>-0.459259174026598</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3290,22 +3172,22 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>-0.3060631041203119</v>
+        <v>-0.3514986130714824</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.5910784730513579</v>
+        <v>0.02544574055289366</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5111258226201523</v>
+        <v>-0.4609703524648203</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5586845865036839</v>
+        <v>-0.4575479955883757</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5424521005201449</v>
+        <v>-0.5313922930166871</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5739820287820051</v>
+        <v>-0.64811671117268</v>
       </c>
     </row>
     <row r="5">
@@ -3320,19 +3202,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.3275418728407907</v>
+        <v>0.3736340265261528</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9029537103531189</v>
+        <v>0.8531536576846697</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3342,26 +3224,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>reportable</t>
+          <t>non-monotone</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.8850546727255526</v>
+        <v>0.8861810781371373</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5002986811705231</v>
+        <v>0.4933814531499772</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9214079847251373</v>
+        <v>0.8483161169047685</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9350347558674083</v>
+        <v>0.9111194506767308</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9208527479806852</v>
+        <v>0.7741138317423767</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8561962013528077</v>
+        <v>0.8579911984645709</v>
       </c>
     </row>
     <row r="6">
@@ -3376,14 +3258,14 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.2773734126547638</v>
+        <v>0.2711194681127142</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3493613287215372</v>
+        <v>0.3398796658540443</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3398,26 +3280,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>weak/noisy</t>
+          <t>non-monotone</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>-0.1032107381408622</v>
+        <v>0.2816895121901261</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4174638922038403</v>
+        <v>0.1626099008040462</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7363635532739682</v>
+        <v>0.7580462299880116</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2812587652392342</v>
+        <v>0.66805978050029</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7427053615415067</v>
+        <v>0.3980698195179626</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.241150567660822</v>
+        <v>-0.2581000162270767</v>
       </c>
     </row>
     <row r="7">
@@ -3432,10 +3314,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2561800350696424</v>
+        <v>0.2438617837240925</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4208330499318674</v>
+        <v>-0.4756552747250419</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3444,7 +3326,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3458,22 +3340,22 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>-0.7931592247819945</v>
+        <v>-0.802501170340802</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3967241847934448</v>
+        <v>-0.4205647811972332</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3895043791282821</v>
+        <v>-0.3855695605643771</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.44494191507029</v>
+        <v>-0.5307457682528506</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3531146271776288</v>
+        <v>-0.3139255792501173</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5208725287142381</v>
+        <v>-0.8253515158062468</v>
       </c>
     </row>
     <row r="8">
@@ -3488,24 +3370,24 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1193977124790572</v>
+        <v>0.1698299638687526</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04557599331390627</v>
+        <v>-0.03459127508660326</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3514,22 +3396,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>-0.09629930569732617</v>
+        <v>-0.2680652635089166</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2454631318451621</v>
+        <v>-0.003364451149075939</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09215629152405835</v>
+        <v>-0.06581809902413058</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2797573075974532</v>
+        <v>0.3761223969168672</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1125944690013834</v>
+        <v>0.3721416420854875</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.001004304896245808</v>
+        <v>-0.2809920050071849</v>
       </c>
     </row>
     <row r="9">
@@ -3544,10 +3426,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.1011193558996304</v>
+        <v>0.123172615486867</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5115169928661184</v>
+        <v>0.6517819493238338</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -3556,7 +3438,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3570,22 +3452,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9446948581645295</v>
+        <v>0.9080295048877592</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2055171304562143</v>
+        <v>0.3531858925148132</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7609499101432272</v>
+        <v>0.6973598171723989</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5563630746846909</v>
+        <v>0.6062040814752687</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4666709110475459</v>
+        <v>0.5398464226468118</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3471567092015995</v>
+        <v>0.8538729263724725</v>
       </c>
     </row>
     <row r="10">
@@ -3600,19 +3482,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.09082432606716123</v>
+        <v>0.09469789612660912</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4294555279147809</v>
+        <v>0.347241732067082</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3626,28 +3508,26 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>-0.3338476561245598</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.5715904730313753</v>
-      </c>
+        <v>-0.2291476560397598</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>0.546826040018039</v>
+        <v>0.347241732067082</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5229421000588953</v>
+        <v>0.5371423300140798</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3359689557706665</v>
+        <v>0.4723725852203932</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1353174598395</v>
+        <v>-0.2741623279549091</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>p_roe</t>
+          <t>p_nim</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3656,10 +3536,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.05473046835154706</v>
+        <v>0.0501994221484055</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4777226175957648</v>
+        <v>-0.6647437064713266</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -3682,26 +3562,26 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>-0.8829776051711064</v>
+        <v>-0.9682074675183311</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>-0.6966622873865808</v>
+        <v>-0.6647437064713266</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3846476250237861</v>
+        <v>-0.5288435454508726</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4777226175957648</v>
+        <v>-0.2049285313940291</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4393462907808177</v>
+        <v>-0.8605446518125274</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>p_nim</t>
+          <t>l_assets</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3710,10 +3590,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04293170879251015</v>
+        <v>0.0480364248226323</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4521540911098725</v>
+        <v>0.7377430388683519</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3722,42 +3602,40 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>lowers risk</t>
+          <t>raises risk</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>non-monotone</t>
+          <t>reportable</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>-0.9399936133719057</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-0.3529095816908794</v>
-      </c>
+        <v>0.9259278099639524</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>-0.7061009443174298</v>
+        <v>0.8910038411523976</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1391119653083442</v>
+        <v>0.1729491813469562</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1426358921537539</v>
+        <v>0.3523185580711675</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5513986005288657</v>
+        <v>0.7377430388683519</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>l_assets</t>
+          <t>l_loans</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3766,19 +3644,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02786723628180906</v>
+        <v>0.03819342155791924</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7212820164239462</v>
+        <v>0.1922082044722806</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3788,32 +3666,26 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>reportable</t>
+          <t>weak/noisy</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9593608852380473</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.2912548156217548</v>
-      </c>
+        <v>-0.6630958784655386</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>0.744583230804149</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.8334196791731932</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.6979808020437432</v>
-      </c>
+        <v>0.2205505755407129</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>0.305870586292858</v>
+        <v>0.1922082044722806</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>p_roa</t>
+          <t>p_roe</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3822,10 +3694,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02295011574974603</v>
+        <v>0.03561318366012897</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3467844784464797</v>
+        <v>-0.3964367663009709</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3834,7 +3706,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3848,28 +3720,26 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6056669098469238</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-0.2220149032530638</v>
-      </c>
+        <v>-0.8851158734747097</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>-0.8520520887291622</v>
+        <v>-0.8040645951157732</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4510167188506159</v>
+        <v>-0.3964367663009709</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4870885407404747</v>
+        <v>-0.000925900095163337</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2425522380423436</v>
+        <v>-0.3526008898781169</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>r_cti</t>
+          <t>r_dep_liab</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3878,54 +3748,52 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.01843497381777106</v>
+        <v>0.02158027769539448</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3284025128537458</v>
+        <v>-0.3746645565378905</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>reportable</t>
+          <t>weak/noisy</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.1739525125801134</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.03130369573642432</v>
-      </c>
+        <v>0.8946506029317803</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>0.5729904391587065</v>
+        <v>-0.3746645565378905</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7886989191386873</v>
+        <v>-0.6291223688782652</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4828525131273782</v>
+        <v>-0.4071066556755911</v>
       </c>
       <c r="N15" t="n">
-        <v>0.01535865970019359</v>
+        <v>0.2542515889202817</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>x_loans_gross</t>
+          <t>inc_nii</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3934,19 +3802,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.01721962998688673</v>
+        <v>0.02020957169428863</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1527592351245601</v>
+        <v>0.4028879456779108</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -3960,26 +3828,26 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.2583954166090168</v>
+        <v>0.7517994829501931</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>0.1527592351245601</v>
+        <v>0.516788529003918</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.01890137895093107</v>
+        <v>0.4028879456779108</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4847434414606122</v>
+        <v>0.3249867446518781</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2235916619418466</v>
+        <v>-0.3601582027400736</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>c_eqratio</t>
+          <t>r_loans_assets</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3988,24 +3856,24 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01675021584638044</v>
+        <v>0.01512156674603825</v>
       </c>
       <c r="D17" t="n">
-        <v>0.05282997114440009</v>
+        <v>-0.1670400509641582</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>3/6</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4014,28 +3882,28 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>-0.9442227256629292</v>
+        <v>-0.07456392640574791</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6743117087762643</v>
+        <v>0.01300348566805474</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1443095191281283</v>
+        <v>-0.2595161755225684</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2671898290856319</v>
+        <v>-0.5642315303272534</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2267675931589018</v>
+        <v>-0.6603438441271843</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1211076508701016</v>
+        <v>-0.07003527957207679</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>c_leverage</t>
+          <t>x_ib_liab</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4044,10 +3912,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01628334930962503</v>
+        <v>0.01364036906304114</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02090598614255212</v>
+        <v>0.046486286282199</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -4056,7 +3924,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4070,28 +3938,26 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8554233531278415</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-0.01372941228540354</v>
-      </c>
+        <v>-0.7806218106059069</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>0.05554138457050777</v>
+        <v>0.8237247314402312</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3125672931641892</v>
+        <v>0.6122961663654769</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4699844374802075</v>
+        <v>0.046486286282199</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1245702620095101</v>
+        <v>-0.3520636920140666</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>inc_nii</t>
+          <t>c_leverage</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4100,14 +3966,14 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0158586996350084</v>
+        <v>0.01358189853932435</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2446780438675702</v>
+        <v>0.6276226079790049</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4126,26 +3992,26 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7957428921585367</v>
+        <v>-0.2036307602359464</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
-        <v>0.4629312423976412</v>
+        <v>0.6276226079790049</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2042913840283628</v>
+        <v>0.6292567548435887</v>
       </c>
       <c r="M19" t="n">
-        <v>0.07114333173461385</v>
+        <v>0.6421480423385177</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2446780438675702</v>
+        <v>-0.2710277864138799</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>l_loans</t>
+          <t>x_loans_gross</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4154,24 +4020,24 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01579385868721337</v>
+        <v>0.01109360575488711</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2102211965039827</v>
+        <v>-0.3609690296214452</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -4180,28 +4046,26 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>-0.9216271484216884</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.3691480340409087</v>
-      </c>
+        <v>-0.5373775139802185</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>0.1271015883484623</v>
+        <v>0.1780334834549049</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6160627695018456</v>
+        <v>-0.4081805589619027</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2933408046595032</v>
+        <v>-0.3609690296214452</v>
       </c>
       <c r="N20" t="n">
-        <v>0.06074357636202452</v>
+        <v>0.4514727289885581</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>inc_op</t>
+          <t>p_roa</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4210,54 +4074,52 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.014775861726635</v>
+        <v>0.01044267546828872</v>
       </c>
       <c r="D21" t="n">
-        <v>0.03879948696708894</v>
+        <v>-0.5932622406243206</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>weak/noisy</t>
+          <t>reportable</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>-0.7854007029733936</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.0956584239277749</v>
-      </c>
+        <v>-0.3631022224445258</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>0.6035777785626077</v>
+        <v>-0.9110870284956921</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3435087042773529</v>
+        <v>-0.5932622406243206</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1077717961005886</v>
+        <v>-0.2784617564373758</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.01805944999359701</v>
+        <v>-0.6925456066794031</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>x_dep</t>
+          <t>c_eqratio</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4266,10 +4128,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01394502921070186</v>
+        <v>0.008357694598917543</v>
       </c>
       <c r="D22" t="n">
-        <v>0.02092406826779631</v>
+        <v>-0.6249783739133871</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4278,42 +4140,40 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>weak/noisy</t>
+          <t>non-monotone</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.01908724499681764</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.01078215976994487</v>
-      </c>
+        <v>-0.9844029845461443</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="n">
-        <v>0.1969284645667818</v>
+        <v>-0.6249783739133871</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02276089153877498</v>
+        <v>-0.2495734851852651</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1156350731373365</v>
+        <v>-0.4862738027719978</v>
       </c>
       <c r="N22" t="n">
-        <v>0.316506137619509</v>
+        <v>-0.6498163545289829</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>x_ib_liab</t>
+          <t>inc_op</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4322,24 +4182,24 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.009152551474894551</v>
+        <v>0.008357480354964041</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.04751412914801201</v>
+        <v>0.1820436864105162</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>lowers risk</t>
+          <t>raises risk</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -4348,28 +4208,26 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>-0.04283346816640132</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-0.4990597395874152</v>
-      </c>
+        <v>-0.08725357667578171</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
-        <v>0.07701146774078677</v>
+        <v>0.4870153196986808</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5045583851396825</v>
+        <v>0.1820436864105162</v>
       </c>
       <c r="M23" t="n">
-        <v>0.191187786639902</v>
+        <v>0.4144096565133321</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.05219479012962269</v>
+        <v>-0.1314720954779827</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>r_loans_assets</t>
+          <t>r_cti</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4378,19 +4236,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.008553948843064438</v>
+        <v>0.005734092854713564</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.07561025955867963</v>
+        <v>-0.05586179517375123</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4404,28 +4262,28 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>-0.288878793842746</v>
+        <v>0.184421149035861</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5069463220709832</v>
+        <v>-0.07737215590971719</v>
       </c>
       <c r="K24" t="n">
-        <v>0.08026007973424193</v>
+        <v>0.4360953186134832</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1815027688649611</v>
+        <v>-0.2636581925702242</v>
       </c>
       <c r="M24" t="n">
-        <v>0.03028224974760179</v>
+        <v>-0.2038948321803037</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2453835145277737</v>
+        <v>-0.03435143443778528</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>r_dep_liab</t>
+          <t>x_dep</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4434,10 +4292,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.007007032705532137</v>
+        <v>0.004661119417071724</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.140599762983867</v>
+        <v>0.1183461368588962</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4446,12 +4304,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>lowers risk</t>
+          <t>raises risk</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4460,20 +4318,20 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>-0.3607412825128094</v>
+        <v>0.1183461368588962</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
-        <v>-0.140599762983867</v>
+        <v>0.1905485262660289</v>
       </c>
       <c r="L25" t="n">
-        <v>0.325176830166655</v>
+        <v>-0.4743557013859739</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1267605301309362</v>
+        <v>-0.1031651012724288</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.28857799339305</v>
+        <v>0.3086496590012688</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/results_15_11a.xlsx
+++ b/outputs/tables/results_15_11a.xlsx
@@ -466,22 +466,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.897</v>
+        <v>0.864</v>
       </c>
       <c r="C2" t="n">
-        <v>0.79</v>
+        <v>0.755</v>
       </c>
       <c r="D2" t="n">
-        <v>0.74</v>
+        <v>0.742</v>
       </c>
       <c r="E2" t="n">
-        <v>0.699</v>
+        <v>0.698</v>
       </c>
       <c r="F2" t="n">
         <v>0.739</v>
       </c>
       <c r="G2" t="n">
-        <v>0.665</v>
+        <v>0.679</v>
       </c>
     </row>
     <row r="3">
@@ -491,22 +491,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.613</v>
+        <v>0.631</v>
       </c>
       <c r="C3" t="n">
-        <v>0.376</v>
+        <v>0.383</v>
       </c>
       <c r="D3" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.38</v>
+        <v>0.413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.53</v>
+        <v>0.659</v>
       </c>
       <c r="G3" t="n">
-        <v>0.361</v>
+        <v>0.399</v>
       </c>
     </row>
     <row r="4">
@@ -516,22 +516,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.745</v>
+        <v>0.757</v>
       </c>
       <c r="C4" t="n">
-        <v>0.579</v>
+        <v>0.576</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="E4" t="n">
-        <v>0.605</v>
+        <v>0.603</v>
       </c>
       <c r="F4" t="n">
-        <v>0.646</v>
+        <v>0.675</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.602</v>
       </c>
     </row>
     <row r="5">
@@ -541,22 +541,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.748</v>
+        <v>0.743</v>
       </c>
       <c r="C5" t="n">
-        <v>0.587</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.708</v>
+        <v>0.679</v>
       </c>
       <c r="E5" t="n">
-        <v>0.606</v>
+        <v>0.53</v>
       </c>
       <c r="F5" t="n">
-        <v>0.677</v>
+        <v>0.654</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.526</v>
       </c>
     </row>
     <row r="6">
@@ -566,22 +566,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.747</v>
+        <v>0.76</v>
       </c>
       <c r="C6" t="n">
-        <v>0.573</v>
+        <v>0.6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.657</v>
+        <v>0.673</v>
       </c>
       <c r="E6" t="n">
-        <v>0.552</v>
+        <v>0.606</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.733</v>
       </c>
       <c r="G6" t="n">
-        <v>0.583</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="7">
@@ -591,22 +591,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.744</v>
+        <v>0.698</v>
       </c>
       <c r="C7" t="n">
-        <v>0.541</v>
+        <v>0.5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.582</v>
+        <v>0.646</v>
       </c>
       <c r="E7" t="n">
-        <v>0.503</v>
+        <v>0.573</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="G7" t="n">
-        <v>0.471</v>
+        <v>0.47</v>
       </c>
     </row>
   </sheetData>
@@ -667,17 +667,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.126</v>
+        <v>0.008</v>
       </c>
       <c r="D2" t="n">
-        <v>0.13</v>
+        <v>0.532</v>
       </c>
       <c r="E2" t="n">
-        <v>0.127</v>
+        <v>0.112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.052</t>
         </is>
       </c>
     </row>
@@ -693,17 +693,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.212</v>
+        <v>0.183</v>
       </c>
       <c r="D3" t="n">
-        <v>0.521</v>
+        <v>0.698</v>
       </c>
       <c r="E3" t="n">
-        <v>0.274</v>
+        <v>0.286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.052</t>
         </is>
       </c>
     </row>
@@ -719,17 +719,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.17</v>
+        <v>0.136</v>
       </c>
       <c r="D4" t="n">
-        <v>0.385</v>
+        <v>0.463</v>
       </c>
       <c r="E4" t="n">
-        <v>0.213</v>
+        <v>0.201</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.033</t>
         </is>
       </c>
     </row>
@@ -745,17 +745,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.189</v>
+        <v>0.165</v>
       </c>
       <c r="D5" t="n">
-        <v>0.394</v>
+        <v>0.518</v>
       </c>
       <c r="E5" t="n">
-        <v>0.23</v>
+        <v>0.236</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.021</t>
+          <t>-0.035</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.181</v>
+        <v>0.294</v>
       </c>
       <c r="D6" t="n">
-        <v>0.408</v>
+        <v>0.369</v>
       </c>
       <c r="E6" t="n">
-        <v>0.227</v>
+        <v>0.309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.023</t>
+          <t>-0.008</t>
         </is>
       </c>
     </row>
@@ -797,17 +797,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.19</v>
+        <v>0.095</v>
       </c>
       <c r="D7" t="n">
-        <v>0.434</v>
+        <v>0.659</v>
       </c>
       <c r="E7" t="n">
-        <v>0.239</v>
+        <v>0.208</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.025</t>
+          <t>-0.056</t>
         </is>
       </c>
     </row>
@@ -823,17 +823,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.111</v>
+        <v>0.064</v>
       </c>
       <c r="D8" t="n">
-        <v>0.315</v>
+        <v>0.777</v>
       </c>
       <c r="E8" t="n">
-        <v>0.152</v>
+        <v>0.207</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.072</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.387</v>
+        <v>0.435</v>
       </c>
       <c r="D9" t="n">
-        <v>0.399</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.389</v>
+        <v>0.46</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.012</t>
         </is>
       </c>
     </row>
@@ -875,17 +875,17 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.215</v>
       </c>
       <c r="D10" t="n">
-        <v>0.466</v>
+        <v>0.654</v>
       </c>
       <c r="E10" t="n">
-        <v>0.162</v>
+        <v>0.303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.038</t>
+          <t>-0.044</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.195</v>
+        <v>0.334</v>
       </c>
       <c r="D11" t="n">
-        <v>0.211</v>
+        <v>0.632</v>
       </c>
       <c r="E11" t="n">
-        <v>0.199</v>
+        <v>0.393</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>-0.030</t>
         </is>
       </c>
     </row>
@@ -927,17 +927,17 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.144</v>
+        <v>0.268</v>
       </c>
       <c r="D12" t="n">
-        <v>0.432</v>
+        <v>0.391</v>
       </c>
       <c r="E12" t="n">
-        <v>0.202</v>
+        <v>0.292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.029</t>
+          <t>-0.012</t>
         </is>
       </c>
     </row>
@@ -953,17 +953,17 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1</v>
+        <v>0.101</v>
       </c>
       <c r="D13" t="n">
-        <v>0.417</v>
+        <v>0.657</v>
       </c>
       <c r="E13" t="n">
-        <v>0.163</v>
+        <v>0.212</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.055</t>
         </is>
       </c>
     </row>
@@ -979,17 +979,17 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.098</v>
+        <v>0.037</v>
       </c>
       <c r="D14" t="n">
-        <v>0.354</v>
+        <v>0.795</v>
       </c>
       <c r="E14" t="n">
-        <v>0.149</v>
+        <v>0.188</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.026</t>
+          <t>-0.076</t>
         </is>
       </c>
     </row>
@@ -1005,17 +1005,17 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.386</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.413</v>
+        <v>0.2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.003</t>
+          <t>-0.100</t>
         </is>
       </c>
     </row>
@@ -1031,17 +1031,17 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.125</v>
+        <v>0.073</v>
       </c>
       <c r="D16" t="n">
-        <v>0.442</v>
+        <v>0.623</v>
       </c>
       <c r="E16" t="n">
-        <v>0.188</v>
+        <v>0.183</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.055</t>
         </is>
       </c>
     </row>
@@ -1057,17 +1057,17 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.282</v>
+        <v>0.272</v>
       </c>
       <c r="D17" t="n">
-        <v>0.183</v>
+        <v>0.636</v>
       </c>
       <c r="E17" t="n">
-        <v>0.262</v>
+        <v>0.345</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.037</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.182</v>
+        <v>0.241</v>
       </c>
       <c r="D18" t="n">
-        <v>0.369</v>
+        <v>0.519</v>
       </c>
       <c r="E18" t="n">
-        <v>0.22</v>
+        <v>0.297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.019</t>
+          <t>-0.028</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1109,17 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.165</v>
+        <v>0.061</v>
       </c>
       <c r="D19" t="n">
-        <v>0.477</v>
+        <v>0.701</v>
       </c>
       <c r="E19" t="n">
-        <v>0.227</v>
+        <v>0.189</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.064</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1150,12 +1150,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Brier Score</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Best Threshold</t>
+          <t>Alarm cut-off (mean over test years)</t>
         </is>
       </c>
     </row>
@@ -1171,10 +1166,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.657</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="3">
@@ -1189,10 +1181,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.473</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4">
@@ -1207,10 +1196,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.437</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="5">
@@ -1225,10 +1211,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.436</v>
+        <v>0.358</v>
       </c>
     </row>
     <row r="6">
@@ -1243,10 +1226,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.467</v>
+        <v>0.416</v>
       </c>
     </row>
     <row r="7">
@@ -1261,10 +1241,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.223</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.466</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="8">
@@ -1279,10 +1256,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.475</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="9">
@@ -1297,10 +1271,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.379</v>
+        <v>0.512</v>
       </c>
     </row>
     <row r="10">
@@ -1315,10 +1286,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.339</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="11">
@@ -1333,10 +1301,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.488</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="12">
@@ -1351,10 +1316,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.349</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.293</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="13">
@@ -1369,10 +1331,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1387,10 +1346,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.48</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="15">
@@ -1405,10 +1361,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1423,10 +1376,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.267</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="17">
@@ -1441,10 +1391,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.535</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="18">
@@ -1459,10 +1406,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.264</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="19">
@@ -1477,10 +1421,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.404</v>
+        <v>0.138</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +1435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1550,25 +1491,20 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>brier</t>
+          <t>best_threshold</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>best_threshold</t>
+          <t>loss_07</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>loss_07</t>
+          <t>loss_09</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
-        <is>
-          <t>loss_09</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
@@ -1586,43 +1522,40 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.53</v>
+        <v>0.659</v>
       </c>
       <c r="D2" t="n">
-        <v>0.451</v>
+        <v>0.417</v>
       </c>
       <c r="E2" t="n">
-        <v>0.58</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.539</v>
+        <v>0.264</v>
       </c>
       <c r="G2" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.386</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.413</v>
+        <v>0.2</v>
       </c>
       <c r="J2" t="n">
-        <v>0.361</v>
+        <v>0.399</v>
       </c>
       <c r="K2" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.667</v>
+        <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0.41</v>
+        <v>0.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.6</v>
+        <v>0.264</v>
       </c>
     </row>
     <row r="3">
@@ -1637,43 +1570,40 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="D3" t="n">
-        <v>0.471</v>
+        <v>0.336</v>
       </c>
       <c r="E3" t="n">
-        <v>0.613</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.492</v>
       </c>
       <c r="G3" t="n">
-        <v>0.387</v>
+        <v>0.435</v>
       </c>
       <c r="H3" t="n">
-        <v>0.399</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.389</v>
+        <v>0.46</v>
       </c>
       <c r="J3" t="n">
-        <v>0.38</v>
+        <v>0.413</v>
       </c>
       <c r="K3" t="n">
-        <v>0.443</v>
+        <v>0.512</v>
       </c>
       <c r="L3" t="n">
-        <v>0.379</v>
+        <v>0.473</v>
       </c>
       <c r="M3" t="n">
-        <v>0.39</v>
+        <v>0.448</v>
       </c>
       <c r="N3" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.602</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="4">
@@ -1688,43 +1618,40 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.613</v>
+        <v>0.631</v>
       </c>
       <c r="D4" t="n">
-        <v>0.501</v>
+        <v>0.454</v>
       </c>
       <c r="E4" t="n">
-        <v>0.788</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.382</v>
+        <v>0.354</v>
       </c>
       <c r="G4" t="n">
-        <v>0.212</v>
+        <v>0.183</v>
       </c>
       <c r="H4" t="n">
-        <v>0.521</v>
+        <v>0.698</v>
       </c>
       <c r="I4" t="n">
-        <v>0.274</v>
+        <v>0.286</v>
       </c>
       <c r="J4" t="n">
-        <v>0.376</v>
+        <v>0.383</v>
       </c>
       <c r="K4" t="n">
-        <v>0.289</v>
+        <v>0.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0.473</v>
+        <v>0.337</v>
       </c>
       <c r="M4" t="n">
-        <v>0.305</v>
+        <v>0.234</v>
       </c>
       <c r="N4" t="n">
-        <v>0.243</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.439</v>
       </c>
     </row>
     <row r="5">
@@ -1739,43 +1666,40 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.733</v>
       </c>
       <c r="D5" t="n">
-        <v>0.65</v>
+        <v>0.474</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.759</v>
       </c>
       <c r="F5" t="n">
-        <v>0.634</v>
+        <v>0.41</v>
       </c>
       <c r="G5" t="n">
-        <v>0.182</v>
+        <v>0.241</v>
       </c>
       <c r="H5" t="n">
-        <v>0.369</v>
+        <v>0.519</v>
       </c>
       <c r="I5" t="n">
-        <v>0.22</v>
+        <v>0.297</v>
       </c>
       <c r="J5" t="n">
-        <v>0.583</v>
+        <v>0.62</v>
       </c>
       <c r="K5" t="n">
-        <v>0.293</v>
+        <v>0.035</v>
       </c>
       <c r="L5" t="n">
-        <v>0.264</v>
+        <v>0.325</v>
       </c>
       <c r="M5" t="n">
-        <v>0.238</v>
+        <v>0.269</v>
       </c>
       <c r="N5" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.661</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="6">
@@ -1790,43 +1714,40 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.657</v>
+        <v>0.673</v>
       </c>
       <c r="D6" t="n">
-        <v>0.586</v>
+        <v>0.537</v>
       </c>
       <c r="E6" t="n">
-        <v>0.856</v>
+        <v>0.732</v>
       </c>
       <c r="F6" t="n">
-        <v>0.503</v>
+        <v>0.593</v>
       </c>
       <c r="G6" t="n">
-        <v>0.144</v>
+        <v>0.268</v>
       </c>
       <c r="H6" t="n">
-        <v>0.432</v>
+        <v>0.391</v>
       </c>
       <c r="I6" t="n">
-        <v>0.202</v>
+        <v>0.292</v>
       </c>
       <c r="J6" t="n">
-        <v>0.552</v>
+        <v>0.606</v>
       </c>
       <c r="K6" t="n">
-        <v>0.349</v>
+        <v>0.115</v>
       </c>
       <c r="L6" t="n">
-        <v>0.293</v>
+        <v>0.305</v>
       </c>
       <c r="M6" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="N6" t="n">
-        <v>0.173</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.644</v>
+        <v>0.639</v>
       </c>
     </row>
     <row r="7">
@@ -1841,43 +1762,40 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.747</v>
+        <v>0.76</v>
       </c>
       <c r="D7" t="n">
-        <v>0.604</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.819</v>
+        <v>0.706</v>
       </c>
       <c r="F7" t="n">
-        <v>0.536</v>
+        <v>0.574</v>
       </c>
       <c r="G7" t="n">
-        <v>0.181</v>
+        <v>0.294</v>
       </c>
       <c r="H7" t="n">
-        <v>0.408</v>
+        <v>0.369</v>
       </c>
       <c r="I7" t="n">
-        <v>0.227</v>
+        <v>0.309</v>
       </c>
       <c r="J7" t="n">
-        <v>0.573</v>
+        <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>0.238</v>
+        <v>0.416</v>
       </c>
       <c r="L7" t="n">
-        <v>0.467</v>
+        <v>0.316</v>
       </c>
       <c r="M7" t="n">
-        <v>0.249</v>
+        <v>0.301</v>
       </c>
       <c r="N7" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.654</v>
+        <v>0.649</v>
       </c>
     </row>
     <row r="8">
@@ -1895,40 +1813,37 @@
         <v>0.739</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="E8" t="n">
-        <v>0.902</v>
+        <v>0.963</v>
       </c>
       <c r="F8" t="n">
-        <v>0.609</v>
+        <v>0.313</v>
       </c>
       <c r="G8" t="n">
-        <v>0.098</v>
+        <v>0.037</v>
       </c>
       <c r="H8" t="n">
-        <v>0.354</v>
+        <v>0.795</v>
       </c>
       <c r="I8" t="n">
-        <v>0.149</v>
+        <v>0.188</v>
       </c>
       <c r="J8" t="n">
-        <v>0.665</v>
+        <v>0.679</v>
       </c>
       <c r="K8" t="n">
-        <v>0.357</v>
+        <v>0.157</v>
       </c>
       <c r="L8" t="n">
-        <v>0.48</v>
+        <v>0.264</v>
       </c>
       <c r="M8" t="n">
-        <v>0.175</v>
+        <v>0.112</v>
       </c>
       <c r="N8" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.715</v>
+        <v>0.406</v>
       </c>
     </row>
     <row r="9">
@@ -1943,43 +1858,40 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.74</v>
+        <v>0.742</v>
       </c>
       <c r="D9" t="n">
-        <v>0.718</v>
+        <v>0.468</v>
       </c>
       <c r="E9" t="n">
-        <v>0.889</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.679</v>
+        <v>0.315</v>
       </c>
       <c r="G9" t="n">
-        <v>0.111</v>
+        <v>0.064</v>
       </c>
       <c r="H9" t="n">
-        <v>0.315</v>
+        <v>0.777</v>
       </c>
       <c r="I9" t="n">
-        <v>0.152</v>
+        <v>0.207</v>
       </c>
       <c r="J9" t="n">
-        <v>0.699</v>
+        <v>0.698</v>
       </c>
       <c r="K9" t="n">
-        <v>0.353</v>
+        <v>0.162</v>
       </c>
       <c r="L9" t="n">
-        <v>0.475</v>
+        <v>0.278</v>
       </c>
       <c r="M9" t="n">
-        <v>0.172</v>
+        <v>0.135</v>
       </c>
       <c r="N9" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.74</v>
+        <v>0.412</v>
       </c>
     </row>
     <row r="10">
@@ -1994,43 +1906,40 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.897</v>
+        <v>0.864</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.631</v>
       </c>
       <c r="E10" t="n">
-        <v>0.874</v>
+        <v>0.992</v>
       </c>
       <c r="F10" t="n">
-        <v>0.763</v>
+        <v>0.507</v>
       </c>
       <c r="G10" t="n">
-        <v>0.126</v>
+        <v>0.008</v>
       </c>
       <c r="H10" t="n">
-        <v>0.13</v>
+        <v>0.532</v>
       </c>
       <c r="I10" t="n">
-        <v>0.127</v>
+        <v>0.112</v>
       </c>
       <c r="J10" t="n">
-        <v>0.79</v>
+        <v>0.755</v>
       </c>
       <c r="K10" t="n">
-        <v>0.186</v>
+        <v>0.286</v>
       </c>
       <c r="L10" t="n">
-        <v>0.657</v>
+        <v>0.165</v>
       </c>
       <c r="M10" t="n">
-        <v>0.127</v>
+        <v>0.06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.871</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="11">
@@ -2045,43 +1954,40 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="D11" t="n">
-        <v>0.58</v>
+        <v>0.514</v>
       </c>
       <c r="E11" t="n">
-        <v>0.835</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.492</v>
+        <v>0.376</v>
       </c>
       <c r="G11" t="n">
-        <v>0.165</v>
+        <v>0.061</v>
       </c>
       <c r="H11" t="n">
-        <v>0.477</v>
+        <v>0.701</v>
       </c>
       <c r="I11" t="n">
-        <v>0.227</v>
+        <v>0.189</v>
       </c>
       <c r="J11" t="n">
-        <v>0.471</v>
+        <v>0.47</v>
       </c>
       <c r="K11" t="n">
-        <v>0.353</v>
+        <v>0.138</v>
       </c>
       <c r="L11" t="n">
-        <v>0.404</v>
+        <v>0.253</v>
       </c>
       <c r="M11" t="n">
-        <v>0.258</v>
+        <v>0.125</v>
       </c>
       <c r="N11" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.609</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="12">
@@ -2096,43 +2002,40 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.582</v>
+        <v>0.646</v>
       </c>
       <c r="D12" t="n">
-        <v>0.644</v>
+        <v>0.527</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9</v>
+        <v>0.899</v>
       </c>
       <c r="F12" t="n">
-        <v>0.536</v>
+        <v>0.434</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1</v>
+        <v>0.101</v>
       </c>
       <c r="H12" t="n">
-        <v>0.417</v>
+        <v>0.657</v>
       </c>
       <c r="I12" t="n">
-        <v>0.163</v>
+        <v>0.212</v>
       </c>
       <c r="J12" t="n">
-        <v>0.503</v>
+        <v>0.573</v>
       </c>
       <c r="K12" t="n">
-        <v>0.352</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.315</v>
+        <v>0.268</v>
       </c>
       <c r="M12" t="n">
-        <v>0.195</v>
+        <v>0.157</v>
       </c>
       <c r="N12" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.67</v>
+        <v>0.487</v>
       </c>
     </row>
     <row r="13">
@@ -2147,43 +2050,40 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.744</v>
+        <v>0.698</v>
       </c>
       <c r="D13" t="n">
-        <v>0.57</v>
+        <v>0.517</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.905</v>
       </c>
       <c r="F13" t="n">
-        <v>0.469</v>
+        <v>0.387</v>
       </c>
       <c r="G13" t="n">
-        <v>0.19</v>
+        <v>0.095</v>
       </c>
       <c r="H13" t="n">
-        <v>0.434</v>
+        <v>0.659</v>
       </c>
       <c r="I13" t="n">
-        <v>0.239</v>
+        <v>0.208</v>
       </c>
       <c r="J13" t="n">
-        <v>0.541</v>
+        <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>0.223</v>
+        <v>0.387</v>
       </c>
       <c r="L13" t="n">
-        <v>0.466</v>
+        <v>0.265</v>
       </c>
       <c r="M13" t="n">
-        <v>0.263</v>
+        <v>0.152</v>
       </c>
       <c r="N13" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.633</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="14">
@@ -2198,43 +2098,40 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.646</v>
+        <v>0.675</v>
       </c>
       <c r="D14" t="n">
-        <v>0.625</v>
+        <v>0.519</v>
       </c>
       <c r="E14" t="n">
-        <v>0.875</v>
+        <v>0.927</v>
       </c>
       <c r="F14" t="n">
-        <v>0.533</v>
+        <v>0.369</v>
       </c>
       <c r="G14" t="n">
-        <v>0.125</v>
+        <v>0.073</v>
       </c>
       <c r="H14" t="n">
-        <v>0.442</v>
+        <v>0.623</v>
       </c>
       <c r="I14" t="n">
-        <v>0.188</v>
+        <v>0.183</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.602</v>
       </c>
       <c r="K14" t="n">
-        <v>0.209</v>
+        <v>0.235</v>
       </c>
       <c r="L14" t="n">
-        <v>0.267</v>
+        <v>0.238</v>
       </c>
       <c r="M14" t="n">
-        <v>0.22</v>
+        <v>0.128</v>
       </c>
       <c r="N14" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.645</v>
+        <v>0.521</v>
       </c>
     </row>
     <row r="15">
@@ -2249,43 +2146,40 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="D15" t="n">
-        <v>0.64</v>
+        <v>0.442</v>
       </c>
       <c r="E15" t="n">
-        <v>0.914</v>
+        <v>0.785</v>
       </c>
       <c r="F15" t="n">
-        <v>0.577</v>
+        <v>0.417</v>
       </c>
       <c r="G15" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.215</v>
       </c>
       <c r="H15" t="n">
-        <v>0.466</v>
+        <v>0.654</v>
       </c>
       <c r="I15" t="n">
-        <v>0.162</v>
+        <v>0.303</v>
       </c>
       <c r="J15" t="n">
-        <v>0.605</v>
+        <v>0.603</v>
       </c>
       <c r="K15" t="n">
-        <v>0.204</v>
+        <v>0.17</v>
       </c>
       <c r="L15" t="n">
-        <v>0.339</v>
+        <v>0.347</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2</v>
+        <v>0.259</v>
       </c>
       <c r="N15" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.639</v>
+        <v>0.459</v>
       </c>
     </row>
     <row r="16">
@@ -2300,43 +2194,40 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.745</v>
+        <v>0.757</v>
       </c>
       <c r="D16" t="n">
-        <v>0.626</v>
+        <v>0.583</v>
       </c>
       <c r="E16" t="n">
-        <v>0.83</v>
+        <v>0.864</v>
       </c>
       <c r="F16" t="n">
-        <v>0.548</v>
+        <v>0.482</v>
       </c>
       <c r="G16" t="n">
-        <v>0.17</v>
+        <v>0.136</v>
       </c>
       <c r="H16" t="n">
-        <v>0.385</v>
+        <v>0.463</v>
       </c>
       <c r="I16" t="n">
-        <v>0.213</v>
+        <v>0.201</v>
       </c>
       <c r="J16" t="n">
-        <v>0.579</v>
+        <v>0.576</v>
       </c>
       <c r="K16" t="n">
-        <v>0.226</v>
+        <v>0.4</v>
       </c>
       <c r="L16" t="n">
-        <v>0.437</v>
+        <v>0.234</v>
       </c>
       <c r="M16" t="n">
-        <v>0.234</v>
+        <v>0.168</v>
       </c>
       <c r="N16" t="n">
-        <v>0.191</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.675</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="17">
@@ -2351,43 +2242,40 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.677</v>
+        <v>0.654</v>
       </c>
       <c r="D17" t="n">
-        <v>0.67</v>
+        <v>0.385</v>
       </c>
       <c r="E17" t="n">
-        <v>0.718</v>
+        <v>0.728</v>
       </c>
       <c r="F17" t="n">
-        <v>0.713</v>
+        <v>0.441</v>
       </c>
       <c r="G17" t="n">
-        <v>0.282</v>
+        <v>0.272</v>
       </c>
       <c r="H17" t="n">
-        <v>0.183</v>
+        <v>0.636</v>
       </c>
       <c r="I17" t="n">
-        <v>0.262</v>
+        <v>0.345</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.526</v>
       </c>
       <c r="K17" t="n">
-        <v>0.25</v>
+        <v>0.194</v>
       </c>
       <c r="L17" t="n">
-        <v>0.535</v>
+        <v>0.381</v>
       </c>
       <c r="M17" t="n">
-        <v>0.253</v>
+        <v>0.308</v>
       </c>
       <c r="N17" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.791</v>
+        <v>0.457</v>
       </c>
     </row>
     <row r="18">
@@ -2402,43 +2290,40 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.708</v>
+        <v>0.679</v>
       </c>
       <c r="D18" t="n">
-        <v>0.709</v>
+        <v>0.323</v>
       </c>
       <c r="E18" t="n">
-        <v>0.805</v>
+        <v>0.666</v>
       </c>
       <c r="F18" t="n">
-        <v>0.696</v>
+        <v>0.277</v>
       </c>
       <c r="G18" t="n">
-        <v>0.195</v>
+        <v>0.334</v>
       </c>
       <c r="H18" t="n">
-        <v>0.211</v>
+        <v>0.632</v>
       </c>
       <c r="I18" t="n">
-        <v>0.199</v>
+        <v>0.393</v>
       </c>
       <c r="J18" t="n">
-        <v>0.606</v>
+        <v>0.53</v>
       </c>
       <c r="K18" t="n">
-        <v>0.25</v>
+        <v>0.222</v>
       </c>
       <c r="L18" t="n">
-        <v>0.488</v>
+        <v>0.423</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2</v>
+        <v>0.363</v>
       </c>
       <c r="N18" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.794</v>
+        <v>0.443</v>
       </c>
     </row>
     <row r="19">
@@ -2453,43 +2338,40 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.748</v>
+        <v>0.743</v>
       </c>
       <c r="D19" t="n">
-        <v>0.604</v>
+        <v>0.533</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.835</v>
       </c>
       <c r="F19" t="n">
-        <v>0.527</v>
+        <v>0.447</v>
       </c>
       <c r="G19" t="n">
-        <v>0.189</v>
+        <v>0.165</v>
       </c>
       <c r="H19" t="n">
-        <v>0.394</v>
+        <v>0.518</v>
       </c>
       <c r="I19" t="n">
-        <v>0.23</v>
+        <v>0.236</v>
       </c>
       <c r="J19" t="n">
-        <v>0.587</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.233</v>
+        <v>0.358</v>
       </c>
       <c r="L19" t="n">
-        <v>0.436</v>
+        <v>0.271</v>
       </c>
       <c r="M19" t="n">
-        <v>0.25</v>
+        <v>0.201</v>
       </c>
       <c r="N19" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.662</v>
+        <v>0.575</v>
       </c>
     </row>
   </sheetData>
@@ -2555,10 +2437,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.174</v>
+        <v>-0.513</v>
       </c>
       <c r="D2" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -2581,10 +2463,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.957</v>
+        <v>1.287</v>
       </c>
       <c r="D3" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>3</v>
@@ -2594,11 +2476,6 @@
           <t>LightGBM</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2612,10 +2489,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-1.108</v>
+        <v>-0.611</v>
       </c>
       <c r="D4" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -2638,10 +2515,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.742</v>
+        <v>-2.492</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
@@ -2664,10 +2541,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-1.932</v>
+        <v>0.141</v>
       </c>
       <c r="D6" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -2690,10 +2567,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.706</v>
+        <v>0.253</v>
       </c>
       <c r="D7" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
@@ -2716,10 +2593,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-2.131</v>
+        <v>0.728</v>
       </c>
       <c r="D8" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
@@ -2742,10 +2619,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-1.107</v>
+        <v>0.065</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -2768,10 +2645,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-4.19</v>
+        <v>-2.795</v>
       </c>
       <c r="D10" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
@@ -2794,10 +2671,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-4.297</v>
+        <v>-3.428</v>
       </c>
       <c r="D11" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -2820,10 +2697,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-2.14</v>
+        <v>-0.976</v>
       </c>
       <c r="D12" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
@@ -2846,10 +2723,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-1.46</v>
+        <v>-1.83</v>
       </c>
       <c r="D13" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>3</v>
@@ -2937,16 +2814,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.174</v>
+        <v>-0.513</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.131</v>
+        <v>0.728</v>
       </c>
       <c r="D4" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2956,21 +2833,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.957</v>
+        <v>1.287</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.107</v>
+        <v>0.065</v>
       </c>
       <c r="D5" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2980,16 +2852,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.108</v>
+        <v>-0.611</v>
       </c>
       <c r="C6" t="n">
-        <v>-4.19</v>
+        <v>-2.795</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.333</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.667</v>
       </c>
     </row>
     <row r="7">
@@ -2999,16 +2871,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.742</v>
+        <v>-2.492</v>
       </c>
       <c r="C7" t="n">
-        <v>-4.297</v>
+        <v>-3.428</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="E7" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="8">
@@ -3018,16 +2890,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.932</v>
+        <v>0.141</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.14</v>
+        <v>-0.976</v>
       </c>
       <c r="D8" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="9">
@@ -3037,16 +2909,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.706</v>
+        <v>0.253</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.46</v>
+        <v>-1.83</v>
       </c>
       <c r="D9" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3152,10 +3024,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9265863122647752</v>
+        <v>0.9885863571119599</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.8501461146113416</v>
+        <v>-0.8690314588372627</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3178,22 +3050,22 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>-0.9560395534847204</v>
+        <v>-0.943717525843264</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.7614875654324363</v>
+        <v>-0.7499053050216398</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.8596650558447358</v>
+        <v>-0.9079510609026601</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.9207121452627373</v>
+        <v>-0.8893738141833631</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8406271733779473</v>
+        <v>-0.8486891034911624</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7654476686680941</v>
+        <v>-0.7184015397527843</v>
       </c>
     </row>
     <row r="3">
@@ -3208,10 +3080,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.6542367001081102</v>
+        <v>0.7362932456960073</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7863099168273141</v>
+        <v>0.8012078186918098</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3234,22 +3106,22 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.7602334581970298</v>
+        <v>0.6504462261562497</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6359875800366256</v>
+        <v>0.7574872284966156</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8290485760380926</v>
+        <v>0.8087006631618269</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8657536232434998</v>
+        <v>0.8481915874446456</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8024969368506468</v>
+        <v>0.8455814404918127</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7701228968039814</v>
+        <v>0.7937149742217927</v>
       </c>
     </row>
     <row r="4">
@@ -3264,10 +3136,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.5710484494305808</v>
+        <v>0.5787229306591292</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5505683435119144</v>
+        <v>-0.4933981596286846</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3276,7 +3148,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3290,22 +3162,22 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>-0.3060631041203119</v>
+        <v>-0.3514986130714824</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.5910784730513579</v>
+        <v>-0.1199853839954683</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5111258226201523</v>
+        <v>-0.4771975857033915</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5586845865036839</v>
+        <v>-0.5110067975137313</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5424521005201449</v>
+        <v>-0.5095987335539777</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5739820287820051</v>
+        <v>-0.5268794361932545</v>
       </c>
     </row>
     <row r="5">
@@ -3320,19 +3192,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.3275418728407907</v>
+        <v>0.3839596130668073</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9029537103531189</v>
+        <v>0.8773597115101497</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3342,32 +3214,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>reportable</t>
+          <t>non-monotone</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.8850546727255526</v>
+        <v>0.8860782092369827</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5002986811705231</v>
+        <v>0.4076285842323947</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9214079847251373</v>
+        <v>0.8852881440326668</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9350347558674083</v>
+        <v>0.8199894173698696</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9208527479806852</v>
+        <v>0.8694312789876325</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8561962013528077</v>
+        <v>0.93264434882647</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PCPIPCH</t>
+          <t>RXF11FX_REVS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3376,54 +3248,54 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.2773734126547638</v>
+        <v>0.2819241191159572</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3493613287215372</v>
+        <v>-0.4927286034851658</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>weak/noisy</t>
+          <t>non-monotone</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>-0.1032107381408622</v>
+        <v>-0.8024041157697863</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4174638922038403</v>
+        <v>-0.3978706823336592</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7363635532739682</v>
+        <v>-0.4898594645261373</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2812587652392342</v>
+        <v>-0.4955977424441944</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7427053615415067</v>
+        <v>-0.4175334780406328</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.241150567660822</v>
+        <v>-0.5736092947324511</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RXF11FX_REVS</t>
+          <t>PCPIPCH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3432,24 +3304,24 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2561800350696424</v>
+        <v>0.2551349225459353</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4208330499318674</v>
+        <v>0.4099741831813072</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>lowers risk</t>
+          <t>raises risk</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3458,22 +3330,22 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>-0.7931592247819945</v>
+        <v>0.2816895121901261</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3967241847934448</v>
+        <v>0.1643604143745238</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3895043791282821</v>
+        <v>0.747038942079877</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.44494191507029</v>
+        <v>0.6561754331232619</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3531146271776288</v>
+        <v>0.5382588541724882</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5208725287142381</v>
+        <v>-0.3320585732758957</v>
       </c>
     </row>
     <row r="8">
@@ -3488,10 +3360,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1193977124790572</v>
+        <v>0.1911205331071681</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04557599331390627</v>
+        <v>0.01194436486474752</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -3500,7 +3372,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3514,22 +3386,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>-0.09629930569732617</v>
+        <v>-0.2680652635089166</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2454631318451621</v>
+        <v>-0.1812028782373915</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09215629152405835</v>
+        <v>-0.1142275616263036</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2797573075974532</v>
+        <v>0.4495773195126967</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1125944690013834</v>
+        <v>0.5375139456670206</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.001004304896245808</v>
+        <v>0.1381162913557986</v>
       </c>
     </row>
     <row r="9">
@@ -3544,10 +3416,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.1011193558996304</v>
+        <v>0.1397347843284264</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5115169928661184</v>
+        <v>0.5896744749350519</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -3570,22 +3442,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9446948581645295</v>
+        <v>0.9080295048877592</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2055171304562143</v>
+        <v>0.4303342721625845</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7609499101432272</v>
+        <v>0.7542139292927121</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5563630746846909</v>
+        <v>0.5893945019774244</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4666709110475459</v>
+        <v>0.5899544478926794</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3471567092015995</v>
+        <v>0.4253972744754023</v>
       </c>
     </row>
     <row r="10">
@@ -3600,10 +3472,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.09082432606716123</v>
+        <v>0.1047455038952878</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4294555279147809</v>
+        <v>0.4509975994065881</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -3626,28 +3498,28 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>-0.3338476561245598</v>
+        <v>-0.2291476560397598</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5715904730313753</v>
+        <v>0.4648330010025928</v>
       </c>
       <c r="K10" t="n">
-        <v>0.546826040018039</v>
+        <v>0.5055796755285188</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5229421000588953</v>
+        <v>0.5201064104548495</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3359689557706665</v>
+        <v>0.4371621978105835</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1353174598395</v>
+        <v>-0.2407102792548046</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>p_roe</t>
+          <t>l_assets</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3656,46 +3528,44 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.05473046835154706</v>
+        <v>0.05257008342111535</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4777226175957648</v>
+        <v>0.8458938473926163</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>lowers risk</t>
+          <t>raises risk</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>reportable</t>
+          <t>weak/noisy</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>-0.8829776051711064</v>
+        <v>0.9258166082896413</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>-0.6966622873865808</v>
+        <v>0.8792466584520346</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3846476250237861</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-0.4777226175957648</v>
-      </c>
+        <v>0.4771615220325487</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>-0.4393462907808177</v>
+        <v>0.8125410363331981</v>
       </c>
     </row>
     <row r="12">
@@ -3710,19 +3580,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04293170879251015</v>
+        <v>0.04946518579441286</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4521540911098725</v>
+        <v>-0.7870711536167664</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3732,32 +3602,30 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>non-monotone</t>
+          <t>weak/noisy</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>-0.9399936133719057</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-0.3529095816908794</v>
-      </c>
+        <v>-0.9680526886385442</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>-0.7061009443174298</v>
+        <v>-0.8024044217114831</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1391119653083442</v>
+        <v>0.05288684866159458</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1426358921537539</v>
+        <v>-0.005418811121158866</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5513986005288657</v>
+        <v>-0.7870711536167664</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>l_assets</t>
+          <t>p_roe</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3766,24 +3634,24 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02786723628180906</v>
+        <v>0.04117481632445684</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7212820164239462</v>
+        <v>-0.5260217016652066</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3792,28 +3660,26 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9593608852380473</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.2912548156217548</v>
-      </c>
+        <v>-0.8849606273039714</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>0.744583230804149</v>
+        <v>-0.8258579967551386</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8334196791731932</v>
+        <v>-0.3586502449652292</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6979808020437432</v>
+        <v>-0.03090871463443269</v>
       </c>
       <c r="N13" t="n">
-        <v>0.305870586292858</v>
+        <v>-0.5260217016652066</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>p_roa</t>
+          <t>l_loans</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3822,19 +3688,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02295011574974603</v>
+        <v>0.03872030022096926</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3467844784464797</v>
+        <v>-0.3557150801273142</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3844,32 +3710,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>reportable</t>
+          <t>weak/noisy</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6056669098469238</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-0.2220149032530638</v>
-      </c>
+        <v>-0.6629807460032748</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>-0.8520520887291622</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-0.4510167188506159</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-0.4870885407404747</v>
-      </c>
+        <v>-0.08623493979920692</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>-0.2425522380423436</v>
+        <v>-0.3557150801273142</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>r_cti</t>
+          <t>r_dep_liab</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3878,54 +3738,54 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.01843497381777106</v>
+        <v>0.02291762566096773</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3284025128537458</v>
+        <v>-0.08515442640984888</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>6/6</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>reportable</t>
+          <t>weak/noisy</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.1739525125801134</v>
+        <v>0.8944051103159321</v>
       </c>
       <c r="J15" t="n">
-        <v>0.03130369573642432</v>
+        <v>0.4596084197305944</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5729904391587065</v>
+        <v>-0.5639864620669205</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7886989191386873</v>
+        <v>-0.5683605835971336</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4828525131273782</v>
+        <v>-0.4665257975211977</v>
       </c>
       <c r="N15" t="n">
-        <v>0.01535865970019359</v>
+        <v>0.2962169447015</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>x_loans_gross</t>
+          <t>inc_nii</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3934,19 +3794,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.01721962998688673</v>
+        <v>0.021361068627439</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1527592351245601</v>
+        <v>0.5263643829312822</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -3956,30 +3816,30 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>weak/noisy</t>
+          <t>reportable</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.2583954166090168</v>
+        <v>0.7516550831204667</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>0.1527592351245601</v>
+        <v>0.4663168422112104</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.01890137895093107</v>
+        <v>0.5267295965508588</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4847434414606122</v>
+        <v>0.5263643829312822</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2235916619418466</v>
+        <v>0.3257874951512848</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>c_eqratio</t>
+          <t>r_loans_assets</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3988,54 +3848,52 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01675021584638044</v>
+        <v>0.02015822717286732</v>
       </c>
       <c r="D17" t="n">
-        <v>0.05282997114440009</v>
+        <v>-0.599493191422514</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>weak/noisy</t>
+          <t>non-monotone</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>-0.9442227256629292</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.6743117087762643</v>
-      </c>
+        <v>-0.07424695291331271</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
-        <v>-0.1443095191281283</v>
+        <v>-0.6132366459576603</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2671898290856319</v>
+        <v>-0.6594898953928605</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2267675931589018</v>
+        <v>-0.599493191422514</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1211076508701016</v>
+        <v>-0.04830311615343221</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>c_leverage</t>
+          <t>x_loans_gross</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4044,54 +3902,52 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01628334930962503</v>
+        <v>0.0182071812551863</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02090598614255212</v>
+        <v>-0.4783904567564263</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>weak/noisy</t>
+          <t>reportable</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8554233531278415</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-0.01372941228540354</v>
-      </c>
+        <v>-0.5375638383057139</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>0.05554138457050777</v>
+        <v>-0.08912061290968729</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3125672931641892</v>
+        <v>-0.4783904567564263</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4699844374802075</v>
+        <v>-0.5434278203289473</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1245702620095101</v>
+        <v>-0.09585425027196119</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>inc_nii</t>
+          <t>x_ib_liab</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4100,14 +3956,14 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0158586996350084</v>
+        <v>0.01643232935939247</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2446780438675702</v>
+        <v>0.1260147071931156</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4126,26 +3982,26 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7957428921585367</v>
+        <v>-0.7804484347563062</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
-        <v>0.4629312423976412</v>
+        <v>0.7065395368724295</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2042913840283628</v>
+        <v>0.5583581500717057</v>
       </c>
       <c r="M19" t="n">
-        <v>0.07114333173461385</v>
+        <v>0.07869397064189801</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2446780438675702</v>
+        <v>0.1260147071931156</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>l_loans</t>
+          <t>c_leverage</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4154,19 +4010,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01579385868721337</v>
+        <v>0.01398744092613009</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2102211965039827</v>
+        <v>0.3189426810173615</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4180,22 +4036,20 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>-0.9216271484216884</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.3691480340409087</v>
-      </c>
+        <v>-0.2032889963524596</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>0.1271015883484623</v>
+        <v>0.5941400888149254</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6160627695018456</v>
+        <v>0.4671947949652293</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2933408046595032</v>
+        <v>0.17744534489176</v>
       </c>
       <c r="N20" t="n">
-        <v>0.06074357636202452</v>
+        <v>0.3189426810173615</v>
       </c>
     </row>
     <row r="21">
@@ -4210,14 +4064,14 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.014775861726635</v>
+        <v>0.01385327322217497</v>
       </c>
       <c r="D21" t="n">
-        <v>0.03879948696708894</v>
+        <v>0.2040597581431681</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4236,28 +4090,28 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>-0.7854007029733936</v>
+        <v>-0.0870114368064303</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0956584239277749</v>
+        <v>0.09622815516921925</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6035777785626077</v>
+        <v>0.6227099508515606</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3435087042773529</v>
+        <v>0.5278048254073249</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1077717961005886</v>
+        <v>0.311891361117117</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.01805944999359701</v>
+        <v>-0.1767860663109414</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>x_dep</t>
+          <t>p_roa</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4266,10 +4120,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01394502921070186</v>
+        <v>0.01156208359192042</v>
       </c>
       <c r="D22" t="n">
-        <v>0.02092406826779631</v>
+        <v>-0.5682722282723427</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4278,42 +4132,40 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>weak/noisy</t>
+          <t>reportable</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.01908724499681764</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.01078215976994487</v>
-      </c>
+        <v>-0.3639479953585161</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="n">
-        <v>0.1969284645667818</v>
+        <v>-0.9186474527794415</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02276089153877498</v>
+        <v>-0.5861690698621121</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1156350731373365</v>
+        <v>-0.5682722282723427</v>
       </c>
       <c r="N22" t="n">
-        <v>0.316506137619509</v>
+        <v>-0.3554059319268127</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>x_ib_liab</t>
+          <t>c_eqratio</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4322,19 +4174,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.009152551474894551</v>
+        <v>0.008946727768330453</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.04751412914801201</v>
+        <v>-0.2146109493484598</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4348,28 +4200,28 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>-0.04283346816640132</v>
+        <v>-0.9842348262517352</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4990597395874152</v>
+        <v>0.03333450670946379</v>
       </c>
       <c r="K23" t="n">
-        <v>0.07701146774078677</v>
+        <v>-0.5646299930720617</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5045583851396825</v>
+        <v>-0.2967976987103411</v>
       </c>
       <c r="M23" t="n">
-        <v>0.191187786639902</v>
+        <v>-0.02908758978908807</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.05219479012962269</v>
+        <v>-0.1324241999865786</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>r_loans_assets</t>
+          <t>r_cti</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4378,24 +4230,24 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.008553948843064438</v>
+        <v>0.007131728509442576</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.07561025955867963</v>
+        <v>0.1569136220160213</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>lowers risk</t>
+          <t>raises risk</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4404,28 +4256,28 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>-0.288878793842746</v>
+        <v>0.1844000416927832</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5069463220709832</v>
+        <v>-0.132084392312663</v>
       </c>
       <c r="K24" t="n">
-        <v>0.08026007973424193</v>
+        <v>0.5061381036765101</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1815027688649611</v>
+        <v>0.1294272023392594</v>
       </c>
       <c r="M24" t="n">
-        <v>0.03028224974760179</v>
+        <v>0.08083912162617715</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2453835145277737</v>
+        <v>0.2391261553101574</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>r_dep_liab</t>
+          <t>x_dep</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4434,24 +4286,24 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.007007032705532137</v>
+        <v>0.005133035392215675</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.140599762983867</v>
+        <v>0.1265759856863312</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>lowers risk</t>
+          <t>raises risk</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4460,20 +4312,22 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>-0.3607412825128094</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
+        <v>0.1183190342362773</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.4696372557706476</v>
+      </c>
       <c r="K25" t="n">
-        <v>-0.140599762983867</v>
+        <v>0.1363181727316114</v>
       </c>
       <c r="L25" t="n">
-        <v>0.325176830166655</v>
+        <v>-0.001866469948011408</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1267605301309362</v>
+        <v>-0.5782162814972787</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.28857799339305</v>
+        <v>0.1348329371363851</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/results_15_11a.xlsx
+++ b/outputs/tables/results_15_11a.xlsx
@@ -466,22 +466,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.897</v>
+        <v>0.864</v>
       </c>
       <c r="C2" t="n">
-        <v>0.79</v>
+        <v>0.755</v>
       </c>
       <c r="D2" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="E2" t="n">
-        <v>0.699</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0.739</v>
       </c>
       <c r="G2" t="n">
-        <v>0.665</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="3">
@@ -491,22 +491,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.613</v>
+        <v>0.645</v>
       </c>
       <c r="C3" t="n">
-        <v>0.376</v>
+        <v>0.412</v>
       </c>
       <c r="D3" t="n">
-        <v>0.54</v>
+        <v>0.526</v>
       </c>
       <c r="E3" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="F3" t="n">
-        <v>0.53</v>
+        <v>0.653</v>
       </c>
       <c r="G3" t="n">
-        <v>0.361</v>
+        <v>0.413</v>
       </c>
     </row>
     <row r="4">
@@ -516,22 +516,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.745</v>
+        <v>0.771</v>
       </c>
       <c r="C4" t="n">
-        <v>0.579</v>
+        <v>0.61</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.642</v>
       </c>
       <c r="E4" t="n">
-        <v>0.605</v>
+        <v>0.57</v>
       </c>
       <c r="F4" t="n">
         <v>0.646</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="5">
@@ -541,22 +541,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.748</v>
+        <v>0.723</v>
       </c>
       <c r="C5" t="n">
-        <v>0.587</v>
+        <v>0.529</v>
       </c>
       <c r="D5" t="n">
-        <v>0.708</v>
+        <v>0.622</v>
       </c>
       <c r="E5" t="n">
-        <v>0.606</v>
+        <v>0.529</v>
       </c>
       <c r="F5" t="n">
-        <v>0.677</v>
+        <v>0.643</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.526</v>
       </c>
     </row>
     <row r="6">
@@ -566,22 +566,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.747</v>
+        <v>0.751</v>
       </c>
       <c r="C6" t="n">
-        <v>0.573</v>
+        <v>0.589</v>
       </c>
       <c r="D6" t="n">
-        <v>0.657</v>
+        <v>0.671</v>
       </c>
       <c r="E6" t="n">
-        <v>0.552</v>
+        <v>0.582</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.707</v>
       </c>
       <c r="G6" t="n">
-        <v>0.583</v>
+        <v>0.571</v>
       </c>
     </row>
     <row r="7">
@@ -591,22 +591,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.744</v>
+        <v>0.719</v>
       </c>
       <c r="C7" t="n">
-        <v>0.541</v>
+        <v>0.551</v>
       </c>
       <c r="D7" t="n">
-        <v>0.582</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.503</v>
+        <v>0.639</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.471</v>
+        <v>0.493</v>
       </c>
     </row>
   </sheetData>
@@ -667,17 +667,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.126</v>
+        <v>0.008</v>
       </c>
       <c r="D2" t="n">
-        <v>0.13</v>
+        <v>0.532</v>
       </c>
       <c r="E2" t="n">
-        <v>0.127</v>
+        <v>0.112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.052</t>
         </is>
       </c>
     </row>
@@ -693,17 +693,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.212</v>
+        <v>0.238</v>
       </c>
       <c r="D3" t="n">
-        <v>0.521</v>
+        <v>0.572</v>
       </c>
       <c r="E3" t="n">
-        <v>0.274</v>
+        <v>0.305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.034</t>
         </is>
       </c>
     </row>
@@ -719,17 +719,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.17</v>
+        <v>0.115</v>
       </c>
       <c r="D4" t="n">
-        <v>0.385</v>
+        <v>0.459</v>
       </c>
       <c r="E4" t="n">
-        <v>0.213</v>
+        <v>0.184</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.034</t>
         </is>
       </c>
     </row>
@@ -745,17 +745,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.189</v>
+        <v>0.111</v>
       </c>
       <c r="D5" t="n">
-        <v>0.394</v>
+        <v>0.644</v>
       </c>
       <c r="E5" t="n">
-        <v>0.23</v>
+        <v>0.218</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.021</t>
+          <t>-0.054</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.181</v>
+        <v>0.195</v>
       </c>
       <c r="D6" t="n">
-        <v>0.408</v>
+        <v>0.421</v>
       </c>
       <c r="E6" t="n">
-        <v>0.227</v>
+        <v>0.24</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.023</t>
+          <t>-0.022</t>
         </is>
       </c>
     </row>
@@ -797,17 +797,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.19</v>
+        <v>0.143</v>
       </c>
       <c r="D7" t="n">
-        <v>0.434</v>
+        <v>0.497</v>
       </c>
       <c r="E7" t="n">
-        <v>0.239</v>
+        <v>0.213</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.025</t>
+          <t>-0.035</t>
         </is>
       </c>
     </row>
@@ -823,17 +823,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.111</v>
+        <v>0.064</v>
       </c>
       <c r="D8" t="n">
-        <v>0.315</v>
+        <v>0.777</v>
       </c>
       <c r="E8" t="n">
-        <v>0.152</v>
+        <v>0.207</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.072</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.387</v>
+        <v>0.276</v>
       </c>
       <c r="D9" t="n">
-        <v>0.399</v>
+        <v>0.707</v>
       </c>
       <c r="E9" t="n">
-        <v>0.389</v>
+        <v>0.362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.043</t>
         </is>
       </c>
     </row>
@@ -875,17 +875,17 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.241</v>
       </c>
       <c r="D10" t="n">
-        <v>0.466</v>
+        <v>0.672</v>
       </c>
       <c r="E10" t="n">
-        <v>0.162</v>
+        <v>0.328</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.038</t>
+          <t>-0.043</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.195</v>
+        <v>0.246</v>
       </c>
       <c r="D11" t="n">
-        <v>0.211</v>
+        <v>0.636</v>
       </c>
       <c r="E11" t="n">
-        <v>0.199</v>
+        <v>0.324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>-0.039</t>
         </is>
       </c>
     </row>
@@ -927,17 +927,17 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.144</v>
+        <v>0.298</v>
       </c>
       <c r="D12" t="n">
-        <v>0.432</v>
+        <v>0.511</v>
       </c>
       <c r="E12" t="n">
-        <v>0.202</v>
+        <v>0.341</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.029</t>
+          <t>-0.022</t>
         </is>
       </c>
     </row>
@@ -953,17 +953,17 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1</v>
+        <v>0.184</v>
       </c>
       <c r="D13" t="n">
-        <v>0.417</v>
+        <v>0.605</v>
       </c>
       <c r="E13" t="n">
-        <v>0.163</v>
+        <v>0.268</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.042</t>
         </is>
       </c>
     </row>
@@ -979,17 +979,17 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.098</v>
+        <v>0.037</v>
       </c>
       <c r="D14" t="n">
-        <v>0.354</v>
+        <v>0.796</v>
       </c>
       <c r="E14" t="n">
-        <v>0.149</v>
+        <v>0.188</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.026</t>
+          <t>-0.076</t>
         </is>
       </c>
     </row>
@@ -1005,17 +1005,17 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.386</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.413</v>
+        <v>0.2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.003</t>
+          <t>-0.100</t>
         </is>
       </c>
     </row>
@@ -1031,17 +1031,17 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.125</v>
+        <v>0.206</v>
       </c>
       <c r="D16" t="n">
-        <v>0.442</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.188</v>
+        <v>0.303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.048</t>
         </is>
       </c>
     </row>
@@ -1057,17 +1057,17 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.282</v>
+        <v>0.246</v>
       </c>
       <c r="D17" t="n">
-        <v>0.183</v>
+        <v>0.632</v>
       </c>
       <c r="E17" t="n">
-        <v>0.262</v>
+        <v>0.323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.039</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.182</v>
+        <v>0.215</v>
       </c>
       <c r="D18" t="n">
-        <v>0.369</v>
+        <v>0.534</v>
       </c>
       <c r="E18" t="n">
-        <v>0.22</v>
+        <v>0.279</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.019</t>
+          <t>-0.032</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1109,17 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.165</v>
+        <v>0.042</v>
       </c>
       <c r="D19" t="n">
-        <v>0.477</v>
+        <v>0.784</v>
       </c>
       <c r="E19" t="n">
-        <v>0.227</v>
+        <v>0.19</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.074</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1150,12 +1150,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Brier Score</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Best Threshold</t>
+          <t>Alarm cut-off (mean over test years)</t>
         </is>
       </c>
     </row>
@@ -1171,10 +1166,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.657</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="3">
@@ -1189,10 +1181,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.473</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="4">
@@ -1207,10 +1196,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.437</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="5">
@@ -1225,10 +1211,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.436</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="6">
@@ -1243,10 +1226,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.467</v>
+        <v>0.336</v>
       </c>
     </row>
     <row r="7">
@@ -1261,10 +1241,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.223</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.466</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="8">
@@ -1279,10 +1256,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.475</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="9">
@@ -1297,10 +1271,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.379</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="10">
@@ -1315,10 +1286,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.339</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="11">
@@ -1333,10 +1301,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.488</v>
+        <v>0.207</v>
       </c>
     </row>
     <row r="12">
@@ -1351,10 +1316,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.349</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.293</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="13">
@@ -1369,10 +1331,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1387,10 +1346,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.48</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="15">
@@ -1405,10 +1361,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1423,10 +1376,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.267</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="17">
@@ -1441,10 +1391,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.535</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="18">
@@ -1459,10 +1406,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.264</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="19">
@@ -1477,10 +1421,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.404</v>
+        <v>0.041</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +1435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1550,25 +1491,20 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>brier</t>
+          <t>best_threshold</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>best_threshold</t>
+          <t>loss_07</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>loss_07</t>
+          <t>loss_09</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
-        <is>
-          <t>loss_09</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
@@ -1586,43 +1522,40 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.53</v>
+        <v>0.653</v>
       </c>
       <c r="D2" t="n">
-        <v>0.451</v>
+        <v>0.417</v>
       </c>
       <c r="E2" t="n">
-        <v>0.58</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.539</v>
+        <v>0.264</v>
       </c>
       <c r="G2" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.386</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J2" t="n">
         <v>0.413</v>
       </c>
-      <c r="J2" t="n">
-        <v>0.361</v>
-      </c>
       <c r="K2" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.667</v>
+        <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0.41</v>
+        <v>0.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.6</v>
+        <v>0.264</v>
       </c>
     </row>
     <row r="3">
@@ -1637,43 +1570,40 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.54</v>
+        <v>0.526</v>
       </c>
       <c r="D3" t="n">
-        <v>0.471</v>
+        <v>0.352</v>
       </c>
       <c r="E3" t="n">
-        <v>0.613</v>
+        <v>0.724</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.288</v>
       </c>
       <c r="G3" t="n">
-        <v>0.387</v>
+        <v>0.276</v>
       </c>
       <c r="H3" t="n">
-        <v>0.399</v>
+        <v>0.707</v>
       </c>
       <c r="I3" t="n">
-        <v>0.389</v>
+        <v>0.362</v>
       </c>
       <c r="J3" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="K3" t="n">
-        <v>0.443</v>
+        <v>0.333</v>
       </c>
       <c r="L3" t="n">
-        <v>0.379</v>
+        <v>0.406</v>
       </c>
       <c r="M3" t="n">
-        <v>0.39</v>
+        <v>0.319</v>
       </c>
       <c r="N3" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.602</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="4">
@@ -1688,43 +1618,40 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.613</v>
+        <v>0.645</v>
       </c>
       <c r="D4" t="n">
-        <v>0.501</v>
+        <v>0.463</v>
       </c>
       <c r="E4" t="n">
-        <v>0.788</v>
+        <v>0.762</v>
       </c>
       <c r="F4" t="n">
-        <v>0.382</v>
+        <v>0.348</v>
       </c>
       <c r="G4" t="n">
-        <v>0.212</v>
+        <v>0.238</v>
       </c>
       <c r="H4" t="n">
-        <v>0.521</v>
+        <v>0.572</v>
       </c>
       <c r="I4" t="n">
-        <v>0.274</v>
+        <v>0.305</v>
       </c>
       <c r="J4" t="n">
-        <v>0.376</v>
+        <v>0.412</v>
       </c>
       <c r="K4" t="n">
-        <v>0.289</v>
+        <v>0.403</v>
       </c>
       <c r="L4" t="n">
-        <v>0.473</v>
+        <v>0.338</v>
       </c>
       <c r="M4" t="n">
-        <v>0.305</v>
+        <v>0.271</v>
       </c>
       <c r="N4" t="n">
-        <v>0.243</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.516</v>
       </c>
     </row>
     <row r="5">
@@ -1739,43 +1666,40 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.707</v>
       </c>
       <c r="D5" t="n">
-        <v>0.65</v>
+        <v>0.478</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.785</v>
       </c>
       <c r="F5" t="n">
-        <v>0.634</v>
+        <v>0.409</v>
       </c>
       <c r="G5" t="n">
-        <v>0.182</v>
+        <v>0.215</v>
       </c>
       <c r="H5" t="n">
-        <v>0.369</v>
+        <v>0.534</v>
       </c>
       <c r="I5" t="n">
-        <v>0.22</v>
+        <v>0.279</v>
       </c>
       <c r="J5" t="n">
-        <v>0.583</v>
+        <v>0.571</v>
       </c>
       <c r="K5" t="n">
-        <v>0.293</v>
+        <v>0.027</v>
       </c>
       <c r="L5" t="n">
-        <v>0.264</v>
+        <v>0.311</v>
       </c>
       <c r="M5" t="n">
-        <v>0.238</v>
+        <v>0.247</v>
       </c>
       <c r="N5" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.661</v>
+        <v>0.547</v>
       </c>
     </row>
     <row r="6">
@@ -1790,43 +1714,40 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.657</v>
+        <v>0.671</v>
       </c>
       <c r="D6" t="n">
-        <v>0.586</v>
+        <v>0.391</v>
       </c>
       <c r="E6" t="n">
-        <v>0.856</v>
+        <v>0.702</v>
       </c>
       <c r="F6" t="n">
-        <v>0.503</v>
+        <v>0.553</v>
       </c>
       <c r="G6" t="n">
-        <v>0.144</v>
+        <v>0.298</v>
       </c>
       <c r="H6" t="n">
-        <v>0.432</v>
+        <v>0.511</v>
       </c>
       <c r="I6" t="n">
-        <v>0.202</v>
+        <v>0.341</v>
       </c>
       <c r="J6" t="n">
-        <v>0.552</v>
+        <v>0.582</v>
       </c>
       <c r="K6" t="n">
-        <v>0.349</v>
+        <v>0.105</v>
       </c>
       <c r="L6" t="n">
-        <v>0.293</v>
+        <v>0.362</v>
       </c>
       <c r="M6" t="n">
-        <v>0.23</v>
+        <v>0.319</v>
       </c>
       <c r="N6" t="n">
-        <v>0.173</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.644</v>
+        <v>0.542</v>
       </c>
     </row>
     <row r="7">
@@ -1841,43 +1762,40 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.747</v>
+        <v>0.751</v>
       </c>
       <c r="D7" t="n">
-        <v>0.604</v>
+        <v>0.584</v>
       </c>
       <c r="E7" t="n">
-        <v>0.819</v>
+        <v>0.805</v>
       </c>
       <c r="F7" t="n">
-        <v>0.536</v>
+        <v>0.502</v>
       </c>
       <c r="G7" t="n">
-        <v>0.181</v>
+        <v>0.195</v>
       </c>
       <c r="H7" t="n">
-        <v>0.408</v>
+        <v>0.421</v>
       </c>
       <c r="I7" t="n">
-        <v>0.227</v>
+        <v>0.24</v>
       </c>
       <c r="J7" t="n">
-        <v>0.573</v>
+        <v>0.589</v>
       </c>
       <c r="K7" t="n">
-        <v>0.238</v>
+        <v>0.336</v>
       </c>
       <c r="L7" t="n">
-        <v>0.467</v>
+        <v>0.263</v>
       </c>
       <c r="M7" t="n">
-        <v>0.249</v>
+        <v>0.218</v>
       </c>
       <c r="N7" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.654</v>
+        <v>0.637</v>
       </c>
     </row>
     <row r="8">
@@ -1895,40 +1813,37 @@
         <v>0.739</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.469</v>
       </c>
       <c r="E8" t="n">
-        <v>0.902</v>
+        <v>0.963</v>
       </c>
       <c r="F8" t="n">
-        <v>0.609</v>
+        <v>0.312</v>
       </c>
       <c r="G8" t="n">
-        <v>0.098</v>
+        <v>0.037</v>
       </c>
       <c r="H8" t="n">
-        <v>0.354</v>
+        <v>0.796</v>
       </c>
       <c r="I8" t="n">
-        <v>0.149</v>
+        <v>0.188</v>
       </c>
       <c r="J8" t="n">
-        <v>0.665</v>
+        <v>0.678</v>
       </c>
       <c r="K8" t="n">
-        <v>0.357</v>
+        <v>0.157</v>
       </c>
       <c r="L8" t="n">
-        <v>0.48</v>
+        <v>0.264</v>
       </c>
       <c r="M8" t="n">
-        <v>0.175</v>
+        <v>0.112</v>
       </c>
       <c r="N8" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.715</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="9">
@@ -1943,43 +1858,40 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="D9" t="n">
-        <v>0.718</v>
+        <v>0.468</v>
       </c>
       <c r="E9" t="n">
-        <v>0.889</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.679</v>
+        <v>0.315</v>
       </c>
       <c r="G9" t="n">
-        <v>0.111</v>
+        <v>0.064</v>
       </c>
       <c r="H9" t="n">
-        <v>0.315</v>
+        <v>0.777</v>
       </c>
       <c r="I9" t="n">
-        <v>0.152</v>
+        <v>0.207</v>
       </c>
       <c r="J9" t="n">
-        <v>0.699</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.353</v>
+        <v>0.162</v>
       </c>
       <c r="L9" t="n">
-        <v>0.475</v>
+        <v>0.278</v>
       </c>
       <c r="M9" t="n">
-        <v>0.172</v>
+        <v>0.135</v>
       </c>
       <c r="N9" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.74</v>
+        <v>0.412</v>
       </c>
     </row>
     <row r="10">
@@ -1994,43 +1906,40 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.897</v>
+        <v>0.864</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.631</v>
       </c>
       <c r="E10" t="n">
-        <v>0.874</v>
+        <v>0.992</v>
       </c>
       <c r="F10" t="n">
-        <v>0.763</v>
+        <v>0.507</v>
       </c>
       <c r="G10" t="n">
-        <v>0.126</v>
+        <v>0.008</v>
       </c>
       <c r="H10" t="n">
-        <v>0.13</v>
+        <v>0.532</v>
       </c>
       <c r="I10" t="n">
-        <v>0.127</v>
+        <v>0.112</v>
       </c>
       <c r="J10" t="n">
-        <v>0.79</v>
+        <v>0.755</v>
       </c>
       <c r="K10" t="n">
-        <v>0.186</v>
+        <v>0.286</v>
       </c>
       <c r="L10" t="n">
-        <v>0.657</v>
+        <v>0.165</v>
       </c>
       <c r="M10" t="n">
-        <v>0.127</v>
+        <v>0.06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.871</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="11">
@@ -2045,43 +1954,40 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>0.58</v>
+        <v>0.472</v>
       </c>
       <c r="E11" t="n">
-        <v>0.835</v>
+        <v>0.958</v>
       </c>
       <c r="F11" t="n">
-        <v>0.492</v>
+        <v>0.318</v>
       </c>
       <c r="G11" t="n">
-        <v>0.165</v>
+        <v>0.042</v>
       </c>
       <c r="H11" t="n">
-        <v>0.477</v>
+        <v>0.784</v>
       </c>
       <c r="I11" t="n">
-        <v>0.227</v>
+        <v>0.19</v>
       </c>
       <c r="J11" t="n">
-        <v>0.471</v>
+        <v>0.493</v>
       </c>
       <c r="K11" t="n">
-        <v>0.353</v>
+        <v>0.041</v>
       </c>
       <c r="L11" t="n">
-        <v>0.404</v>
+        <v>0.264</v>
       </c>
       <c r="M11" t="n">
-        <v>0.258</v>
+        <v>0.116</v>
       </c>
       <c r="N11" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.609</v>
+        <v>0.412</v>
       </c>
     </row>
     <row r="12">
@@ -2096,43 +2002,40 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.582</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.644</v>
+        <v>0.502</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.536</v>
+        <v>0.467</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1</v>
+        <v>0.184</v>
       </c>
       <c r="H12" t="n">
-        <v>0.417</v>
+        <v>0.605</v>
       </c>
       <c r="I12" t="n">
-        <v>0.163</v>
+        <v>0.268</v>
       </c>
       <c r="J12" t="n">
-        <v>0.503</v>
+        <v>0.639</v>
       </c>
       <c r="K12" t="n">
-        <v>0.352</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.315</v>
+        <v>0.311</v>
       </c>
       <c r="M12" t="n">
-        <v>0.195</v>
+        <v>0.226</v>
       </c>
       <c r="N12" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.67</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="13">
@@ -2147,43 +2050,40 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.744</v>
+        <v>0.719</v>
       </c>
       <c r="D13" t="n">
-        <v>0.57</v>
+        <v>0.551</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.857</v>
       </c>
       <c r="F13" t="n">
-        <v>0.469</v>
+        <v>0.422</v>
       </c>
       <c r="G13" t="n">
-        <v>0.19</v>
+        <v>0.143</v>
       </c>
       <c r="H13" t="n">
-        <v>0.434</v>
+        <v>0.497</v>
       </c>
       <c r="I13" t="n">
-        <v>0.239</v>
+        <v>0.213</v>
       </c>
       <c r="J13" t="n">
-        <v>0.541</v>
+        <v>0.551</v>
       </c>
       <c r="K13" t="n">
-        <v>0.223</v>
+        <v>0.389</v>
       </c>
       <c r="L13" t="n">
-        <v>0.466</v>
+        <v>0.249</v>
       </c>
       <c r="M13" t="n">
-        <v>0.263</v>
+        <v>0.178</v>
       </c>
       <c r="N13" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.633</v>
+        <v>0.595</v>
       </c>
     </row>
     <row r="14">
@@ -2201,40 +2101,37 @@
         <v>0.646</v>
       </c>
       <c r="D14" t="n">
-        <v>0.625</v>
+        <v>0.429</v>
       </c>
       <c r="E14" t="n">
-        <v>0.875</v>
+        <v>0.794</v>
       </c>
       <c r="F14" t="n">
-        <v>0.533</v>
+        <v>0.356</v>
       </c>
       <c r="G14" t="n">
-        <v>0.125</v>
+        <v>0.206</v>
       </c>
       <c r="H14" t="n">
-        <v>0.442</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>0.188</v>
+        <v>0.303</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="K14" t="n">
-        <v>0.209</v>
+        <v>0.16</v>
       </c>
       <c r="L14" t="n">
-        <v>0.267</v>
+        <v>0.352</v>
       </c>
       <c r="M14" t="n">
-        <v>0.22</v>
+        <v>0.255</v>
       </c>
       <c r="N14" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.645</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="15">
@@ -2249,43 +2146,40 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.642</v>
       </c>
       <c r="D15" t="n">
-        <v>0.64</v>
+        <v>0.428</v>
       </c>
       <c r="E15" t="n">
-        <v>0.914</v>
+        <v>0.759</v>
       </c>
       <c r="F15" t="n">
-        <v>0.577</v>
+        <v>0.408</v>
       </c>
       <c r="G15" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.241</v>
       </c>
       <c r="H15" t="n">
-        <v>0.466</v>
+        <v>0.672</v>
       </c>
       <c r="I15" t="n">
-        <v>0.162</v>
+        <v>0.328</v>
       </c>
       <c r="J15" t="n">
-        <v>0.605</v>
+        <v>0.57</v>
       </c>
       <c r="K15" t="n">
-        <v>0.204</v>
+        <v>0.154</v>
       </c>
       <c r="L15" t="n">
-        <v>0.339</v>
+        <v>0.371</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2</v>
+        <v>0.285</v>
       </c>
       <c r="N15" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.639</v>
+        <v>0.438</v>
       </c>
     </row>
     <row r="16">
@@ -2300,43 +2194,40 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.745</v>
+        <v>0.771</v>
       </c>
       <c r="D16" t="n">
-        <v>0.626</v>
+        <v>0.604</v>
       </c>
       <c r="E16" t="n">
-        <v>0.83</v>
+        <v>0.885</v>
       </c>
       <c r="F16" t="n">
-        <v>0.548</v>
+        <v>0.503</v>
       </c>
       <c r="G16" t="n">
-        <v>0.17</v>
+        <v>0.115</v>
       </c>
       <c r="H16" t="n">
-        <v>0.385</v>
+        <v>0.459</v>
       </c>
       <c r="I16" t="n">
-        <v>0.213</v>
+        <v>0.184</v>
       </c>
       <c r="J16" t="n">
-        <v>0.579</v>
+        <v>0.61</v>
       </c>
       <c r="K16" t="n">
-        <v>0.226</v>
+        <v>0.396</v>
       </c>
       <c r="L16" t="n">
-        <v>0.437</v>
+        <v>0.218</v>
       </c>
       <c r="M16" t="n">
-        <v>0.234</v>
+        <v>0.15</v>
       </c>
       <c r="N16" t="n">
-        <v>0.191</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.675</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="17">
@@ -2351,43 +2242,40 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.677</v>
+        <v>0.643</v>
       </c>
       <c r="D17" t="n">
-        <v>0.67</v>
+        <v>0.422</v>
       </c>
       <c r="E17" t="n">
-        <v>0.718</v>
+        <v>0.754</v>
       </c>
       <c r="F17" t="n">
-        <v>0.713</v>
+        <v>0.485</v>
       </c>
       <c r="G17" t="n">
-        <v>0.282</v>
+        <v>0.246</v>
       </c>
       <c r="H17" t="n">
-        <v>0.183</v>
+        <v>0.632</v>
       </c>
       <c r="I17" t="n">
-        <v>0.262</v>
+        <v>0.323</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.526</v>
       </c>
       <c r="K17" t="n">
-        <v>0.25</v>
+        <v>0.209</v>
       </c>
       <c r="L17" t="n">
-        <v>0.535</v>
+        <v>0.362</v>
       </c>
       <c r="M17" t="n">
-        <v>0.253</v>
+        <v>0.284</v>
       </c>
       <c r="N17" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.791</v>
+        <v>0.466</v>
       </c>
     </row>
     <row r="18">
@@ -2402,43 +2290,40 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.708</v>
+        <v>0.622</v>
       </c>
       <c r="D18" t="n">
-        <v>0.709</v>
+        <v>0.423</v>
       </c>
       <c r="E18" t="n">
-        <v>0.805</v>
+        <v>0.754</v>
       </c>
       <c r="F18" t="n">
-        <v>0.696</v>
+        <v>0.514</v>
       </c>
       <c r="G18" t="n">
-        <v>0.195</v>
+        <v>0.246</v>
       </c>
       <c r="H18" t="n">
-        <v>0.211</v>
+        <v>0.636</v>
       </c>
       <c r="I18" t="n">
-        <v>0.199</v>
+        <v>0.324</v>
       </c>
       <c r="J18" t="n">
-        <v>0.606</v>
+        <v>0.529</v>
       </c>
       <c r="K18" t="n">
-        <v>0.25</v>
+        <v>0.207</v>
       </c>
       <c r="L18" t="n">
-        <v>0.488</v>
+        <v>0.363</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2</v>
+        <v>0.285</v>
       </c>
       <c r="N18" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.794</v>
+        <v>0.464</v>
       </c>
     </row>
     <row r="19">
@@ -2453,43 +2338,40 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.748</v>
+        <v>0.723</v>
       </c>
       <c r="D19" t="n">
-        <v>0.604</v>
+        <v>0.513</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.889</v>
       </c>
       <c r="F19" t="n">
-        <v>0.527</v>
+        <v>0.398</v>
       </c>
       <c r="G19" t="n">
-        <v>0.189</v>
+        <v>0.111</v>
       </c>
       <c r="H19" t="n">
-        <v>0.394</v>
+        <v>0.644</v>
       </c>
       <c r="I19" t="n">
-        <v>0.23</v>
+        <v>0.218</v>
       </c>
       <c r="J19" t="n">
-        <v>0.587</v>
+        <v>0.529</v>
       </c>
       <c r="K19" t="n">
-        <v>0.233</v>
+        <v>0.34</v>
       </c>
       <c r="L19" t="n">
-        <v>0.436</v>
+        <v>0.271</v>
       </c>
       <c r="M19" t="n">
-        <v>0.25</v>
+        <v>0.164</v>
       </c>
       <c r="N19" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.662</v>
+        <v>0.497</v>
       </c>
     </row>
   </sheetData>
@@ -2555,10 +2437,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.174</v>
+        <v>2.256</v>
       </c>
       <c r="D2" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -2581,10 +2463,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.957</v>
+        <v>1.308</v>
       </c>
       <c r="D3" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>3</v>
@@ -2594,11 +2476,6 @@
           <t>LightGBM</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2612,10 +2489,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-1.108</v>
+        <v>0.479</v>
       </c>
       <c r="D4" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -2638,10 +2515,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.742</v>
+        <v>-3.538</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
@@ -2664,10 +2541,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-1.932</v>
+        <v>0.829</v>
       </c>
       <c r="D6" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -2690,10 +2567,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.706</v>
+        <v>3.001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
@@ -2716,10 +2593,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-2.131</v>
+        <v>0.319</v>
       </c>
       <c r="D8" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
@@ -2742,10 +2619,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-1.107</v>
+        <v>-0.318</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -2768,10 +2645,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-4.19</v>
+        <v>-2.833</v>
       </c>
       <c r="D10" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
@@ -2794,10 +2671,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-4.297</v>
+        <v>-3.369</v>
       </c>
       <c r="D11" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -2820,10 +2697,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-2.14</v>
+        <v>-2.174</v>
       </c>
       <c r="D12" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
@@ -2846,10 +2723,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-1.46</v>
+        <v>-1.586</v>
       </c>
       <c r="D13" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>3</v>
@@ -2937,16 +2814,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.174</v>
+        <v>2.256</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.131</v>
+        <v>0.319</v>
       </c>
       <c r="D4" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2956,21 +2833,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.957</v>
+        <v>1.308</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.107</v>
+        <v>-0.318</v>
       </c>
       <c r="D5" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2980,16 +2852,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.108</v>
+        <v>0.479</v>
       </c>
       <c r="C6" t="n">
-        <v>-4.19</v>
+        <v>-2.833</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.333</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.667</v>
       </c>
     </row>
     <row r="7">
@@ -2999,16 +2871,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.742</v>
+        <v>-3.538</v>
       </c>
       <c r="C7" t="n">
-        <v>-4.297</v>
+        <v>-3.369</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="E7" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="8">
@@ -3018,16 +2890,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.932</v>
+        <v>0.829</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.14</v>
+        <v>-2.174</v>
       </c>
       <c r="D8" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="9">
@@ -3037,16 +2909,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.706</v>
+        <v>3.001</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.46</v>
+        <v>-1.586</v>
       </c>
       <c r="D9" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3152,10 +3024,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9265863122647752</v>
+        <v>0.9971524660289562</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.8501461146113416</v>
+        <v>-0.8617030942111585</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3178,22 +3050,22 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>-0.9560395534847204</v>
+        <v>-0.943717525843264</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.7614875654324363</v>
+        <v>-0.7305125363825457</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.8596650558447358</v>
+        <v>-0.909929771407867</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.9207121452627373</v>
+        <v>-0.9012910916089705</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8406271733779473</v>
+        <v>-0.8221150968133466</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7654476686680941</v>
+        <v>-0.8079735986439772</v>
       </c>
     </row>
     <row r="3">
@@ -3208,10 +3080,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.6542367001081102</v>
+        <v>0.7732220326114602</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7863099168273141</v>
+        <v>0.8025268706300158</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3234,22 +3106,22 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.7602334581970298</v>
+        <v>0.6504462261562497</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6359875800366256</v>
+        <v>0.7879313815936232</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8290485760380926</v>
+        <v>0.8541570001773346</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8657536232434998</v>
+        <v>0.8171223596664084</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8024969368506468</v>
+        <v>0.885023295478968</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7701228968039814</v>
+        <v>0.7536925535010178</v>
       </c>
     </row>
     <row r="4">
@@ -3264,10 +3136,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.5710484494305808</v>
+        <v>0.635818258795403</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5505683435119144</v>
+        <v>-0.4663490100269996</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3276,7 +3148,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3290,22 +3162,22 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>-0.3060631041203119</v>
+        <v>-0.3514986130714824</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.5910784730513579</v>
+        <v>-0.1352585334824077</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5111258226201523</v>
+        <v>-0.4890332395422311</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5586845865036839</v>
+        <v>-0.4627507601567506</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5424521005201449</v>
+        <v>-0.4699472598972486</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5739820287820051</v>
+        <v>-0.630319516011782</v>
       </c>
     </row>
     <row r="5">
@@ -3320,19 +3192,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.3275418728407907</v>
+        <v>0.4037932344311975</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9029537103531189</v>
+        <v>0.8698586830507399</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3342,26 +3214,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>reportable</t>
+          <t>non-monotone</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.8850546727255526</v>
+        <v>0.8860782092369827</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5002986811705231</v>
+        <v>0.4077205769921546</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9214079847251373</v>
+        <v>0.8305206487279593</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9350347558674083</v>
+        <v>0.9027316644597486</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9208527479806852</v>
+        <v>0.8536391568644971</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8561962013528077</v>
+        <v>0.9211463708004842</v>
       </c>
     </row>
     <row r="6">
@@ -3376,14 +3248,14 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.2773734126547638</v>
+        <v>0.285406615105275</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3493613287215372</v>
+        <v>0.3502765102653616</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3398,26 +3270,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>weak/noisy</t>
+          <t>non-monotone</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>-0.1032107381408622</v>
+        <v>0.2816895121901261</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4174638922038403</v>
+        <v>0.1592151818938076</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7363635532739682</v>
+        <v>0.6629717940948511</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2812587652392342</v>
+        <v>0.6908056545155293</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7427053615415067</v>
+        <v>0.418863508340597</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.241150567660822</v>
+        <v>-0.2456291221485024</v>
       </c>
     </row>
     <row r="7">
@@ -3432,10 +3304,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2561800350696424</v>
+        <v>0.2810111112678593</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4208330499318674</v>
+        <v>-0.4174999247462483</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3444,7 +3316,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3458,22 +3330,22 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>-0.7931592247819945</v>
+        <v>-0.8024041157697863</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3967241847934448</v>
+        <v>-0.4013925516699274</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3895043791282821</v>
+        <v>-0.422500150182836</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.44494191507029</v>
+        <v>-0.4124996993096606</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3531146271776288</v>
+        <v>-0.3424351096119927</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5208725287142381</v>
+        <v>-0.6657040913952907</v>
       </c>
     </row>
     <row r="8">
@@ -3488,14 +3360,14 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1193977124790572</v>
+        <v>0.1829969781032568</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04557599331390627</v>
+        <v>0.269101322863253</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3514,22 +3386,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>-0.09629930569732617</v>
+        <v>-0.2680652635089166</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2454631318451621</v>
+        <v>-0.1823399126904421</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09215629152405835</v>
+        <v>0.2907075620784701</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2797573075974532</v>
+        <v>0.5658010782867997</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1125944690013834</v>
+        <v>0.4480516942195223</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.001004304896245808</v>
+        <v>0.2474950836480359</v>
       </c>
     </row>
     <row r="9">
@@ -3544,10 +3416,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.1011193558996304</v>
+        <v>0.1371707299478813</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5115169928661184</v>
+        <v>0.5778066829152961</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -3570,22 +3442,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9446948581645295</v>
+        <v>0.9080295048877592</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2055171304562143</v>
+        <v>0.4900434635081176</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7609499101432272</v>
+        <v>0.714121374230541</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5563630746846909</v>
+        <v>0.6042803852534195</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4666709110475459</v>
+        <v>0.5513329805771727</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3471567092015995</v>
+        <v>0.5072176173294635</v>
       </c>
     </row>
     <row r="10">
@@ -3600,10 +3472,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.09082432606716123</v>
+        <v>0.1093728316745451</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4294555279147809</v>
+        <v>0.4500445822596705</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -3626,28 +3498,28 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>-0.3338476561245598</v>
+        <v>-0.2291476560397598</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5715904730313753</v>
+        <v>0.4699040102876081</v>
       </c>
       <c r="K10" t="n">
-        <v>0.546826040018039</v>
+        <v>0.4301851542317328</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5229421000588953</v>
+        <v>0.5706736180370495</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3359689557706665</v>
+        <v>0.4883765289454305</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1353174598395</v>
+        <v>-0.4266538629364948</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>p_roe</t>
+          <t>l_assets</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3656,10 +3528,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.05473046835154706</v>
+        <v>0.05455986895651982</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4777226175957648</v>
+        <v>0.9037655173395067</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -3673,7 +3545,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>lowers risk</t>
+          <t>raises risk</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3682,20 +3554,20 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>-0.8829776051711064</v>
+        <v>0.9257989032257974</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>-0.6966622873865808</v>
+        <v>0.9037655173395067</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3846476250237861</v>
+        <v>0.5537261904001473</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4777226175957648</v>
+        <v>0.6308261750146125</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4393462907808177</v>
+        <v>0.9450913896453453</v>
       </c>
     </row>
     <row r="12">
@@ -3710,10 +3582,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04293170879251015</v>
+        <v>0.04750747405447954</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4521540911098725</v>
+        <v>-0.6315566736568541</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3722,7 +3594,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3732,32 +3604,32 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>non-monotone</t>
+          <t>reportable</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>-0.9399936133719057</v>
+        <v>-0.9680322160414889</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3529095816908794</v>
+        <v>0.08582894523125513</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7061009443174298</v>
+        <v>-0.758712926954521</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1391119653083442</v>
+        <v>-0.5660179020189927</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1426358921537539</v>
+        <v>-0.1083185707935747</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5513986005288657</v>
+        <v>-0.6970954452947156</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>l_assets</t>
+          <t>l_loans</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3766,54 +3638,48 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02786723628180906</v>
+        <v>0.03963031163613973</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7212820164239462</v>
+        <v>-0.6629237660872213</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>reportable</t>
+          <t>weak/noisy</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9593608852380473</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.2912548156217548</v>
-      </c>
+        <v>-0.6629237660872213</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>0.744583230804149</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.8334196791731932</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.6979808020437432</v>
-      </c>
+        <v>0.0250085759934885</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>0.305870586292858</v>
+        <v>-0.7489684858720682</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>p_roa</t>
+          <t>p_roe</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3822,10 +3688,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02295011574974603</v>
+        <v>0.03612834372156064</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3467844784464797</v>
+        <v>-0.6355317729002429</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3834,7 +3700,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3848,28 +3714,26 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6056669098469238</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-0.2220149032530638</v>
-      </c>
+        <v>-0.8849634633075203</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>-0.8520520887291622</v>
+        <v>-0.8460976355397243</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4510167188506159</v>
+        <v>-0.53799356206764</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4870885407404747</v>
+        <v>-0.06435203800817428</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2425522380423436</v>
+        <v>-0.6355317729002429</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>r_cti</t>
+          <t>r_dep_liab</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3878,54 +3742,52 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.01843497381777106</v>
+        <v>0.02230221831509959</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3284025128537458</v>
+        <v>-0.4322365877871074</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>reportable</t>
+          <t>weak/noisy</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.1739525125801134</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.03130369573642432</v>
-      </c>
+        <v>0.8943827147301482</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>0.5729904391587065</v>
+        <v>-0.5619245074715747</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7886989191386873</v>
+        <v>-0.4322365877871074</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4828525131273782</v>
+        <v>-0.5637553044965622</v>
       </c>
       <c r="N15" t="n">
-        <v>0.01535865970019359</v>
+        <v>0.6011326463372367</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>x_loans_gross</t>
+          <t>inc_nii</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3934,19 +3796,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.01721962998688673</v>
+        <v>0.02039040340839227</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1527592351245601</v>
+        <v>0.5018623150423902</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -3956,30 +3818,30 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>weak/noisy</t>
+          <t>reportable</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.2583954166090168</v>
+        <v>0.7516115515597954</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>0.1527592351245601</v>
+        <v>0.7114079660101814</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.01890137895093107</v>
+        <v>0.5018623150423902</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4847434414606122</v>
+        <v>0.4697244344447229</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2235916619418466</v>
+        <v>0.2607697157701903</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>c_eqratio</t>
+          <t>r_loans_assets</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3988,24 +3850,24 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01675021584638044</v>
+        <v>0.01665972827862254</v>
       </c>
       <c r="D17" t="n">
-        <v>0.05282997114440009</v>
+        <v>-0.07450750803089595</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4014,28 +3876,26 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>-0.9442227256629292</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.6743117087762643</v>
-      </c>
+        <v>-0.07450750803089595</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
-        <v>-0.1443095191281283</v>
+        <v>-0.3546238307953481</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2671898290856319</v>
+        <v>-0.6970985374420995</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2267675931589018</v>
+        <v>-0.05414368951207644</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1211076508701016</v>
+        <v>0.032698419965724</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>c_leverage</t>
+          <t>x_ib_liab</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4044,10 +3904,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01628334930962503</v>
+        <v>0.01298087987243366</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02090598614255212</v>
+        <v>0.0009608045733943529</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -4056,7 +3916,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4070,28 +3930,26 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8554233531278415</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-0.01372941228540354</v>
-      </c>
+        <v>-0.7804448673180101</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>0.05554138457050777</v>
+        <v>0.7635419235149985</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3125672931641892</v>
+        <v>0.5819637289638131</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4699844374802075</v>
+        <v>0.0009608045733943529</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1245702620095101</v>
+        <v>-0.05198815825662495</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>inc_nii</t>
+          <t>c_leverage</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4100,10 +3958,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0158586996350084</v>
+        <v>0.01261229274935117</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2446780438675702</v>
+        <v>0.4743939883758932</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -4112,7 +3970,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4122,30 +3980,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>weak/noisy</t>
+          <t>non-monotone</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7957428921585367</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
+        <v>-0.2032347911108028</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.4801415635549076</v>
+      </c>
       <c r="K19" t="n">
-        <v>0.4629312423976412</v>
+        <v>0.4686464131968788</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2042913840283628</v>
+        <v>0.4928238744949666</v>
       </c>
       <c r="M19" t="n">
-        <v>0.07114333173461385</v>
+        <v>0.621779080033969</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2446780438675702</v>
+        <v>0.3858314268112985</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>l_loans</t>
+          <t>p_roa</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4154,10 +4014,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01579385868721337</v>
+        <v>0.01183248406885384</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2102211965039827</v>
+        <v>-0.5730741746186684</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -4166,42 +4026,40 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>weak/noisy</t>
+          <t>reportable</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>-0.9216271484216884</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.3691480340409087</v>
-      </c>
+        <v>-0.3632718576411123</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>0.1271015883484623</v>
+        <v>-0.9085783904150433</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6160627695018456</v>
+        <v>-0.5258955921487589</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2933408046595032</v>
+        <v>-0.6367129310557801</v>
       </c>
       <c r="N20" t="n">
-        <v>0.06074357636202452</v>
+        <v>-0.5730741746186684</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>inc_op</t>
+          <t>x_loans_gross</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4210,24 +4068,24 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.014775861726635</v>
+        <v>0.01026555298420267</v>
       </c>
       <c r="D21" t="n">
-        <v>0.03879948696708894</v>
+        <v>-0.4044127229023147</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>raises risk</t>
+          <t>lowers risk</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -4236,28 +4094,26 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>-0.7854007029733936</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.0956584239277749</v>
-      </c>
+        <v>-0.5372212073351369</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>0.6035777785626077</v>
+        <v>0.08322321379617216</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3435087042773529</v>
+        <v>-0.4044127229023147</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1077717961005886</v>
+        <v>-0.5375088934227307</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.01805944999359701</v>
+        <v>-0.06684031490237409</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>x_dep</t>
+          <t>inc_op</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4266,19 +4122,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01394502921070186</v>
+        <v>0.008513593227194796</v>
       </c>
       <c r="D22" t="n">
-        <v>0.02092406826779631</v>
+        <v>0.3270519497277334</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4292,28 +4148,26 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.01908724499681764</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.01078215976994487</v>
-      </c>
+        <v>-0.08706012573180018</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="n">
-        <v>0.1969284645667818</v>
+        <v>0.7162207315899987</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02276089153877498</v>
+        <v>0.3270519497277334</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1156350731373365</v>
+        <v>0.4175276765308683</v>
       </c>
       <c r="N22" t="n">
-        <v>0.316506137619509</v>
+        <v>-0.1464205616604819</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>x_ib_liab</t>
+          <t>c_eqratio</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4322,19 +4176,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.009152551474894551</v>
+        <v>0.00769064252432819</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.04751412914801201</v>
+        <v>-0.1825692663712086</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4348,28 +4202,26 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>-0.04283346816640132</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-0.4990597395874152</v>
-      </c>
+        <v>-0.9843525203754511</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
-        <v>0.07701146774078677</v>
+        <v>-0.5678863727383976</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5045583851396825</v>
+        <v>-0.1825692663712086</v>
       </c>
       <c r="M23" t="n">
-        <v>0.191187786639902</v>
+        <v>0.1734833414207651</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.05219479012962269</v>
+        <v>0.2100874047658071</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>r_loans_assets</t>
+          <t>r_cti</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4378,24 +4230,24 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.008553948843064438</v>
+        <v>0.006272613149943773</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.07561025955867963</v>
+        <v>0.03404641024846812</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>lowers risk</t>
+          <t>raises risk</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4404,28 +4256,28 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>-0.288878793842746</v>
+        <v>0.1843740786698423</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5069463220709832</v>
+        <v>-0.07737215590971719</v>
       </c>
       <c r="K24" t="n">
-        <v>0.08026007973424193</v>
+        <v>0.4147986454866427</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1815027688649611</v>
+        <v>0.00700265169913446</v>
       </c>
       <c r="M24" t="n">
-        <v>0.03028224974760179</v>
+        <v>-0.02988792819016232</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2453835145277737</v>
+        <v>0.06109016879780178</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>r_dep_liab</t>
+          <t>x_dep</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4434,24 +4286,24 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.007007032705532137</v>
+        <v>0.004397996844469555</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.140599762983867</v>
+        <v>0.1183779465183502</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>lowers risk</t>
+          <t>raises risk</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4460,20 +4312,20 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>-0.3607412825128094</v>
+        <v>0.1183779465183502</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
-        <v>-0.140599762983867</v>
+        <v>0.4583066914366907</v>
       </c>
       <c r="L25" t="n">
-        <v>0.325176830166655</v>
+        <v>0.6312784322616585</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1267605301309362</v>
+        <v>0.07569149990528727</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.28857799339305</v>
+        <v>0.04666805972272759</v>
       </c>
     </row>
   </sheetData>
